--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1353,7 +1353,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
+    <row r="66" ht="18" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
           <t>想定給与（概算給与）</t>
@@ -1361,8 +1361,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>月給者：単位給与額
-時給者：単位給与額 × 所定労働時間</t>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -1490,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
+    <row r="74" ht="18" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
           <t>交通費</t>
@@ -1498,8 +1497,7 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>月額：そのまま
-日額：単位交通費 × 出勤日数</t>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -2063,7 +2061,7 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="20" customHeight="1">
+    <row r="120" ht="18" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
           <t>② エクスポートデータ詳細選択</t>
@@ -2071,8 +2069,7 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>設定：対象（複数選択可）＋データ項目
-実績：給与実績の月＋データ項目</t>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
@@ -2510,12 +2507,12 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>~~1~~</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>~~月の途中で給与が変わる場合の計算例~~</t>
+          <t>月の途中で給与が変わる場合の計算例</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -2532,12 +2529,12 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>~~2~~</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>~~ヘルプ勤務の人件費の計上先~~</t>
+          <t>ヘルプ勤務の人件費の計上先</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2554,12 +2551,12 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>~~3~~</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>~~交通費が人件費に含まれるか~~</t>
+          <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,10 +52,6 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11.5"/>
     </font>
   </fonts>
   <fills count="4">
@@ -102,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,8 +115,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2261,150 +2256,443 @@
     <row r="136" ht="24" customHeight="1">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>移行について</t>
+          <t>権限による違い</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="28" customHeight="1">
+          <t>オーナー・会社</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>人件費実績の閲覧</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>月次の締め・締め解除</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="28" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>本機能の対象外</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>対象外の内容</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース（手動編集／CSVインポート）</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="28" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="55">
     <mergeCell ref="A137:C137"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A163:C163"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A95:C95"/>
@@ -2419,13 +2707,16 @@
     <mergeCell ref="A126:C126"/>
     <mergeCell ref="A135:C135"/>
     <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A144:C144"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A156:C156"/>
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A125:C125"/>
     <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A152:C152"/>
     <mergeCell ref="A63:C63"/>
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A31:C31"/>
@@ -2435,7 +2726,10 @@
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A157:C157"/>
     <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="A169:C169"/>
     <mergeCell ref="A107:C107"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
@@ -2446,6 +2740,7 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A162:C162"/>
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
@@ -2459,7 +2754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2468,56 +2763,93 @@
     <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>ヘルプページ 掲載前チェック（社内用・顧客には出しません）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>■ 判断待ちで確定できない箇所</t>
+          <t>判断待ちで確定できない箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>待っている判断</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>月の途中で給与が変わる場合の計算例</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>判断1＝所定労働日割</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>箇所</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>待っている判断</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>期限</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ勤務の人件費の計上先</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>月の途中で給与が変わる場合の計算例</t>
+          <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>判断1＝所定労働日割</t>
+          <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2529,61 +2861,61 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ勤務の人件費の計上先</t>
+          <t>深夜残業代の金額</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
+          <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>✅ 2026-08-03 確定・本文へ反映済み</t>
+          <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>交通費が人件費に含まれるか</t>
+          <t>みなし残業を超えた/届かなかったときの扱い</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
+          <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>✅ 2026-08-03 確定・本文へ反映済み</t>
+          <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代の金額</t>
+          <t>人件費実績のモーダルから直したときの適用日付</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
+          <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2595,602 +2927,557 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>みなし残業を超えた/届かなかったときの扱い</t>
+          <t>翌月で差額を調整する条件</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
+          <t>判断2（対象費目）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>実装前</t>
+          <t>次段階可</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>人件費実績のモーダルから直したときの適用日付</t>
+          <t>「設定インポート」「設定取込データ」の画面名</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
+          <t>判断3・4（名称の統一）</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>実装前</t>
+          <t>リリースまで</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>翌月で差額を調整する条件</t>
+          <t>権限による違いの表</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>判断2（対象費目）</t>
+          <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>次段階可</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>「設定インポート」「設定取込データ」の画面名</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>判断3・4（名称の統一）</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
           <t>リリースまで</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>実装確認が必要な箇所</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>権限による違いの表</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>リリースまで</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>■ 実装確認が必要な箇所</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>確認すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>予約した変更の取り消し手順</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>実装されているか、手順は何か</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>箇所</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>確認すること</t>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>従業員を削除したときの過去実績の扱い</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>実績が残るか、消えるか</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>予約した変更の取り消し手順</t>
+          <t>締め解除の記録（誰が・いつ）</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>実装されているか、手順は何か</t>
+          <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>従業員を削除したときの過去実績の扱い</t>
+          <t>締め済み期間への適用時の警告表示</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>実績が残るか、消えるか</t>
+          <t>警告が出るか（モック未実装。T-D07）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>締め解除の記録（誰が・いつ）</t>
+          <t>締め実行時の事前チェック</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
+          <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間への適用時の警告表示</t>
+          <t>CSV取り込みのエラー表示</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>警告が出るか（モック未実装。T-D07）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>締め実行時の事前チェック</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
+          <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>撮影が必要なスクリーンショット（12枚）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>CSV取り込みのエラー表示</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>■ 撮影が必要なスクリーンショット（12枚）</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>撮影する状態</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>対応する検証ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>サイドバー</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>「従業員管理」を展開した状態（7項目）</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>T-Z04</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>撮影する状態</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>対応する検証ID</t>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>右上のテンプレートDLボタンが見える状態</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>T-I02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>サイドバー</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>「従業員管理」を展開した状態（7項目）</t>
+          <t>CSVをドロップし、取り込み列設定が表示された状態</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-I03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員登録</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>右上のテンプレートDLボタンが見える状態</t>
+          <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-R04</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>CSVをドロップし、取り込み列設定が表示された状態</t>
+          <t>適用日付の入力欄と設定変更履歴が見える状態</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-D01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
+          <t>フィルタ（変更ソース・期間）が見える状態</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>T-R04</t>
+          <t>T-H04</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>適用日付の入力欄と設定変更履歴が見える状態</t>
+          <t>月別実績・実績モードで内訳の列が出た状態</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>T-D01</t>
+          <t>T-A02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>フィルタ（変更ソース・期間）が見える状態</t>
+          <t>締めの確認モーダル</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-S03</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>月別実績・実績モードで内訳の列が出た状態</t>
+          <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-D07</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>締めの確認モーダル</t>
+          <t>①②が選択され、データ項目カードが見える状態</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-E04</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
+          <t>実績データ取込中の進捗モーダル</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-A08</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>①②が選択され、データ項目カードが見える状態</t>
+          <t>前回差分表示のモーダル（前回→新規の差）</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-N02</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>実績データ取込中の進捗モーダル</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>T-A08</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>前回差分表示のモーダル（前回→新規の差）</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>T-N02</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>※ 撮影は実装完了後の画面で行ってください。 モックの画面をそのまま掲載すると、実装との差異が顧客に見えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>掲載の可否</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>撮影は実装完了後の画面で行ってください。 モックの画面をそのまま掲載すると、実装との差異が顧客に見えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>■ 掲載の可否</t>
+          <t>判断1・5・6が確定し（2026-08-03）、人件費の説明を本文に反映しました。 残る掲載条件は次の2つです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>1. 判断7・8の確認（深夜残業の割増率／みなし残業の超過・未達の扱い）— 法定に沿った暫定値を適用しています</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>判断1・5・6が確定し（2026-08-03）、人件費の説明を本文に反映しました。 残る掲載条件は次の2つです。</t>
+          <t>2. 実装状況の確認と画面の撮影（未実装の機能を説明したまま公開しない）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1. 判断7・8の確認（深夜残業の割増率／みなし残業の超過・未達の扱い）— 法定に沿った暫定値を適用しています</t>
+          <t>- 判断7・8の確認 → 8/7 第1回ジャッジ</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2. 実装状況の確認と画面の撮影（未実装の機能を説明したまま公開しない）</t>
+          <t>- M4（ヘルプページ作成）→ 8/12〜8/13</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>- 判断7・8の確認 → 8/7 第1回ジャッジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>- M4（ヘルプページ作成）→ 8/12〜8/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
           <t>- リリース Go/No-Go 判定 → 8/14</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A38:D38"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48" ht="28" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。</t>
+          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
@@ -1631,1114 +1631,1209 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えた14列です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="28" customHeight="1">
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>対象の従業員の設定編集モーダルを開く</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>14項目（名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>更新保存</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>変更を保存し、人件費実績に戻る</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>変更の経路で絞り込み</t>
+          <t>数字が再計算されます</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>変更せずに閉じる</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えた14列です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路で絞り込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
           <t>店舗・雇用区分</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>対象者で絞り込み</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>編集日時範囲</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>入力した日時の期間で絞り込み</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr"/>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>従業員名</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="C97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>CSVテンプレート</t>
+          <t>編集日時範囲</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
-        </is>
-      </c>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr"/>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>データ種類</t>
+          <t>従業員名</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>King of Time／ジョブカン／新規作成</t>
+          <t>氏名で検索</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>CSV位置合わせ設定</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>例</t>
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>CSVテンプレート</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>セミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>青山店;新宿店</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr"/>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
+          <t>保存済みの列の対応づけ</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>青山店:700;新宿店:900</t>
+          <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+          <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>記法</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>例</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
+          <t>セミコロン区切り</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
           <t>編集・削除</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>保存済みテンプレートの変更</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C113" s="7" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>① エクスポート種別</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>設定／実績</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>① エクスポート種別</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>設定／実績</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
           <t>② エクスポートデータ詳細選択</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>データ項目のカテゴリ</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>給与設定</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>前回の取込との差を表示</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr">
         <is>
           <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>読み込み</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>取込を実行</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>進捗を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>オーナー・会社</t>
+          <t>タブ</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>店長</t>
+          <t>画面間の移動</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>設定取込データ</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>従業員設定／給与設定</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・会社</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>権限設定によります</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="24" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>エラーが表示されたときは</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>人件費実績の閲覧</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードが空</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードは必須です。全行にご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
           <t>従業員コードが重複</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>同じコードの従業員は登録できません。コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>金額がマイナス・数字以外</t>
-        </is>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="28" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>設定を保存できない場合は次をご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="24" customHeight="1">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>移行について</t>
+          <t>お問い合わせ</t>
         </is>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="28" customHeight="1">
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>対象の従業員コードと年月</t>
         </is>
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
       <c r="A166" s="7" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>画面に表示されたメッセージ</t>
         </is>
       </c>
       <c r="B166" s="7" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>該当画面</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="28" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>対象外の内容</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1">
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="28" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="172" ht="18" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
           <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t>権限設定</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A108:C108"/>
+  <mergeCells count="57">
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A113:C113"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A175:C175"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A85:C85"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A131:C131"/>
     <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A122:C122"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A109:C109"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A152:C152"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A93:C93"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A127:C127"/>
     <mergeCell ref="A143:C143"/>
+    <mergeCell ref="A92:C92"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A114:C114"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A148:C148"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A157:C157"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A94:C94"/>
     <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A123:C123"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A78:C78"/>
     <mergeCell ref="A162:C162"/>
     <mergeCell ref="A87:C87"/>
@@ -2766,7 +2861,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>判断待ちで確定できない箇所</t>
+          <t>ヘルプページ 掲載前チェック（社内用・顧客には出しません）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,2331 +513,2925 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>会社スコープ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理メニューは2つのグループで構成しております。</t>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>導入時（最初の1回）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>グループ</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>メニュー</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>画面</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>閲覧・管理</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>店舗マスタを登録する</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>従業員の設定を一覧で確認・登録・編集</t>
+          <t>店舗管理</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>閲覧・管理</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員の設定をCSVで一括登録する</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>閲覧・管理</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>取り込んだ内容を確認する</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>不足分を1名ずつ登録する</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>項目を選択してCSVで出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データを確認</t>
+          <t>従業員一覧 → 従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>毎月の運用</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>月次の人件費を確認する</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わない場合は元データを確認する</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ／従業員設定履歴</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>従業員の氏名</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>クリックで従業員詳細へ遷移</t>
+          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>勤怠データとの突合に使用するコード</t>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>重複した登録は不可</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>所属店舗</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>主に勤務する店舗</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>1店舗のみ設定可能。人件費の計上先</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>応援に行く店舗</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>複数設定可能</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイト</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>給与単位</t>
+          <t>従業員を1名登録する</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>月給／時給</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr"/>
+          <t>従業員一覧 → 従業員登録</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>単位給与額</t>
+          <t>給与改定を予約する</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>月給額または時給額</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
+          <t>従業員詳細（適用日付に未来日を入力）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>交通費単位</t>
+          <t>変更の経緯を確認する</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>日額／月額</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr"/>
+          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>単位交通費</t>
+          <t>数字を見ながらその場で設定を直す</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>交通費の金額</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr"/>
+          <t>人件費実績 →「従業員設定」</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>締めたあとに修正が必要になった</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>みなし残業時間</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+          <t>人件費実績 →「締め解除」→ 修正 → 再度「締め」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>会社スコープ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理メニューは2つのグループで構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>メニュー</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を一覧で確認・登録・編集</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>入力項目</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認。月次の締めを実行</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>従業員の氏名</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>全従業員の設定変更履歴を横断で確認</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>勤怠データとの突合コード</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>必須。既存と重複する場合は登録不可</t>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>必須。1店舗のみ</t>
+          <t>項目を選択してCSVで出力</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>設定取込データ</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>取り込んだ設定の元データを確認</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>データ連携</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>給与単位・単位給与額</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>月給／時給と金額</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>交通費単位・単位交通費</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>日額／月額と金額</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr"/>
+          <t>取り込んだ勤怠実績の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>応援先ごとの交通費</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>移動元</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>移動先</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr"/>
+          <t>名前をクリック／詳細アイコン</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr"/>
+          <t>「従業員登録」</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>適用日付</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>この内容が有効となる日付</t>
+          <t>「設定インポート」</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>必須。初期値は当日</t>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>「設定・実績エクスポート」</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>2段目「設定取込データへ」</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>「保存」／「一覧へ戻る」</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>「実績データ取込」</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>取込中の進捗表示 → 人件費実績に反映</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>未来日</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
+          <t>「従業員設定」</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>設定変更履歴に「予約中」で追加</t>
+          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>当日・過去日</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>「即時反映しました」と表示。その時点から反映</t>
+          <t>「実績取込データへ」</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>設定変更履歴に「適用中」で追加</t>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間内</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>警告を表示。反映されない</t>
+          <t>「人件費実績へ」</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>締め済みの月は変更不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴は全14列で構成しております。</t>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>名前をクリック</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>「列マッピングテンプレート管理」</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>「登録」</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>適用日付と同じ</t>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>編集日時</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>設定を入力した日時</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>変更反映日時とは異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>変更の経路を記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>その他の列</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>変更時点の値</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>従業員の氏名</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>クリックで従業員詳細へ遷移</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>勤怠データとの突合に使用するコード</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>重複した登録は不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>主に勤務する店舗</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>1店舗のみ設定可能。人件費の計上先</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>複数設定可能</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイト</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr"/>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>給与単位</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
-        </is>
-      </c>
+          <t>月給／時給</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>単位給与額</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>月給額または時給額</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>交通費単位</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
+          <t>日額／月額</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>みなし労働時間差分</t>
+          <t>単位交通費</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
-        </is>
-      </c>
+          <t>交通費の金額</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代</t>
+          <t>所定労働時間</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
-        </is>
-      </c>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>給与（実績給与）</t>
+          <t>みなし残業時間</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>所属店舗労働時間</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>総労働時間 − ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>日別実績の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>交通費</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>給与とは別の費目</t>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>総支給額</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr"/>
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>入力項目</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>従業員の氏名</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>勤怠データとの突合コード</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>必須。既存と重複する場合は登録不可</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>※ 日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績タブにのみ表示されます。</t>
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>主に勤務する店舗</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>必須。1店舗のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイト</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>締め前</t>
+          <t>給与単位・単位給与額</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>月給／時給と金額</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>締め後</t>
+          <t>交通費単位・単位交通費</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
+          <t>日額／月額と金額</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr"/>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>締め解除後</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>応援先ごとの交通費</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>この内容が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>必須。初期値は当日</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>設定変更履歴に「予約中」で追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>当日・過去日</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>「即時反映しました」と表示。その時点から反映</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>設定変更履歴に「適用中」で追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>締め済み期間内</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>警告を表示。反映されない</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>締め済みの月は変更不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴は全14列で構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="42" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員の設定編集モーダルを開く</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>14項目（名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>更新保存</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>変更を保存し、人件費実績に戻る</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>数字が再計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>キャンセル</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>変更せずに閉じる</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えた14列です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>変更の経路で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>店舗・雇用区分</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr"/>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>適用日付と同じ</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>編集日時範囲</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>入力した日時の期間で絞り込み</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr"/>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>従業員名</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>適用日を迎えると予約中→適用中に変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>その他の列</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>変更時点の値</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
+          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>データ種類</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C106" s="7" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>先頭に説明行があるCSVに対応</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>取り込み列設定</t>
+          <t>想定給与（概算給与）</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>CSV列とラクミー項目の対応</t>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>勤怠実績の実働時間の合計</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>例</t>
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>みなし労働時間差分</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>セミコロン区切り</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>青山店;新宿店</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>青山店:700;新宿店:900</t>
+          <t>交通費は含みません</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗労働時間</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>日別実績の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>総支給額</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
-        </is>
-      </c>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr"/>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>※ 日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績タブにのみ表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>締め前</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>締め後</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>① エクスポート種別</t>
+          <t>締め解除後</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>設定／実績</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>② エクスポートデータ詳細選択</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>データ項目のカテゴリ</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="42" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>設定取込データ／実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ元のデータを確認する画面です。</t>
-        </is>
-      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>対象の従業員の設定編集モーダルを開く</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>14項目（名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>更新保存</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>変更を保存し、人件費実績に戻る</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>数字が再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>変更せずに閉じる</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr"/>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えた14列です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C135" s="7" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>前回差分表示</t>
-        </is>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>前回の取込との差を表示</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="inlineStr">
-        <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>読み込み</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>取込を実行</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>進捗を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>店舗・雇用区分</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
-        </is>
-      </c>
+          <t>対象者で絞り込み</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr"/>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>編集日時範囲</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
-        </is>
-      </c>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr"/>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>オーナー・会社</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>店長</t>
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>従業員名</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>氏名で検索</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C145" s="7" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>CSVテンプレート</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr"/>
     </row>
     <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="24" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>エラーが表示されたときは</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>保存済みの列の対応づけ</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>選択すると取込列設定に自動反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>記法</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>例</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>セミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="28" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>設定を保存できない場合は次をご確認ください。</t>
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="24" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="6" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>確認場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>該当画面</t>
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
         <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
+          <t>① エクスポート種別</t>
         </is>
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="24" customHeight="1">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>移行について</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>設定／実績</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>② エクスポートデータ詳細選択</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>データ項目のカテゴリ</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>給与設定</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="18" customHeight="1">
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="28" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="28" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="24" customHeight="1">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>対象外の内容</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>取り込む内容の一覧を表示</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
         <is>
+          <t>読み込み</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>取込を実行</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>進捗を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・会社</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="24" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードが空</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードは必須です。全行にご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードが重複</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="28" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="24" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="16" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース（手動編集／CSVインポート）</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="16" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="28" customHeight="1">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B214" s="7" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="7" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="28" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="24" customHeight="1">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
           <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t>権限設定</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
         <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B222" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A149:C149"/>
+  <mergeCells count="67">
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A217:C217"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A163:C163"/>
-    <mergeCell ref="A158:C158"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A95:C95"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A175:C175"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A185:C185"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A184:C184"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A190:C190"/>
+    <mergeCell ref="A72:C72"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A127:C127"/>
     <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A191:C191"/>
     <mergeCell ref="A142:C142"/>
-    <mergeCell ref="A169:C169"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A103:C103"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A119:C119"/>
     <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A205:C205"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:C223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>店舗管理</t>
+          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
         </is>
       </c>
     </row>
@@ -809,67 +809,57 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>締めたあとに修正が必要になった</t>
+          <t>締めたあとに遡って給与改定が決まった</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>人件費実績 →「締め解除」→ 修正 → 再度「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>会社スコープ</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>サイドバーの構成</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>従業員管理メニューは2つのグループで構成しております。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>グループ</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>メニュー</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>従業員の設定を一覧で確認・登録・編集</t>
         </is>
       </c>
     </row>
@@ -881,12 +871,12 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+          <t>従業員の設定を一覧で確認・登録・編集</t>
         </is>
       </c>
     </row>
@@ -898,29 +888,29 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
+          <t>月別・日別の人件費を確認。月次の締めを実行</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
+          <t>全従業員の設定変更履歴を横断で確認</t>
         </is>
       </c>
     </row>
@@ -932,12 +922,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>項目を選択してCSVで出力</t>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
         </is>
       </c>
     </row>
@@ -949,12 +939,12 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データを確認</t>
+          <t>項目を選択してCSVで出力</t>
         </is>
       </c>
     </row>
@@ -966,60 +956,60 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>取り込んだ勤怠実績の元データを確認</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>画面の移動</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>移動元</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>移動先</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>名前をクリック／詳細アイコン</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1021,12 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>「従業員登録」</t>
+          <t>名前をクリック／詳細アイコン</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1038,12 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>「設定インポート」</t>
+          <t>「従業員登録」</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員登録</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1055,12 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>「設定・実績エクスポート」</t>
+          <t>「設定インポート」</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
@@ -1082,41 +1072,41 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>2段目「設定取込データへ」</t>
+          <t>「設定・実績エクスポート」</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>「保存」／「一覧へ戻る」</t>
+          <t>2段目「設定取込データへ」</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>「登録」</t>
+          <t>「保存」／「一覧へ戻る」</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -1128,17 +1118,17 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員登録</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>「実績データ取込」</t>
+          <t>「登録」</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>取込中の進捗表示 → 人件費実績に反映</t>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1140,12 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>「従業員設定」</t>
+          <t>「実績データ取込」</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
+          <t>取込中の進捗表示 → 人件費実績に反映</t>
         </is>
       </c>
     </row>
@@ -1167,63 +1157,63 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>「実績取込データへ」</t>
+          <t>「従業員設定」</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>「実績取込データへ」</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
           <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>名前をクリック</t>
+          <t>「人件費実績へ」</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>人件費実績</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」</t>
+          <t>名前をクリック</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
@@ -1235,143 +1225,147 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
+          <t>「列マッピングテンプレート管理」</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
           <t>「登録」</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>勤怠データとの突合に使用するコード</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>重複した登録は不可</t>
+          <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
+          <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>1店舗のみ設定可能。人件費の計上先</t>
+          <t>重複した登録は不可</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>複数設定可能</t>
+          <t>1店舗のみ設定可能。人件費の計上先</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr"/>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>複数設定可能</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>給与単位</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>月給／時給</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr"/>
@@ -1379,42 +1373,42 @@
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>単位給与額</t>
+          <t>給与単位</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>月給額または時給額</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
-        </is>
-      </c>
+          <t>月給／時給</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr"/>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>交通費単位</t>
+          <t>単位給与額</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>日額／月額</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr"/>
+          <t>月給額または時給額</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>単位交通費</t>
+          <t>交通費単位</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>交通費の金額</t>
+          <t>日額／月額</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr"/>
@@ -1422,12 +1416,12 @@
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>単位交通費</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
+          <t>交通費の金額</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr"/>
@@ -1435,155 +1429,151 @@
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
           <t>みなし残業時間</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>月あたりのみなし残業時間</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr"/>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>入力項目</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>勤怠データとの突合コード</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>必須。既存と重複する場合は登録不可</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
+          <t>勤怠データとの突合コード</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>必須。1店舗のみ</t>
+          <t>必須。既存と重複する場合は登録不可</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>必須。1店舗のみ</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
+          <t>応援に行く店舗</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>給与単位・単位給与額</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>月給／時給と金額</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
@@ -1595,55 +1585,59 @@
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>交通費単位・単位交通費</t>
+          <t>給与単位・単位給与額</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>日額／月額と金額</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr"/>
+          <t>月給／時給と金額</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>交通費単位・単位交通費</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>応援先ごとの交通費</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
-        </is>
-      </c>
+          <t>日額／月額と金額</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr"/>
+          <t>応援先ごとの交通費</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>所定労働時間</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
+          <t>月あたりの所定労働時間</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr"/>
@@ -1651,718 +1645,718 @@
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>この内容が有効となる日付</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>保存時の動作</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>未来日</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>設定変更履歴に「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>当日・過去日</t>
+          <t>未来日</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>「即時反映しました」と表示。その時点から反映</t>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>設定変更履歴に「適用中」で追加</t>
+          <t>設定変更履歴に「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
+          <t>当日・過去日</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>「即時反映しました」と表示。その時点から反映</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>設定変更履歴に「適用中」で追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
           <t>締め済み期間内</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>警告を表示。反映されない</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>締め済みの月は変更不可</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴は全14列で構成しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴は次の列で構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>適用日付と同じ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>設定を入力した日時</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>変更反映日時とは異なる</t>
+          <t>適用日付と同じ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>適用中／予約中／過去</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>変更の経路を記録</t>
         </is>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
           <t>その他の列</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>変更時点の値</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>算出方法</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>基礎時給</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>想定給与（概算給与）</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>実績データ取込後に反映</t>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>みなし労働時間差分</t>
+          <t>総労働時間</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+          <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>プラスが超過、マイナスが未達</t>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代</t>
+          <t>みなし労働時間差分</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>給与（実績給与）</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>交通費は含みません</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>交通費は含みません</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>所属店舗労働時間</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
           <t>総支給額</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>実績給与 ＋ 交通費</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr"/>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>※ 日別実績に概算モードはございません。</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>締めは月別実績タブにのみ表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>給与設定を過去日で変更</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>勤怠を再取込</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C123" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>締め後</t>
+          <t>締め前</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
+          <t>締め後</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
           <t>締め解除後</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="42" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="132" ht="42" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>対象の従業員の設定編集モーダルを開く</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>14項目（名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>更新保存</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>変更を保存し、人件費実績に戻る</t>
-        </is>
-      </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>数字が再計算されます</t>
+          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
+          <t>更新保存</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>変更を保存し、人件費実績に戻る</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>数字が再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
           <t>キャンセル</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>変更せずに閉じる</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr"/>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えた14列です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>絞り込み</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>変更ソース</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>変更の経路で絞り込み</t>
         </is>
       </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr"/>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>編集日時範囲</t>
+          <t>店舗・雇用区分</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>入力した日時の期間で絞り込み</t>
+          <t>対象者で絞り込み</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr"/>
@@ -2370,618 +2364,614 @@
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
+          <t>編集日時範囲</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
           <t>従業員名</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>氏名で検索</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr"/>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C146" s="7" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>データ種類</t>
+          <t>CSVテンプレート</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="inlineStr"/>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C148" s="7" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr"/>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
+          <t>保存済みの列の対応づけ</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>先頭に説明行があるCSVに対応</t>
+          <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>CSV列とラクミー項目の対応</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>記法</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
         <is>
           <t>例</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>セミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="154" ht="18" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>セミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>青山店;新宿店</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>店舗名:金額 をセミコロン区切り</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="3" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="7" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
           <t>マッピングテンプレートファイル</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B163" s="7" t="inlineStr">
         <is>
           <t>記入したCSVをアップロード</t>
         </is>
       </c>
-      <c r="C162" s="7" t="inlineStr">
+      <c r="C163" s="7" t="inlineStr">
         <is>
           <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="28" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
+    <row r="164" ht="28" customHeight="1">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C167" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>① エクスポート種別</t>
-        </is>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C167" s="7" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="7" t="inlineStr">
         <is>
+          <t>① エクスポート種別</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>設定／実績</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
           <t>② エクスポートデータ詳細選択</t>
         </is>
       </c>
-      <c r="B168" s="7" t="inlineStr">
+      <c r="B169" s="7" t="inlineStr">
         <is>
           <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C169" s="7" t="inlineStr">
         <is>
           <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="6" t="inlineStr">
         <is>
           <t>データ項目のカテゴリ</t>
         </is>
       </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="B170" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B170" s="7" t="inlineStr">
+      <c r="B171" s="7" t="inlineStr">
         <is>
           <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="28" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
       <c r="A172" s="7" t="inlineStr">
         <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B172" s="7" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="3" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B176" s="6" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C177" s="7" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
         <is>
+          <t>前回差分表示</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
           <t>読み込み</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>取込を実行</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>進捗を表示</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="6" t="inlineStr">
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="B180" s="6" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t>画面間の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C181" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="7" t="inlineStr">
         <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B183" s="7" t="inlineStr">
         <is>
           <t>月別データ／日別データ</t>
         </is>
       </c>
-      <c r="C182" s="7" t="inlineStr">
+      <c r="C183" s="7" t="inlineStr">
         <is>
           <t>「人件費実績へ」で人件費実績に戻ります</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="3" t="inlineStr">
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="24" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>権限による違い</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="6" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>オーナー・会社</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C187" s="6" t="inlineStr">
         <is>
           <t>店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B187" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C187" s="7" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="7" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr">
@@ -2998,438 +2988,456 @@
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
           <t>月次の締め・締め解除</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="3" t="inlineStr">
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="24" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
+    <row r="192" ht="24" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>エラーが表示されたときは</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="6" t="inlineStr">
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>エラーの内容</t>
         </is>
       </c>
-      <c r="B193" s="6" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B194" s="7" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="7" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B196" s="7" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
           <t>雇用区分が不正</t>
         </is>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B199" s="7" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="28" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
+    <row r="200" ht="28" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
         <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B200" s="7" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="2" t="inlineStr">
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>設定を保存できない場合は次をご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="A201" s="6" t="inlineStr">
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="6" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="B201" s="6" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B202" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
         <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
           <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="B204" s="7" t="inlineStr">
         <is>
           <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="24" customHeight="1">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="205" ht="24" customHeight="1">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t>お問い合わせ</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="6" t="inlineStr">
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="6" t="inlineStr">
         <is>
           <t>お知らせいただく内容</t>
         </is>
       </c>
-      <c r="B206" s="6" t="inlineStr">
+      <c r="B207" s="6" t="inlineStr">
         <is>
           <t>確認場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="18" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B207" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="7" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>対象の従業員コードと年月</t>
         </is>
       </c>
       <c r="B208" s="7" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
         <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="24" customHeight="1">
-      <c r="A210" s="4" t="inlineStr">
+    <row r="211" ht="24" customHeight="1">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t>移行について</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="2" t="inlineStr">
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="6" t="inlineStr">
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="28" customHeight="1">
-      <c r="A213" s="7" t="inlineStr">
+    <row r="214" ht="28" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>過去の月の人件費</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="A214" s="7" t="inlineStr">
-        <is>
-          <t>設定の入力</t>
-        </is>
-      </c>
-      <c r="B214" s="7" t="inlineStr">
-        <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
         <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B215" s="7" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="7" t="inlineStr">
+        <is>
           <t>変更履歴</t>
         </is>
       </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="28" customHeight="1">
-      <c r="A216" s="7" t="inlineStr">
+    <row r="217" ht="28" customHeight="1">
+      <c r="A217" s="7" t="inlineStr">
         <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B216" s="7" t="inlineStr">
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="24" customHeight="1">
-      <c r="A217" s="4" t="inlineStr">
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>本機能の対象外</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="18" customHeight="1">
-      <c r="A218" s="6" t="inlineStr">
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>対象外の内容</t>
         </is>
       </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="7" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B219" s="7" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="7" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="221" ht="18" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="7" t="inlineStr">
         <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B222" s="7" t="inlineStr">
+      <c r="B223" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="A183:C183"/>
+  <mergeCells count="68">
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A90:C90"/>
     <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A217:C217"/>
-    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A193:C193"/>
     <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A145:C145"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A192:C192"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A95:C95"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A129:C129"/>
     <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A204:C204"/>
     <mergeCell ref="A175:C175"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A71:C71"/>
     <mergeCell ref="A185:C185"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A91:C91"/>
     <mergeCell ref="A184:C184"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A96:C96"/>
     <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A165:C165"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A218:C218"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A127:C127"/>
     <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A173:C173"/>
     <mergeCell ref="A211:C211"/>
+    <mergeCell ref="A130:C130"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A176:C176"/>
+    <mergeCell ref="A186:C186"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A73:C73"/>
     <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A201:C201"/>
     <mergeCell ref="A191:C191"/>
-    <mergeCell ref="A142:C142"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A103:C103"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A87:C87"/>
     <mergeCell ref="A174:C174"/>
     <mergeCell ref="A205:C205"/>
   </mergeCells>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -39,15 +39,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000969DA"/>
-      <sz val="11.5"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000969DA"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -108,13 +108,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C223"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,2933 +513,3041 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>どなたが何にお使いいただけるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ご担当によってお使いいただく箇所が異なります。該当する行からお読みください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ご担当</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>この機能で分かること・できること</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>主にお使いいただく箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・経営</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>店舗別・全社の人件費が毎月同じ基準で分かります。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実態と合います</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>本部管理</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定の登録・更新、勤怠実績の取込、月次の締め、給与計算へ渡すCSVの出力を行います</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>全画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、店長のご担当者様がお使いいただける機能はございません</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>※ 店長が自店のみの人件費をご確認いただく機能は、今回のリリースでは対応しておりません。現時点で人件費実績を公開すると全社の金額が表示されるため、権限設定では非公開とすることを推奨しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>ご利用の流れ</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。操作はいずれも本部管理のご担当者様が行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>導入時（最初の1回）</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>店舗マスタを登録する</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>従業員管理の対象外です。先に登録をお願いいたします</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>従業員の設定をCSVで一括登録する</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>取り込んだ内容を確認する</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>不足分を1名ずつ登録する</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>従業員一覧 → 従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>毎月の運用</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>勤怠実績を取り込む</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績 →「実績データ取込」</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>月次の人件費を確認する</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績／日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>数字が合わない場合は元データを確認する</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ／従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>随時</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>月次の人件費を確認する</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績／日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>数字が合わない場合は元データを確認する</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ／従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>月を締めて数字を確定する</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「締め」</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>従業員を1名登録する</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>従業員一覧 → 従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>給与改定を予約する</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>従業員詳細（適用日付に未来日を入力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>変更の経緯を確認する</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>数字を見ながらその場で設定を直す</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績 →「従業員設定」</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>締めたあとに遡って給与改定が決まった</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="42" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>会社スコープ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理メニューは2つのグループで構成しております。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>変更の経緯を確認する</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>数字を見ながらその場で設定を直す</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「従業員設定」</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>締めたあとに遡って給与改定が決まった</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>会社スコープ（オーナー・本部管理のご担当者様）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理メニューは2つのグループで構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>グループ</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>メニュー</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>閲覧・管理</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>従業員の設定を一覧で確認・登録・編集</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>閲覧・管理</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>月別・日別の人件費を確認。月次の締めを実行</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>項目を選択してCSVで出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>画面の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>項目を選択してCSVで出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
           <t>移動元</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>移動先</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>名前をクリック／詳細アイコン</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>「従業員登録」</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>「設定インポート」</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>「設定・実績エクスポート」</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>2段目「設定取込データへ」</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>設定取込データ</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>「保存」／「一覧へ戻る」</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>「登録」</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>「実績データ取込」</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>取込中の進捗表示 → 人件費実績に反映</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>「従業員設定」</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>「実績取込データへ」</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>名前をクリック</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>「列マッピングテンプレート管理」</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>「登録」</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>名前をクリック</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>「列マッピングテンプレート管理」</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>重複した登録は不可</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>1店舗のみ設定可能。人件費の計上先</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>複数設定可能</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>給与単位</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>月給／時給</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>単位給与額</t>
         </is>
       </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>月給額または時給額</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>交通費単位</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>日額／月額</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr"/>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>単位交通費</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>交通費の金額</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>所定労働時間</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>みなし残業時間</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr"/>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
-        </is>
-      </c>
+      <c r="C75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
+          <t>単位交通費</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>交通費の金額</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
           <t>入力項目</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>勤怠データとの突合コード</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>必須。既存と重複する場合は登録不可</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>必須。1店舗のみ</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>給与単位・単位給与額</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>月給／時給と金額</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>交通費単位・単位交通費</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>日額／月額と金額</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>応援先ごとの交通費</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>所定労働時間</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>みなし残業時間</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr"/>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>この内容が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>必須。初期値は当日</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>この内容が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>必須。初期値は当日</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>保存時の動作</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>未来日</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>設定変更履歴に「予約中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>当日・過去日</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。その時点から反映</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>設定変更履歴に「適用中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>締め済み期間内</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>警告を表示。反映されない</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>締め済みの月は変更不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴は次の列で構成しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>適用日付と同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>編集日時</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>設定を入力した日時</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>変更反映日時とは異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>変更の経路を記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>その他の列</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>変更時点の値</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
+          <t>設定変更履歴は次の列で構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>適用日付と同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>適用日を迎えると予約中→適用中に変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>その他の列</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>変更時点の値</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>算出方法</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>基礎時給</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>想定給与（概算給与）</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>総労働時間</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
-      <c r="C110" s="7" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>みなし労働時間差分</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
-      <c r="C111" s="7" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>深夜残業代</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>給与（実績給与）</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>交通費は含みません</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="7" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>所属店舗労働時間</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>所属店舗で勤務した時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>日別実績の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>交通費</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>給与とは別の費目</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
-        <is>
-          <t>総支給額</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr"/>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>※ 日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績タブにのみ表示されます。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>給与設定を過去日で変更</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>勤怠を再取込</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>締め後</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>反映されません</t>
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>締め解除後</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>総支給額</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr"/>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+          <t>※ 日別実績に概算モードはございません。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+          <t>締めは月別実績タブにのみ表示されます。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="42" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員の設定編集モーダルを開く</t>
-        </is>
-      </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>締め前</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>更新保存</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>変更を保存し、人件費実績に戻る</t>
-        </is>
-      </c>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>数字が再計算されます</t>
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>締め後</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>キャンセル</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>変更せずに閉じる</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr"/>
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
+          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="28" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>変更の経路で絞り込み</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr"/>
+    <row r="140" ht="42" customHeight="1">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員の設定編集モーダルを開く</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>編集日時範囲</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>入力した日時の期間で絞り込み</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr"/>
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>更新保存</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>変更を保存し、人件費実績に戻る</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>数字が再計算されます</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>従業員名</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C142" s="7" t="inlineStr"/>
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>変更せずに閉じる</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr"/>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>変更の経路で絞り込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>店舗・雇用区分</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>対象者で絞り込み</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>編集日時範囲</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>従業員名</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>氏名で検索</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
           <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
         <is>
           <t>CSVテンプレート</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
         </is>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C155" s="6" t="inlineStr">
         <is>
           <t>画面右上からダウンロード。BOM付きCSV</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
         <is>
           <t>データ種類</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>King of Time／ジョブカン／新規作成</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr"/>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
+      <c r="C156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>保存済みの列の対応づけ</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
         <is>
           <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>CSV位置合わせ設定</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>ヘッダー行／データ開始行／開始列</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>例</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>セミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>青山店;新宿店</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>青山店:700;新宿店:900</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>取り込み列設定</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>CSV列とラクミー項目の対応</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>「全解除」で取込チェックを一括解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>記法</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>例</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C162" s="7" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>セミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C163" s="7" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="28" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C167" s="6" t="inlineStr">
+      <c r="C167" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="7" t="inlineStr">
-        <is>
-          <t>① エクスポート種別</t>
-        </is>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>② エクスポートデータ詳細選択</t>
-        </is>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
-        </is>
-      </c>
-      <c r="C169" s="7" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>編集・削除</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>データ項目のカテゴリ</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="28" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="22" customHeight="1">
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ元のデータを確認する画面です。</t>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>① エクスポート種別</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>設定／実績</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
+          <t>② エクスポートデータ詳細選択</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>データ項目のカテゴリ</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="28" customHeight="1">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ元のデータを確認する画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C185" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
         <is>
           <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>前回差分表示</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>前回の取込との差を表示</t>
-        </is>
-      </c>
-      <c r="C179" s="7" t="inlineStr">
-        <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>読み込み</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>取込を実行</t>
-        </is>
-      </c>
-      <c r="C180" s="7" t="inlineStr">
-        <is>
-          <t>進捗を表示</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C182" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C183" s="7" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="24" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
+          <t>前回差分表示</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>読み込み</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>取込を実行</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>進捗を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>オーナー・会社</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
         <is>
           <t>店長</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="7" t="inlineStr">
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="6" t="inlineStr">
         <is>
           <t>従業員一覧・設定の編集</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr">
+      <c r="B196" s="6" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C188" s="7" t="inlineStr">
+      <c r="C196" s="6" t="inlineStr">
         <is>
           <t>権限設定によります</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>人件費実績の閲覧</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B197" s="6" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
         <is>
           <t>月次の締め・締め解除</t>
         </is>
       </c>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="B198" s="6" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C190" s="7" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="3" t="inlineStr">
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="24" customHeight="1">
-      <c r="A192" s="4" t="inlineStr">
+    <row r="200" ht="28" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>※ 店長のご担当者様が自店の人件費をご確認いただく機能は、参照範囲を店舗単位に絞り込める段階での対応を予定しております。現時点で公開すると全社の金額が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t>エラーが表示されたときは</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="16" customHeight="1">
-      <c r="A193" s="2" t="inlineStr">
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="18" customHeight="1">
-      <c r="A194" s="6" t="inlineStr">
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="5" t="inlineStr">
         <is>
           <t>エラーの内容</t>
         </is>
       </c>
-      <c r="B194" s="6" t="inlineStr">
+      <c r="B203" s="5" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="6" t="inlineStr">
         <is>
           <t>従業員コードが空</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B204" s="6" t="inlineStr">
         <is>
           <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="6" t="inlineStr">
         <is>
           <t>従業員コードが重複</t>
         </is>
       </c>
-      <c r="B196" s="7" t="inlineStr">
+      <c r="B205" s="6" t="inlineStr">
         <is>
           <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="6" t="inlineStr">
         <is>
           <t>金額がマイナス・数字以外</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B206" s="6" t="inlineStr">
         <is>
           <t>単位給与額・交通費は0以上の数字でご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B198" s="7" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="7" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B200" s="7" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>設定を保存できない場合は次をご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B203" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="7" t="inlineStr">
-        <is>
-          <t>締め済み期間の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B204" s="7" t="inlineStr">
-        <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="24" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>確認場所</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B208" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="7" t="inlineStr">
-        <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B209" s="7" t="inlineStr">
-        <is>
-          <t>該当画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="18" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
-        </is>
-      </c>
-      <c r="B210" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="24" customHeight="1">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>移行について</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="28" customHeight="1">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="16" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="28" customHeight="1">
-      <c r="A214" s="7" t="inlineStr">
-        <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B214" s="7" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="18" customHeight="1">
-      <c r="A215" s="7" t="inlineStr">
-        <is>
-          <t>設定の入力</t>
-        </is>
-      </c>
-      <c r="B215" s="7" t="inlineStr">
-        <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="24" customHeight="1">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="7" t="inlineStr">
-        <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="28" customHeight="1">
-      <c r="A217" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B217" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>該当画面</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
+          <t>変更ソース（手動編集／CSVインポート）</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="24" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="28" customHeight="1">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="28" customHeight="1">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
           <t>対象外の内容</t>
         </is>
       </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="B228" s="5" t="inlineStr">
         <is>
           <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="18" customHeight="1">
-      <c r="A220" s="7" t="inlineStr">
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
-      <c r="B220" s="7" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="18" customHeight="1">
-      <c r="A221" s="7" t="inlineStr">
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="6" t="inlineStr">
         <is>
           <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
-      <c r="B221" s="7" t="inlineStr">
+      <c r="B230" s="6" t="inlineStr">
         <is>
           <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="18" customHeight="1">
-      <c r="A222" s="7" t="inlineStr">
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="6" t="inlineStr">
         <is>
           <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
-      <c r="B222" s="7" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>権限設定</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="18" customHeight="1">
-      <c r="A223" s="7" t="inlineStr">
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="6" t="inlineStr">
         <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B223" s="7" t="inlineStr">
+      <c r="B232" s="6" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="73">
     <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A221:C221"/>
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A214:C214"/>
     <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A105:C105"/>
     <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A192:C192"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A113:C113"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A175:C175"/>
-    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A210:C210"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A97:C97"/>
     <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A206:C206"/>
-    <mergeCell ref="A106:C106"/>
     <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A215:C215"/>
     <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A81:C81"/>
     <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A218:C218"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A199:C199"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A173:C173"/>
     <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A211:C211"/>
     <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A186:C186"/>
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A114:C114"/>
     <mergeCell ref="A166:C166"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A138:C138"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A227:C227"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A172:C172"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3468,220 +3576,220 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>待っている判断</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>月の途中で給与が変わる場合の計算例</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>判断1＝所定労働日割</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ヘルプ勤務の人件費の計上先</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>深夜残業代の金額</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>みなし残業を超えた/届かなかったときの扱い</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>人件費実績のモーダルから直したときの適用日付</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>翌月で差額を調整する条件</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>判断2（対象費目）</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>次段階可</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>「設定インポート」「設定取込データ」の画面名</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>判断3・4（名称の統一）</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>権限による違いの表</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
@@ -3695,119 +3803,119 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>確認すること</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>予約した変更の取り消し手順</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>実装されているか、手順は何か</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>従業員を削除したときの過去実績の扱い</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>実績が残るか、消えるか</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>締め解除の記録（誰が・いつ）</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>締め済み期間への適用時の警告表示</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>警告が出るか（モック未実装。T-D07）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>締め実行時の事前チェック</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>CSV取り込みのエラー表示</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
         </is>
@@ -3821,286 +3929,286 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>撮影する状態</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>対応する検証ID</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>サイドバー</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>「従業員管理」を展開した状態（7項目）</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>右上のテンプレートDLボタンが見える状態</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>CSVをドロップし、取り込み列設定が表示された状態</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>適用日付の入力欄と設定変更履歴が見える状態</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>フィルタ（変更ソース・期間）が見える状態</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>月別実績・実績モードで内訳の列が出た状態</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>締めの確認モーダル</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>①②が選択され、データ項目カードが見える状態</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>実績データ取込中の進捗モーダル</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>前回差分表示のモーダル（前回→新規の差）</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C232"/>
+  <dimension ref="A1:C252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,1220 +513,1178 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>目次</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>どなたが何にお使いいただけるか</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ご担当によってお使いいただく箇所が異なります。該当する行からお読みください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ご担当</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>この機能で分かること・できること</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>主にお使いいただく箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ご担当ごとの読みどころ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>オーナー・経営</t>
+          <t>ご利用の流れ</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>店舗別・全社の人件費が毎月同じ基準で分かります。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実態と合います</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>導入時・毎月の運用・随時の操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>本部管理</t>
+          <t>会社スコープ</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>従業員設定の登録・更新、勤怠実績の取込、月次の締め、給与計算へ渡すCSVの出力を行います</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>全画面</t>
+          <t>ここから各画面の説明です</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>店長</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>今回のリリースでは、店長のご担当者様がお使いいただける機能はございません</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>─</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>※ 店長が自店のみの人件費をご確認いただく機能は、今回のリリースでは対応しておりません。現時点で人件費実績を公開すると全社の金額が表示されるため、権限設定では非公開とすることを推奨しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>ご利用の流れ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。操作はいずれも本部管理のご担当者様が行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>導入時（最初の1回）</t>
+          <t>メニューの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>画面から画面への移動経路</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>表示項目・絞り込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>入力項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>設定の編集・適用日付・設定変更履歴・給与実績</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>各金額の算出方法・締め・実績データ取込・設定の編集</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>店舗マスタを登録する</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
+          <t>全従業員の変更履歴の絞り込み</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>従業員の設定をCSVで一括登録する</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
+          <t>CSVでの一括登録・CSVの記法</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ内容を確認する</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
+          <t>CSV列とラクミー項目の対応づけ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>不足分を1名ずつ登録する</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧 → 従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>毎月の運用</t>
+          <t>CSVでの出力手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ元データの確認・前回差分</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ご担当ごとに操作できる範囲</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>メッセージ別の対処</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>お問い合わせ</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>勤怠実績を取り込む</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「実績データ取込」</t>
+          <t>ご連絡の前にご確認いただきたい内容</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>移行について</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>月次の人件費を確認する</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績／日別実績）</t>
+          <t>既存でご利用中のお客様へ</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>他の機能でご利用いただく内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>※ 上から順にお読みいただくか、目次の項目名を目印に該当箇所までスクロールしてご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>どなたが何にお使いいただけるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ご担当によってお使いいただく箇所が異なります。該当する行の「主にお使いいただく箇所」までスクロールしてお読みください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>ご担当</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>この機能で分かること・できること</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>主にお使いいただく箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・経営</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>店舗別・全社の人件費が毎月同じ基準で分かります。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実態と合います</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>本部管理</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定の登録・更新、勤怠実績の取込、月次の締め、給与計算へ渡すCSVの出力を行います</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ご利用の流れ（以降すべて）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。操作はいずれも本部管理のご担当者様が行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>導入時（最初の1回）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>店舗マスタを登録する</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>従業員の設定をCSVで一括登録する</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>数字が合わない場合は元データを確認する</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ／従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ内容を確認する</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>不足分を1名ずつ登録する</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧 → 従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>毎月の運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>従業員を1名登録する</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧 → 従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>給与改定を予約する</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細（適用日付に未来日を入力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>変更の経緯を確認する</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>数字を見ながらその場で設定を直す</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「従業員設定」</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>締めたあとに遡って給与改定が決まった</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>会社スコープ（オーナー・本部管理のご担当者様）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理メニューは2つのグループで構成しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>グループ</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>メニュー</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>従業員の設定を一覧で確認・登録・編集</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認。月次の締めを実行</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>閲覧・管理</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>勤怠実績を取り込む</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
+          <t>人件費実績 →「実績データ取込」</t>
         </is>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>月次の人件費を確認する</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
+          <t>人件費実績（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>数字が合わない場合は元データを確認する</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>項目を選択してCSVで出力</t>
+          <t>実績取込データ／従業員設定履歴</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データを確認</t>
+          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>画面の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>随時</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>移動元</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>移動先</t>
+          <t>画面</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>従業員を1名登録する</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>名前をクリック／詳細アイコン</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
+          <t>従業員一覧 → 従業員登録</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>給与改定を予約する</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>「従業員登録」</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
+          <t>従業員詳細（適用日付に未来日を入力）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>変更の経緯を確認する</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>「設定インポート」</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
+          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>数字を見ながらその場で設定を直す</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>「設定・実績エクスポート」</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
+          <t>人件費実績 →「従業員設定」</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>締めたあとに遡って給与改定が決まった</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>2段目「設定取込データへ」</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>「保存」／「一覧へ戻る」</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>「登録」</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>「実績データ取込」</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>取込中の進捗表示 → 人件費実績に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>「従業員設定」</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
+          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>会社スコープ（オーナー・本部管理のご担当者様）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理メニューは2つのグループで構成しております。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>「実績取込データへ」</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>メニュー</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>「人件費実績へ」</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員の設定を一覧で確認・登録・編集</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>名前をクリック</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>月別・日別の人件費を確認。月次の締めを実行</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>全従業員の設定変更履歴を横断で確認</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>「登録」</t>
-        </is>
-      </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>クリックで従業員詳細へ遷移</t>
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>項目を選択してCSVで出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>勤怠データとの突合に使用するコード</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>重複した登録は不可</t>
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>移動元</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>移動先</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
+          <t>名前をクリック／詳細アイコン</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>1店舗のみ設定可能。人件費の計上先</t>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>「従業員登録」</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>複数設定可能</t>
+          <t>従業員登録</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr"/>
+          <t>「設定インポート」</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>給与単位</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>月給／時給</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr"/>
+          <t>「設定・実績エクスポート」</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>単位給与額</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>月給額または時給額</t>
+          <t>2段目「設定取込データへ」</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>交通費単位</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>日額／月額</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr"/>
+          <t>「保存」／「一覧へ戻る」</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>単位交通費</t>
+          <t>従業員登録</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>交通費の金額</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr"/>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr"/>
+          <t>「実績データ取込」</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>取込中の進捗表示 → 人件費実績に反映</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr"/>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
+          <t>「従業員設定」</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>「実績取込データへ」</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>名前をクリック</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>「列マッピングテンプレート管理」</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>入力項目</t>
-        </is>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>勤怠データとの突合コード</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>必須。既存と重複する場合は登録不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>所属店舗</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>主に勤務する店舗</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>必須。1店舗のみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>応援に行く店舗</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>給与単位・単位給与額</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>月給／時給と金額</t>
+          <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>重複した登録は不可</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>交通費単位・単位交通費</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>日額／月額と金額</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr"/>
+          <t>主に勤務する店舗</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>1店舗のみ設定可能。人件費の計上先</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>応援先ごとの交通費</t>
+          <t>応援に行く店舗</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
+          <t>複数設定可能</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
@@ -1734,12 +1692,12 @@
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>給与単位</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
+          <t>月給／時給</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr"/>
@@ -1747,1806 +1705,2079 @@
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>適用日付</t>
+          <t>単位給与額</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>この内容が有効となる日付</t>
+          <t>月給額または時給額</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>必須。初期値は当日</t>
+          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>交通費単位</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>日額／月額</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>単位交通費</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>交通費の金額</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>入力項目</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>未来日</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>設定変更履歴に「予約中」で追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>当日・過去日</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>「即時反映しました」と表示。その時点から反映</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>設定変更履歴に「適用中」で追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>締め済み期間内</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>警告を表示。反映されない</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>締め済みの月は変更不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴は次の列で構成しております。</t>
-        </is>
-      </c>
-    </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B104" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>従業員の氏名</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>勤怠データとの突合コード</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>適用日付と同じ</t>
+          <t>必須。既存と重複する場合は登録不可</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>設定を入力した日時</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>変更反映日時とは異なる</t>
+          <t>必須。1店舗のみ</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>応援に行く店舗</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>変更の経路を記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28" customHeight="1">
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>その他の列</t>
+          <t>給与単位・単位給与額</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+          <t>月給／時給と金額</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>変更時点の値</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>交通費単位・単位交通費</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>日額／月額と金額</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>応援先ごとの交通費</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>この内容が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>基礎時給</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>想定給与（概算給与）</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>勤怠実績の実働時間の合計</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>みなし労働時間差分</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>深夜残業代</t>
+          <t>未来日</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+          <t>設定変更履歴に「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>給与（実績給与）</t>
+          <t>当日・過去日</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+          <t>「即時反映しました」と表示。その時点から反映</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>交通費は含みません</t>
+          <t>設定変更履歴に「適用中」で追加</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>締め済み期間内</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>警告を表示。反映されない</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>日別実績の合計</t>
+          <t>締め済みの月は変更不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴は次の列で構成しております。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
+          <t>適用日付と同じ</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>総支給額</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr"/>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>適用日を迎えると予約中→適用中に変化</t>
         </is>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>※ 日別実績に概算モードはございません。</t>
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>その他の列</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>変更時点の値</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>締めは月別実績タブにのみ表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>締め後</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>締め解除後</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
+          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>基礎時給</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>単位給与額 ÷ 所定労働時間</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>想定給与（概算給与）</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績の実働時間の合計</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="42" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>みなし労働時間差分</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>プラスが超過、マイナスが未達</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>対象の従業員の設定編集モーダルを開く</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>更新保存</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>変更を保存し、人件費実績に戻る</t>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>数字が再計算されます</t>
+          <t>交通費は含みません</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>所属店舗労働時間</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>変更せずに閉じる</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr"/>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>日別実績の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>総支給額</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>※ 日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績タブにのみ表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>締め前</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>締め後</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C159" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="28" customHeight="1">
-      <c r="A147" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路で絞り込み</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr"/>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>編集日時範囲</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>入力した日時の期間で絞り込み</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr"/>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>従業員名</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr"/>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
-        <is>
-          <t>データ種類</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr"/>
-    </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>CSV位置合わせ設定</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
+    <row r="160" ht="42" customHeight="1">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員の設定編集モーダルを開く</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>例</t>
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>更新保存</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>変更を保存し、人件費実績に戻る</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>数字が再計算されます</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>セミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>青山店;新宿店</t>
-        </is>
-      </c>
+          <t>変更せずに閉じる</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr"/>
     </row>
     <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>青山店:700;新宿店:900</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C167" s="5" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>変更の経路で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>店舗・雇用区分</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
-        </is>
-      </c>
+          <t>対象者で絞り込み</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr"/>
     </row>
     <row r="169" ht="18" customHeight="1">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>編集日時範囲</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr"/>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>従業員名</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
+          <t>氏名で検索</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr"/>
     </row>
     <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="28" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="16" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>CSVテンプレート</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>① エクスポート種別</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr"/>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>② エクスポートデータ詳細選択</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
+          <t>保存済みの列の対応づけ</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+          <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>データ項目のカテゴリ</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>取り込み列設定</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="28" customHeight="1">
-      <c r="A180" s="6" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="28" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>CSVの記法は次のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>記法</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>例</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ／実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ元のデータを確認する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>セミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>青山店;新宿店</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B185" s="5" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C185" s="5" t="inlineStr">
+      <c r="C187" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="6" t="inlineStr">
-        <is>
-          <t>前回差分表示</t>
-        </is>
-      </c>
-      <c r="B187" s="6" t="inlineStr">
-        <is>
-          <t>前回の取込との差を表示</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>読み込み</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>取込を実行</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>進捗を表示</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>編集・削除</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>マッピングテンプレートファイル</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
+          <t>記入したCSVをアップロード</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="18" customHeight="1">
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="28" customHeight="1">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="24" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>オーナー・本部管理</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>店長</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>① エクスポート種別</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>設定／実績</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>② エクスポートデータ詳細選択</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>不可</t>
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>データ項目のカテゴリ</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>※ 店長のご担当者様が自店の人件費をご確認いただく機能は、参照範囲を店舗単位に絞り込める段階での対応を予定しております。現時点で公開すると全社の金額が表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="24" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>エラーが表示されたときは</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードが重複</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>取り込む内容の一覧を表示</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="28" customHeight="1">
-      <c r="A209" s="6" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>設定を保存できない場合は次をご確認ください。</t>
+          <t>取込を実行</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>進捗を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B211" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B212" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>締め済み期間の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
-        <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="24" customHeight="1">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>店長</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="5" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B216" s="5" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>人件費実績の閲覧</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧／人件費実績</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>月次の締め・締め解除</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="24" customHeight="1">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>移行について</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="16" customHeight="1">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="18" customHeight="1">
-      <c r="A222" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B222" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="28" customHeight="1">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="28" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="24" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="225" ht="18" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="28" customHeight="1">
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>店舗別の人件費</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="24" customHeight="1">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="228" ht="18" customHeight="1">
-      <c r="A228" s="5" t="inlineStr">
-        <is>
-          <t>対象外の内容</t>
-        </is>
-      </c>
-      <c r="B228" s="5" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="18" customHeight="1">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="28" customHeight="1">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="18" customHeight="1">
-      <c r="A230" s="6" t="inlineStr">
-        <is>
-          <t>出退勤の打刻・シフトの作成</t>
-        </is>
-      </c>
-      <c r="B230" s="6" t="inlineStr">
-        <is>
-          <t>ラクミータイムレコード</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="16" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>ログインアカウントの発行・権限の設定</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>権限設定</t>
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="24" customHeight="1">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="16" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース（手動編集／CSVインポート）</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="16" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="28" customHeight="1">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B243" s="6" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="28" customHeight="1">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="24" customHeight="1">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B252" s="6" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A183:C183"/>
+  <mergeCells count="74">
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A84:C84"/>
     <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A163:C163"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A151:C151"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A204:C204"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A203:C203"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A32:C32"/>
     <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A215:C215"/>
+    <mergeCell ref="A234:C234"/>
+    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A100:C100"/>
     <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A200:C200"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A180:C180"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A240:C240"/>
+    <mergeCell ref="A147:C147"/>
     <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A199:C199"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A220:C220"/>
-    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="A67:C67"/>
     <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A186:C186"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A201:C201"/>
-    <mergeCell ref="A182:C182"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A227:C227"/>
-    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A241:C241"/>
+    <mergeCell ref="A123:C123"/>
     <mergeCell ref="A172:C172"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -39,15 +39,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000969DA"/>
+      <sz val="11.5"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000969DA"/>
-      <sz val="11.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -108,13 +108,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -513,3272 +513,3389 @@
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>この機能で分かること</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店舗別・全社の人件費が、毎月同じ基準で分かります。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実際の働き方と合います。数字は月次で締めて確定でき、確定後は変わりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>※ 数字をご覧いただくだけの場合は、[人件費実績]の項目までスクロールしてください。それ以外の項目は、設定と運用を行うご担当者様向けの内容です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
           <t>目次</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>どなたが何にお使いいただけるか</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>ご担当ごとの読みどころ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>ご利用の流れ</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>導入時・毎月の運用・随時の操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>会社スコープ</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>ここから各画面の説明です</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>メニューの構成</t>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>このページは上から順にお読みいただけます。お探しの内容が決まっている場合は、下の表の項目名を目印に、該当箇所までスクロールしてご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>やりたいことから探す</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>やりたいこと</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>お読みいただく項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>導入時に従業員をまとめて登録する</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>取り込むCSVの列名がラクミーと違う</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>従業員を1名ずつ登録する</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>ご利用の流れ（毎月の運用）／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>人件費の計算方法を確認する</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わない原因を調べる</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴／設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まった</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>ご利用の流れ（随時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>給与計算・社労士へデータを渡す</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>CSVが取り込めない・エラーが出た</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>どなたが何を操作できるか知りたい</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中で、移行の影響を知りたい</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>画面から探す</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>導入時・毎月の運用・随時の操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>メニューの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
           <t>画面の移動</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>画面から画面への移動経路</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>表示項目・絞り込み</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>入力項目</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>設定の編集・適用日付・設定変更履歴・給与実績</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>各金額の算出方法・締め・実績データ取込・設定の編集</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>全従業員の変更履歴の絞り込み</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>CSVでの一括登録・CSVの記法</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>CSV列とラクミー項目の対応づけ</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>CSVでの出力手順</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>取り込んだ元データの確認・前回差分</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>権限による違い</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>ご担当ごとに操作できる範囲</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>エラーが表示されたときは</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>メッセージ別の対処</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>お問い合わせ</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>ご連絡の前にご確認いただきたい内容</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>移行について</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>既存でご利用中のお客様へ</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>他の機能でご利用いただく内容</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>※ 上から順にお読みいただくか、目次の項目名を目印に該当箇所までスクロールしてご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>どなたが何にお使いいただけるか</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ご担当によってお使いいただく箇所が異なります。該当する行の「主にお使いいただく箇所」までスクロールしてお読みください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>ご担当</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>この機能で分かること・できること</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>主にお使いいただく箇所</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>オーナー・経営</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>店舗別・全社の人件費が毎月同じ基準で分かります。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実態と合います</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>本部管理</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定の登録・更新、勤怠実績の取込、月次の締め、給与計算へ渡すCSVの出力を行います</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ご利用の流れ（以降すべて）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>ご利用の流れ</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。操作はいずれも本部管理のご担当者様が行います。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ここから先は、従業員設定の登録・勤怠実績の取込・月次の締めを行うご担当者様向けの内容です。導入時にお使いいただく機能と、毎月の運用でお使いいただく機能が異なります。初めてご利用いただく場合は、導入時の流れから順にお進みください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>導入時（最初の1回）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>店舗マスタを登録する</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>従業員の設定をCSVで一括登録する</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ内容を確認する</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>不足分を1名ずつ登録する</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧 → 従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>毎月の運用</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>勤怠実績を取り込む</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「実績データ取込」</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>月次の人件費を確認する</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績／日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>数字が合わない場合は元データを確認する</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ／従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>画面</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>店舗マスタを登録する</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定をCSVで一括登録する</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ内容を確認する</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>従業員を1名登録する</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>不足分を1名ずつ登録する</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>従業員一覧 → 従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>給与改定を予約する</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細（適用日付に未来日を入力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>変更の経緯を確認する</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は、列マッピングテンプレートで対応づけを保存いただくと、2回目以降は選択するだけで取り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>毎月の運用</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>数字を見ながらその場で設定を直す</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>人件費実績 →「従業員設定」</t>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>締めたあとに遡って給与改定が決まった</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="42" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>会社スコープ（オーナー・本部管理のご担当者様）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>月次の人件費を確認する</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績／日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わない場合は元データを確認する</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ／従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理メニューは2つのグループで構成しております。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>月を締めて数字を確定する</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績 →「締め」</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>グループ</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>メニュー</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>従業員の設定を一覧で確認・登録・編集</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>閲覧・管理</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+          <t>画面</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>従業員を1名登録する</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧 → 従業員登録</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を予約する</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細（適用日付に未来日を入力）</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>項目を選択してCSVで出力</t>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>変更の経緯を確認する</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴 → 名前 → 従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データを確認</t>
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>数字を見ながらその場で設定を直す</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績 →「従業員設定」</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>データ連携</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>画面の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>締めたあとに遡って給与改定が決まった</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細（適用日付を締め済み期間の翌日以降に指定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。適用日付を締め済み期間の翌日以降に直して保存し、差額が必要な場合は翌月で調整いただく形を標準としております。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>会社スコープ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>移動元</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>移動先</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>名前をクリック／詳細アイコン</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理メニューは2つのグループで構成しております。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>メニュー</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>「従業員登録」</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>「設定インポート」</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を一覧で確認・登録・編集</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>「設定・実績エクスポート」</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>2段目「設定取込データへ」</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>項目を選択してCSVで出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>設定取込データ</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>「保存」／「一覧へ戻る」</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>「登録」</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>「実績データ取込」</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>取込中の進捗表示 → 人件費実績に反映</t>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データを確認</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>「従業員設定」</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>「実績取込データへ」</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
+          <t>移動元</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>移動先</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>名前をクリック／詳細アイコン</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>「従業員登録」</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>「設定インポート」</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>「設定・実績エクスポート」</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>2段目「設定取込データへ」</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>「保存」／「一覧へ戻る」</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>「実績データ取込」</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>取込中の進捗表示 → 人件費実績に反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>「従業員設定」</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>「実績取込データへ」</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>名前をクリック</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>「列マッピングテンプレート管理」</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>「登録」</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>重複した登録は不可</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>1店舗のみ設定可能。人件費の計上先</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>複数設定可能</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr"/>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>給与単位</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>月給／時給</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr"/>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>単位給与額</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>月給額または時給額</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>交通費単位</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>日額／月額</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr"/>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>単位交通費</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>交通費の金額</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>所定労働時間</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>月あたりの所定労働時間</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>みなし残業時間</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>月あたりのみなし残業時間</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr"/>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>入力項目</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C116" s="7" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>勤怠データとの突合コード</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr">
         <is>
           <t>必須。既存と重複する場合は登録不可</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B118" s="7" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>必須。1店舗のみ</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B119" s="7" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>給与単位・単位給与額</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>月給／時給と金額</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>交通費単位・単位交通費</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>日額／月額と金額</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr"/>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>応援先ごとの交通費</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>所定労働時間</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>月あたりの所定労働時間</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>みなし残業時間</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>月あたりのみなし残業時間</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>この内容が有効となる日付</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>保存時の動作</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>未来日</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>設定変更履歴に「予約中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
         <is>
           <t>当日・過去日</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。その時点から反映</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>設定変更履歴に「適用中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>締め済み期間内</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>警告を表示。反映されない</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>締め済みの月は変更不可</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴は次の列で構成しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>適用日付と同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>編集日時</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>設定を入力した日時</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時とは異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="28" customHeight="1">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路を記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>その他の列</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>変更時点の値</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>適用日付と同じ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>適用日を迎えると予約中→適用中に変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>その他の列</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>変更時点の値</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
           <t>基礎時給</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B148" s="7" t="inlineStr">
         <is>
           <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C148" s="7" t="inlineStr">
         <is>
           <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t>想定給与（概算給与）</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>総労働時間</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B150" s="7" t="inlineStr">
         <is>
           <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="C150" s="7" t="inlineStr">
         <is>
           <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
         <is>
           <t>みなし労働時間差分</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="6" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>深夜残業代</t>
         </is>
       </c>
-      <c r="B140" s="6" t="inlineStr">
+      <c r="B152" s="7" t="inlineStr">
         <is>
           <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
+      <c r="C152" s="7" t="inlineStr">
         <is>
           <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>給与（実績給与）</t>
         </is>
       </c>
-      <c r="B141" s="6" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C153" s="7" t="inlineStr">
         <is>
           <t>交通費は含みません</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>所属店舗労働時間</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C154" s="7" t="inlineStr">
         <is>
           <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>ヘルプ時間</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>日別実績の合計</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>ヘルプ人件費</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B156" s="7" t="inlineStr">
         <is>
           <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C156" s="7" t="inlineStr">
         <is>
           <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>交通費</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B157" s="7" t="inlineStr">
         <is>
           <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C157" s="7" t="inlineStr">
         <is>
           <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="7" t="inlineStr">
         <is>
           <t>総支給額</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B158" s="7" t="inlineStr">
         <is>
           <t>実績給与 ＋ 交通費</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr"/>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="C158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="3" t="inlineStr">
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>※ 日別実績に概算モードはございません。</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>締めは月別実績タブにのみ表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>給与設定を過去日で変更</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C163" s="6" t="inlineStr">
         <is>
           <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>締め前</t>
         </is>
       </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C164" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="7" t="inlineStr">
         <is>
           <t>締め後</t>
         </is>
       </c>
-      <c r="B153" s="6" t="inlineStr">
+      <c r="B165" s="7" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C165" s="7" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="6" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
         <is>
           <t>締め解除後</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
+      <c r="B166" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C154" s="6" t="inlineStr">
+      <c r="C166" s="7" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="3" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="42" customHeight="1">
-      <c r="A160" s="6" t="inlineStr">
+    <row r="172" ht="42" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="B172" s="7" t="inlineStr">
         <is>
           <t>対象の従業員の設定編集モーダルを開く</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
+      <c r="C172" s="7" t="inlineStr">
         <is>
           <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>更新保存</t>
         </is>
       </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>変更を保存し、人件費実績に戻る</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
+      <c r="C173" s="7" t="inlineStr">
         <is>
           <t>数字が再計算されます</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>キャンセル</t>
         </is>
       </c>
-      <c r="B162" s="6" t="inlineStr">
+      <c r="B174" s="7" t="inlineStr">
         <is>
           <t>変更せずに閉じる</t>
         </is>
       </c>
-      <c r="C162" s="6" t="inlineStr"/>
-    </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="C174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="28" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路で絞り込み</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr"/>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>編集日時範囲</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>入力した日時の期間で絞り込み</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr"/>
-    </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>従業員名</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr"/>
-    </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>データ種類</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr"/>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
         </is>
       </c>
     </row>
     <row r="178" ht="18" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="28" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>変更の経路で絞り込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>店舗・雇用区分</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>対象者で絞り込み</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>編集日時範囲</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>入力した日時の期間で絞り込み</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>従業員名</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>氏名で検索</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>CSVテンプレート</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>データ種類</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>保存済みの列の対応づけ</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>選択すると取込列設定に自動反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
           <t>CSV位置合わせ設定</t>
         </is>
       </c>
-      <c r="B178" s="6" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>ヘッダー行／データ開始行／開始列</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>先頭に説明行があるCSVに対応</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="6" t="inlineStr">
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>CSV列とラクミー項目の対応</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C191" s="7" t="inlineStr">
         <is>
           <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="5" t="inlineStr">
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="B193" s="6" t="inlineStr">
         <is>
           <t>記法</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
+      <c r="C193" s="6" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="6" t="inlineStr">
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>セミコロン区切り</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="C194" s="7" t="inlineStr">
         <is>
           <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="6" t="inlineStr">
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="B195" s="7" t="inlineStr">
         <is>
           <t>店舗名:金額 をセミコロン区切り</t>
         </is>
       </c>
-      <c r="C183" s="6" t="inlineStr">
+      <c r="C195" s="7" t="inlineStr">
         <is>
           <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="5" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="18" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B195" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C195" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="6" t="inlineStr">
-        <is>
-          <t>① エクスポート種別</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>② エクスポートデータ詳細選択</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>データ項目のカテゴリ</t>
-        </is>
-      </c>
-      <c r="B198" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
         </is>
       </c>
     </row>
     <row r="199" ht="18" customHeight="1">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="6" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B200" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>編集・削除</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="22" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ元のデータを確認する画面です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="18" customHeight="1">
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="28" customHeight="1">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="22" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="6" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B206" s="6" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="6" t="inlineStr">
-        <is>
-          <t>読み込み</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>取込を実行</t>
-        </is>
-      </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>進捗を表示</t>
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>① エクスポート種別</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>設定／実績</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B209" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C209" s="5" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>② エクスポートデータ詳細選択</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>データ項目のカテゴリ</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+          <t>項目</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="18" customHeight="1">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="28" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="28" customHeight="1">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="22" customHeight="1">
       <c r="A215" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C215" s="5" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="16" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C218" s="6" t="inlineStr">
-        <is>
-          <t>不可</t>
+      <c r="A218" s="7" t="inlineStr">
+        <is>
+          <t>プレビュー</t>
+        </is>
+      </c>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t>取り込む内容の一覧を表示</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="28" customHeight="1">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="24" customHeight="1">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>エラーが表示されたときは</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="16" customHeight="1">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
+      <c r="A219" s="7" t="inlineStr">
+        <is>
+          <t>前回差分表示</t>
+        </is>
+      </c>
+      <c r="B219" s="7" t="inlineStr">
+        <is>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C219" s="7" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t>読み込み</t>
+        </is>
+      </c>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t>取込を実行</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr">
+        <is>
+          <t>進捗を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B222" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C222" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B223" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B223" s="7" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C223" s="7" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
-      <c r="A224" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B224" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="18" customHeight="1">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードが重複</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
-        <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="18" customHeight="1">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>金額がマイナス・数字以外</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="16" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B228" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C229" s="7" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="7" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="28" customHeight="1">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="24" customHeight="1">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="16" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードが空</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードは必須です。全行にご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="A237" s="7" t="inlineStr">
+        <is>
+          <t>従業員コードが重複</t>
+        </is>
+      </c>
+      <c r="B237" s="7" t="inlineStr">
+        <is>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B238" s="7" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="A239" s="7" t="inlineStr">
+        <is>
           <t>店舗が見つからない</t>
         </is>
       </c>
-      <c r="B227" s="6" t="inlineStr">
+      <c r="B239" s="7" t="inlineStr">
         <is>
           <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="18" customHeight="1">
-      <c r="A228" s="6" t="inlineStr">
+    <row r="240" ht="18" customHeight="1">
+      <c r="A240" s="7" t="inlineStr">
         <is>
           <t>雇用区分が不正</t>
         </is>
       </c>
-      <c r="B228" s="6" t="inlineStr">
+      <c r="B240" s="7" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="28" customHeight="1">
-      <c r="A229" s="6" t="inlineStr">
+    <row r="241" ht="28" customHeight="1">
+      <c r="A241" s="7" t="inlineStr">
         <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B229" s="6" t="inlineStr">
+      <c r="B241" s="7" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="16" customHeight="1">
-      <c r="A230" s="2" t="inlineStr">
+    <row r="242" ht="16" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>設定を保存できない場合は次をご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="5" t="inlineStr">
+    <row r="243" ht="18" customHeight="1">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="18" customHeight="1">
-      <c r="A232" s="6" t="inlineStr">
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B244" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="18" customHeight="1">
-      <c r="A233" s="6" t="inlineStr">
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="7" t="inlineStr">
         <is>
           <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B245" s="7" t="inlineStr">
         <is>
           <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="4" t="inlineStr">
+    <row r="246" ht="24" customHeight="1">
+      <c r="A246" s="4" t="inlineStr">
         <is>
           <t>お問い合わせ</t>
         </is>
       </c>
     </row>
-    <row r="235" ht="16" customHeight="1">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="247" ht="16" customHeight="1">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="18" customHeight="1">
-      <c r="A236" s="5" t="inlineStr">
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="6" t="inlineStr">
         <is>
           <t>お知らせいただく内容</t>
         </is>
       </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="B248" s="6" t="inlineStr">
         <is>
           <t>確認場所</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="18" customHeight="1">
-      <c r="A237" s="6" t="inlineStr">
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="7" t="inlineStr">
         <is>
           <t>対象の従業員コードと年月</t>
         </is>
       </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="B249" s="7" t="inlineStr">
         <is>
           <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="18" customHeight="1">
-      <c r="A238" s="6" t="inlineStr">
+    <row r="250" ht="18" customHeight="1">
+      <c r="A250" s="7" t="inlineStr">
         <is>
           <t>画面に表示されたメッセージ</t>
         </is>
       </c>
-      <c r="B238" s="6" t="inlineStr">
+      <c r="B250" s="7" t="inlineStr">
         <is>
           <t>該当画面</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="18" customHeight="1">
-      <c r="A239" s="6" t="inlineStr">
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="7" t="inlineStr">
         <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="24" customHeight="1">
-      <c r="A240" s="4" t="inlineStr">
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
         <is>
           <t>移行について</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="16" customHeight="1">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="253" ht="16" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
         <is>
           <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="18" customHeight="1">
-      <c r="A242" s="5" t="inlineStr">
+    <row r="254" ht="18" customHeight="1">
+      <c r="A254" s="6" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B242" s="5" t="inlineStr">
+      <c r="B254" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="28" customHeight="1">
-      <c r="A243" s="6" t="inlineStr">
+    <row r="255" ht="28" customHeight="1">
+      <c r="A255" s="7" t="inlineStr">
         <is>
           <t>過去の月の人件費</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B255" s="7" t="inlineStr">
         <is>
           <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="18" customHeight="1">
-      <c r="A244" s="6" t="inlineStr">
+    <row r="256" ht="18" customHeight="1">
+      <c r="A256" s="7" t="inlineStr">
         <is>
           <t>設定の入力</t>
         </is>
       </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="B256" s="7" t="inlineStr">
         <is>
           <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="18" customHeight="1">
-      <c r="A245" s="6" t="inlineStr">
+    <row r="257" ht="18" customHeight="1">
+      <c r="A257" s="7" t="inlineStr">
         <is>
           <t>変更履歴</t>
         </is>
       </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="B257" s="7" t="inlineStr">
         <is>
           <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="6" t="inlineStr">
+    <row r="258" ht="28" customHeight="1">
+      <c r="A258" s="7" t="inlineStr">
         <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="B258" s="7" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="247" ht="24" customHeight="1">
-      <c r="A247" s="4" t="inlineStr">
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="4" t="inlineStr">
         <is>
           <t>本機能の対象外</t>
         </is>
       </c>
     </row>
-    <row r="248" ht="18" customHeight="1">
-      <c r="A248" s="5" t="inlineStr">
+    <row r="260" ht="18" customHeight="1">
+      <c r="A260" s="6" t="inlineStr">
         <is>
           <t>対象外の内容</t>
         </is>
       </c>
-      <c r="B248" s="5" t="inlineStr">
+      <c r="B260" s="6" t="inlineStr">
         <is>
           <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
-    <row r="249" ht="18" customHeight="1">
-      <c r="A249" s="6" t="inlineStr">
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="7" t="inlineStr">
         <is>
           <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="B261" s="7" t="inlineStr">
         <is>
           <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
-    <row r="250" ht="18" customHeight="1">
-      <c r="A250" s="6" t="inlineStr">
+    <row r="262" ht="18" customHeight="1">
+      <c r="A262" s="7" t="inlineStr">
         <is>
           <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="B262" s="7" t="inlineStr">
         <is>
           <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="18" customHeight="1">
-      <c r="A251" s="6" t="inlineStr">
+    <row r="263" ht="18" customHeight="1">
+      <c r="A263" s="7" t="inlineStr">
         <is>
           <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B263" s="7" t="inlineStr">
         <is>
           <t>権限設定</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="18" customHeight="1">
-      <c r="A252" s="6" t="inlineStr">
+    <row r="264" ht="18" customHeight="1">
+      <c r="A264" s="7" t="inlineStr">
         <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A164:C164"/>
-    <mergeCell ref="A149:C149"/>
+  <mergeCells count="77">
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A233:C233"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A247:C247"/>
+    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A234:C234"/>
+    <mergeCell ref="A184:C184"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A198:C198"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A224:C224"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A226:C226"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A197:C197"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A252:C252"/>
     <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A163:C163"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A86:C86"/>
     <mergeCell ref="A204:C204"/>
-    <mergeCell ref="A235:C235"/>
-    <mergeCell ref="A213:C213"/>
-    <mergeCell ref="A247:C247"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A185:C185"/>
-    <mergeCell ref="A203:C203"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A234:C234"/>
-    <mergeCell ref="A219:C219"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A171:C171"/>
-    <mergeCell ref="A240:C240"/>
-    <mergeCell ref="A147:C147"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A215:C215"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A176:C176"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A225:C225"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A177:C177"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A242:C242"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A259:C259"/>
+    <mergeCell ref="A253:C253"/>
+    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A212:C212"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A230:C230"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A220:C220"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A186:C186"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A222:C222"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A143:C143"/>
+    <mergeCell ref="A232:C232"/>
+    <mergeCell ref="A142:C142"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A241:C241"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A216:C216"/>
+    <mergeCell ref="A168:C168"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3807,220 +3924,220 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>待っている判断</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>月の途中で給与が変わる場合の計算例</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>判断1＝所定労働日割</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>ヘルプ勤務の人件費の計上先</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>深夜残業代の金額</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>みなし残業を超えた/届かなかったときの扱い</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>人件費実績のモーダルから直したときの適用日付</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>翌月で差額を調整する条件</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>判断2（対象費目）</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>次段階可</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>「設定インポート」「設定取込データ」の画面名</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>判断3・4（名称の統一）</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>権限による違いの表</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
@@ -4034,119 +4151,119 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>確認すること</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>予約した変更の取り消し手順</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>実装されているか、手順は何か</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>従業員を削除したときの過去実績の扱い</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>実績が残るか、消えるか</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>締め解除の記録（誰が・いつ）</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>締め済み期間への適用時の警告表示</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>警告が出るか（モック未実装。T-D07）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>締め実行時の事前チェック</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>CSV取り込みのエラー表示</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
         </is>
@@ -4160,286 +4277,286 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>撮影する状態</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>対応する検証ID</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>サイドバー</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>「従業員管理」を展開した状態（7項目）</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>右上のテンプレートDLボタンが見える状態</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>CSVをドロップし、取り込み列設定が表示された状態</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>適用日付の入力欄と設定変更履歴が見える状態</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>フィルタ（変更ソース・期間）が見える状態</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>月別実績・実績モードで内訳の列が出た状態</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>締めの確認モーダル</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>①②が選択され、データ項目カードが見える状態</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>実績データ取込中の進捗モーダル</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>前回差分表示のモーダル（前回→新規の差）</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C277"/>
+  <dimension ref="A1:C270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>データを外に出す</t>
+          <t>データを出力する</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>操作する場所</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>従業員管理の対象外です。先に登録をお願いいたします</t>
+          <t>店舗の管理画面（従業員管理の対象外です）</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。2では両方を取り込んでください。</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>操作する場所</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>「数字が合わないとき」をご覧ください</t>
+          <t>次の「数字が合わないとき」の手順</t>
         </is>
       </c>
     </row>
@@ -990,719 +990,729 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="28" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。毎月はじめに実施してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めたあとは金額が変わりません。給与計算・会計へ数字をお渡しになる前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>従業員を登録・変更する</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>採用や給与改定など、必要が生じたつど行います。</t>
         </is>
       </c>
     </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>やりたいこと</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+    </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>やりたいこと</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>従業員を1名登録する</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧 →「従業員登録」→ 入力 →「登録」</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>従業員を1名登録する</t>
+          <t>設定を変更する</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧 →「従業員登録」→ 入力 →「登録」</t>
+          <t>従業員一覧 → 詳細アイコン → 従業員詳細で修正 →「保存」</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>設定を変更する</t>
+          <t>給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧 → 詳細アイコン → 従業員詳細で修正 →「保存」</t>
+          <t>従業員詳細で新しい金額を入力し、適用日付に改定日を指定 →「保存」</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>数字を見ながらその場で直す</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力し、適用日付に改定日を指定 →「保存」</t>
+          <t>人件費実績 →「従業員設定」→ 修正 →「更新保存」</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>数字を見ながらその場で直す</t>
+          <t>変更の経緯を確認する</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>人件費実績 →「従業員設定」→ 修正 →「更新保存」</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>変更の経緯を確認する</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
           <t>従業員設定履歴 → 名前をクリック → 従業員詳細</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>※ 適用日付に未来の日付を指定すると、その日まで反映されません。改定日を待たずにご登録いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員詳細と人件費実績のどちらから編集しても、変更は設定変更履歴に記録されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>※ 適用日付に未来の日付を指定すると、その日まで反映されません。改定日を待たずにご登録いただけます。なお従業員詳細と人件費実績のどちらから編集しても、変更は設定変更履歴に記録されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴（変更ソースで絞り込み）</t>
+        </is>
+      </c>
+    </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>取り込んだ勤怠実績の元データ</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴（変更ソースで絞り込み）</t>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。応援に出た分は所属店舗から差し引かれ、応援先の店舗に計上されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>※ 各金額の算出方法は、画面ごとの項目の「人件費実績」に記載しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい設定を入力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。応援に出た分は所属店舗から差し引かれ、応援先の店舗に計上されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>※ 各金額の算出方法は、画面ごとの項目の「人件費実績」に記載しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>新しい設定を入力する</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>適用日付に締め済み期間の翌日以降を指定して保存する</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は翌月で調整する</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>─</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は、警告が表示され反映されません。</t>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から、①エクスポート種別（設定／実績）②対象とデータ項目 を選び、「出力」でCSVを取得いただけます。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>※ 締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>※ 選択できる組み合わせと出力されるファイル数は、画面ごとの項目の「設定・実績エクスポート」に記載しております。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>データを外に出す</t>
+          <t>画面ごとの項目</t>
         </is>
       </c>
     </row>
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
+          <t>ここから先は、画面ごとの表示項目・ボタン・入力欄の説明です。操作の手順は前半の各項目をご覧ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理メニューは2つのグループで構成しております。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>対象とデータ項目を選ぶ</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>グループ</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>メニュー</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>閲覧・管理</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>「出力」でCSVを取得する</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
+          <t>従業員の設定を一覧で確認・登録・編集</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>閲覧・管理</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>全従業員の設定変更履歴を横断で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>※ 選択肢の詳細とファイル数は、画面ごとの項目の「設定・実績エクスポート」に記載しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>画面ごとの項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>ここから先は、画面ごとの表示項目・ボタン・入力欄の説明です。操作の手順は前半の各項目をご覧ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>サイドバーの構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理メニューは2つのグループで構成しております。</t>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>項目を選択してCSVで出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データを確認</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>グループ</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>メニュー</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>従業員の設定を一覧で確認・登録・編集</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認。月次の締めを実行</t>
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>データ連携</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>画面の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>閲覧・管理</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認</t>
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>移動元</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>移動先</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>名前をクリック／詳細アイコン</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録</t>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>「従業員登録」</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>項目を選択してCSVで出力</t>
+          <t>従業員登録</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>「設定インポート」</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データを確認</t>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>データ連携</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>「設定・実績エクスポート」</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データを確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>画面の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>2段目「設定取込データへ」</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>「保存」／「一覧へ戻る」</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>移動元</t>
-        </is>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>移動先</t>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>「登録」</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>名前をクリック／詳細アイコン</t>
+          <t>「実績データ取込」</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>取込中の進捗表示 → 人件費実績に反映</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>「従業員登録」</t>
+          <t>「従業員設定」</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>「設定インポート」</t>
+          <t>「実績取込データへ」</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>実績取込データ</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>「設定・実績エクスポート」</t>
+          <t>「人件費実績へ」</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>人件費実績</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>従業員設定履歴</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>2段目「設定取込データへ」</t>
+          <t>名前をクリック</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>従業員詳細</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>「保存」／「一覧へ戻る」</t>
+          <t>「列マッピングテンプレート管理」</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>設定インポート</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -1717,1113 +1727,1079 @@
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>「実績データ取込」</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>取込中の進捗表示 → 人件費実績に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>「従業員設定」</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>「実績取込データへ」</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>名前をクリック</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>クリックで従業員詳細へ遷移</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」</t>
+          <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>重複した登録は不可</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>「登録」</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>1店舗のみ設定可能。人件費の計上先</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>登録済みの従業員を一覧で表示しております。設定の登録・編集・削除の起点となる画面です。</t>
-        </is>
-      </c>
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>複数設定可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイト</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>給与単位</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>月給／時給</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr"/>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>単位給与額</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>月給額または時給額</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>交通費単位</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>クリックで従業員詳細へ遷移</t>
-        </is>
-      </c>
+          <t>日額／月額</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr"/>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>単位交通費</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>勤怠データとの突合に使用するコード</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>重複した登録は不可</t>
-        </is>
-      </c>
+          <t>交通費の金額</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr"/>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>所定労働時間</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>1店舗のみ設定可能。人件費の計上先</t>
-        </is>
-      </c>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr"/>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>みなし残業時間</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>複数設定可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイト</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr"/>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>給与単位</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>月給／時給</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr"/>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>単位給与額</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>月給額または時給額</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>月給＝バッジ濃色、時給＝バッジ淡色</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>交通費単位</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>日額／月額</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr"/>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>単位交通費</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>交通費の金額</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>入力項目</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr"/>
+          <t>従業員の氏名</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr"/>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
+          <t>勤怠データとの突合コード</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>必須。既存と重複する場合は登録不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>主に勤務する店舗</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>必須。1店舗のみ</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>従業員を1名ずつ登録する画面です。従業員一覧の右上「従業員登録」から遷移します。</t>
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイト</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>給与単位・単位給与額</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>月給／時給と金額</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>入力項目</t>
-        </is>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>交通費単位・単位交通費</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>日額／月額と金額</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr"/>
     </row>
     <row r="129" ht="18" customHeight="1">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>従業員の氏名</t>
+          <t>応援先ごとの交通費</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>従業員コード</t>
+          <t>所定労働時間</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>勤怠データとの突合コード</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>必須。既存と重複する場合は登録不可</t>
-        </is>
-      </c>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr"/>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>みなし残業時間</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>必須。1店舗のみ</t>
-        </is>
-      </c>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr"/>
     </row>
     <row r="132" ht="18" customHeight="1">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>適用日付</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>この内容が有効となる日付</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
     <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイト</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>給与単位・単位給与額</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>月給／時給と金額</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>交通費単位・単位交通費</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>日額／月額と金額</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>応援先ごとの交通費</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択すると入力欄を自動表示。店舗ごとに個別設定</t>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>所定労働時間</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>未来日</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr"/>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>設定変更履歴に「予約中」で追加</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>適用日付</t>
+          <t>当日・過去日</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>この内容が有効となる日付</t>
+          <t>「即時反映しました」と表示。その時点から反映</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>必須。初期値は当日</t>
+          <t>設定変更履歴に「適用中」で追加</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>従業員1名の設定・変更履歴・給与実績を確認する画面です。従業員一覧の詳細アイコンから遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>基本情報は従業員登録と同じ項目を編集可能です。適用日付は所定労働時間・みなし残業時間の下に配置しております。修正後は画面下の「保存」で確定し、従業員一覧に戻ります。「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>締め済み期間内</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>警告を表示。反映されない</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>締め済みの月は変更不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴は次の列で構成しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>適用日付と同じ</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>設定を入力した日時</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時とは異なる</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>未来日</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されない</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>設定変更履歴に「予約中」で追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
+          <t>適用日を迎えると予約中→適用中に変化</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>当日・過去日</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>「即時反映しました」と表示。その時点から反映</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>設定変更履歴に「適用中」で追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="18" customHeight="1">
+          <t>変更の経路を記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="28" customHeight="1">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>締め済み期間内</t>
+          <t>その他の列</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>警告を表示。反映されない</t>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>締め済みの月は変更不可</t>
+          <t>変更時点の値</t>
         </is>
       </c>
     </row>
     <row r="148" ht="16" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴は次の列で構成しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
+          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>適用日付と同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>編集日時</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>設定を入力した日時</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時とは異なる</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>適用日を迎えると予約中→適用中に変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路を記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="28" customHeight="1">
+    <row r="154" ht="18" customHeight="1">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>その他の列</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>変更時点の値</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>給与実績は月次実績（17列）・日次実績（14列）のタブで構成しております。年・月での絞り込みとCSV出力が可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>月別・日別の人件費を確認する画面です。月次の締めもこの画面から実行します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="28" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・経営のご担当者様は、月別実績の「実績」モードをご確認ください。店舗ごとの人件費と、その合計である全社の人件費が表示されます。以下の表は各列の算出方法です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="28" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>月別実績は給与計算モード（概算／実績）で表示列が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>想定給与（概算給与）</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績の実働時間の合計</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>実績データ取込後に反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>みなし労働時間差分</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>プラスが超過、マイナスが未達</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>深夜残業代</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>時間外1.25＋深夜0.25の割増</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>給与（実績給与）</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>交通費は含みません</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗労働時間</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>交通費</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>実績データ取込後に反映</t>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>みなし労働時間差分</t>
+          <t>総支給額</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
-        </is>
-      </c>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr"/>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>深夜残業代</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>給与（実績給与）</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>所属店舗労働時間</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間 − ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>所属店舗で勤務した時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>日別実績の合計</t>
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>※ 日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績タブにのみ表示されます。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>締め前</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="171" ht="18" customHeight="1">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>総支給額</t>
+          <t>締め後</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr"/>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="28" customHeight="1">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>日別実績は全21列で、1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費を確認可能です。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>※ 日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績タブにのみ表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="42" customHeight="1">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>締め後</t>
+          <t>従業員設定</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>対象の従業員の設定編集モーダルを開く</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
         </is>
       </c>
     </row>
     <row r="179" ht="18" customHeight="1">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>締め解除後</t>
+          <t>更新保存</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>変更を保存し、人件費実績に戻る</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>数字が再計算されます</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め後はデータの編集ができなくなります。給与計算・会計へ数字を渡す前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>※ 実績データを取り込むまで、実績の金額は表示されません。締めは取込後に実行してください。</t>
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>変更せずに閉じる</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>人件費実績の画面から従業員設定を直すことも可能です。数字を確認しながら、画面を移動せずに修正いただけます。</t>
+          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>絞り込み</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -2837,130 +2813,126 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="42" customHeight="1">
+    <row r="185" ht="28" customHeight="1">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>対象の従業員の設定編集モーダルを開く</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>名前／従業員コード／所属店舗／ヘルプ先店舗／雇用区分／給与単位／単位給与額／交通費単位／単位交通費／ヘルプ先交通費／所定労働時間／みなし残業時間／変更反映日時範囲</t>
+          <t>変更の経路で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="186" ht="18" customHeight="1">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>更新保存</t>
+          <t>店舗・雇用区分</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>変更を保存し、人件費実績に戻る</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>数字が再計算されます</t>
-        </is>
-      </c>
+          <t>対象者で絞り込み</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr"/>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>編集日時範囲</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>変更せずに閉じる</t>
+          <t>入力した日時の期間で絞り込み</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr"/>
     </row>
     <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員詳細から編集した場合と同じく、変更は設定変更履歴に記録されます。どちらから編集しても「いつ・何を変えたか」は残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>全従業員の設定変更履歴を横断で確認する画面です。列構成は従業員詳細の設定変更履歴に「名前」を加えたものです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>従業員名</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>氏名で検索</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
+      <c r="C192" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B192" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>店舗・雇用区分</t>
+          <t>CSVテンプレート</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>対象者で絞り込み</t>
-        </is>
-      </c>
-      <c r="C193" s="6" t="inlineStr"/>
+          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。BOM付きCSV</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>編集日時範囲</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>入力した日時の期間で絞り込み</t>
+          <t>King of Time／ジョブカン／新規作成</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr"/>
@@ -2968,34 +2940,58 @@
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>従業員名</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr"/>
+          <t>保存済みの列の対応づけ</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>選択すると取込列設定に自動反映</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費の数字に疑問がある場合、まず変更ソースをご確認ください。CSVインポートの場合は設定取込データで元のファイルを確認可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CSVで従業員設定・給与設定を一括登録する画面です。</t>
+          <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
@@ -3007,1060 +3003,952 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>記法</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>例</t>
         </is>
       </c>
     </row>
     <row r="200" ht="18" customHeight="1">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>CSVテンプレート</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
+          <t>セミコロン区切り</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
+          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>データ種類</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C201" s="6" t="inlineStr"/>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="6" t="inlineStr">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="7" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>CSV位置合わせ設定</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
+    </row>
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B206" s="5" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C206" s="5" t="inlineStr">
-        <is>
-          <t>例</t>
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="207" ht="18" customHeight="1">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>セミコロン区切り</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>青山店;新宿店</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>青山店:700;新宿店:900</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。給与のみ変更する場合は給与設定のみ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>CSVの列名とラクミーの項目の対応づけを保存する画面です。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="28" customHeight="1">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C212" s="5" t="inlineStr">
+      <c r="C213" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="A213" s="6" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B213" s="6" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="214" ht="18" customHeight="1">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>① エクスポート種別</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>設定／実績</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="215" ht="18" customHeight="1">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>② エクスポートデータ詳細選択</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C216" s="6" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="28" customHeight="1">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>※ 勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。テンプレートに保存することで、次回以降は選択のみで取り込み可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="22" customHeight="1">
-      <c r="A218" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="16" customHeight="1">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>必要な項目を選択してCSVで出力する画面です。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>データ項目のカテゴリ</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="28" customHeight="1">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="28" customHeight="1">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
-      <c r="A220" s="5" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B220" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C220" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="18" customHeight="1">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>① エクスポート種別</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="18" customHeight="1">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>② エクスポートデータ詳細選択</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
-        <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
-        </is>
-      </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="22" customHeight="1">
+      <c r="A221" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ元のデータを確認する画面です。</t>
         </is>
       </c>
     </row>
     <row r="223" ht="18" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>データ項目のカテゴリ</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="28" customHeight="1">
+          <t>取り込む内容の一覧を表示</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>給与設定</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="28" customHeight="1">
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+          <t>取込を実行</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>進捗を表示</t>
         </is>
       </c>
     </row>
     <row r="227" ht="18" customHeight="1">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ／実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ元のデータを確認する画面です。</t>
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
         </is>
       </c>
     </row>
     <row r="230" ht="18" customHeight="1">
-      <c r="A230" s="5" t="inlineStr">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="24" customHeight="1">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="16" customHeight="1">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="A233" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B230" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C231" s="6" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="18" customHeight="1">
-      <c r="A232" s="6" t="inlineStr">
-        <is>
-          <t>前回差分表示</t>
-        </is>
-      </c>
-      <c r="B232" s="6" t="inlineStr">
-        <is>
-          <t>前回の取込との差を表示</t>
-        </is>
-      </c>
-      <c r="C232" s="6" t="inlineStr">
-        <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="18" customHeight="1">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>読み込み</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
-        <is>
-          <t>取込を実行</t>
-        </is>
-      </c>
-      <c r="C233" s="6" t="inlineStr">
-        <is>
-          <t>進捗を表示</t>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>店長</t>
         </is>
       </c>
     </row>
     <row r="234" ht="18" customHeight="1">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B234" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C234" s="5" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>人件費実績の閲覧</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
+          <t>可</t>
         </is>
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
     </row>
     <row r="236" ht="18" customHeight="1">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>月次の締め・締め解除</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
+          <t>可</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="237" ht="18" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="24" customHeight="1">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="16" customHeight="1">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="18" customHeight="1">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B240" s="5" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C240" s="5" t="inlineStr">
-        <is>
-          <t>店長</t>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="28" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>エラーが表示されたときは</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="16" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
         </is>
       </c>
     </row>
     <row r="241" ht="18" customHeight="1">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="242" ht="18" customHeight="1">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C242" s="6" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="243" ht="18" customHeight="1">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="244" ht="18" customHeight="1">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="28" customHeight="1">
-      <c r="A245" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="24" customHeight="1">
-      <c r="A246" s="4" t="inlineStr">
-        <is>
-          <t>エラーが表示されたときは</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="16" customHeight="1">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーとなる場合、次の原因が考えられます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="18" customHeight="1">
-      <c r="A248" s="5" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B248" s="5" t="inlineStr">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="28" customHeight="1">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B247" s="6" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="16" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>設定を保存できない場合は次をご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
         <is>
           <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="18" customHeight="1">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="250" ht="18" customHeight="1">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="251" ht="18" customHeight="1">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="18" customHeight="1">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B252" s="6" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="18" customHeight="1">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="28" customHeight="1">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B254" s="6" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="16" customHeight="1">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>設定を保存できない場合は次をご確認ください。</t>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="16" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="18" customHeight="1">
+      <c r="A254" s="5" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="18" customHeight="1">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
     <row r="256" ht="18" customHeight="1">
-      <c r="A256" s="5" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B256" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>該当画面</t>
         </is>
       </c>
     </row>
     <row r="257" ht="18" customHeight="1">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="18" customHeight="1">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>締め済み期間の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
-        <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="24" customHeight="1">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="16" customHeight="1">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="18" customHeight="1">
-      <c r="A261" s="5" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>移行について</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="16" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="18" customHeight="1">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="28" customHeight="1">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="262" ht="18" customHeight="1">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧／人件費実績</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="263" ht="18" customHeight="1">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>該当画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="18" customHeight="1">
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="28" customHeight="1">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
+          <t>店舗別の人件費</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
     <row r="265" ht="24" customHeight="1">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>移行について</t>
-        </is>
-      </c>
-    </row>
-    <row r="266" ht="16" customHeight="1">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>本機能の対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="18" customHeight="1">
+      <c r="A266" s="5" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="267" ht="18" customHeight="1">
-      <c r="A267" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B267" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="28" customHeight="1">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="18" customHeight="1">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="269" ht="18" customHeight="1">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>権限設定</t>
         </is>
       </c>
     </row>
     <row r="270" ht="18" customHeight="1">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>入退社の手続き・年末調整</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="28" customHeight="1">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="24" customHeight="1">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="18" customHeight="1">
-      <c r="A273" s="5" t="inlineStr">
-        <is>
-          <t>対象外の内容</t>
-        </is>
-      </c>
-      <c r="B273" s="5" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="18" customHeight="1">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B274" s="6" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="18" customHeight="1">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>出退勤の打刻・シフトの作成</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
-        <is>
-          <t>ラクミータイムレコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="18" customHeight="1">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>ログインアカウントの発行・権限の設定</t>
-        </is>
-      </c>
-      <c r="B276" s="6" t="inlineStr">
-        <is>
-          <t>権限設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="18" customHeight="1">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>入退社の手続き・年末調整</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
-        <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A255:C255"/>
-    <mergeCell ref="A80:C80"/>
+  <mergeCells count="88">
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A136:C136"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A210:C210"/>
-    <mergeCell ref="A272:C272"/>
-    <mergeCell ref="A247:C247"/>
     <mergeCell ref="A71:C71"/>
     <mergeCell ref="A181:C181"/>
-    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A165:C165"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A220:C220"/>
     <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A83:C83"/>
     <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A196:C196"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A69:C69"/>
     <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A205:C205"/>
     <mergeCell ref="A183:C183"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A246:C246"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A198:C198"/>
     <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A55:C55"/>
     <mergeCell ref="A239:C239"/>
+    <mergeCell ref="A248:C248"/>
+    <mergeCell ref="A104:C104"/>
     <mergeCell ref="A175:C175"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A159:C159"/>
-    <mergeCell ref="A219:C219"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A265:C265"/>
     <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A258:C258"/>
     <mergeCell ref="A211:C211"/>
     <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A266:C266"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A260:C260"/>
-    <mergeCell ref="A197:C197"/>
-    <mergeCell ref="A228:C228"/>
-    <mergeCell ref="A124:C124"/>
     <mergeCell ref="A237:C237"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A172:C172"/>
+    <mergeCell ref="A212:C212"/>
+    <mergeCell ref="A252:C252"/>
+    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A189:C189"/>
-    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A188:C188"/>
-    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A204:C204"/>
+    <mergeCell ref="A151:C151"/>
     <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A134:C134"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A176:C176"/>
     <mergeCell ref="A182:C182"/>
     <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A227:C227"/>
+    <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A217:C217"/>
     <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A244:C244"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A203:C203"/>
+    <mergeCell ref="A85:C85"/>
     <mergeCell ref="A259:C259"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A253:C253"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A231:C231"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A245:C245"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A142:C142"/>
+    <mergeCell ref="A240:C240"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A232:C232"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A218:C218"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A168:C168"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -637,7 +637,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>└ サイドバーの構成 ／ 画面の移動</t>
+          <t>画面ごとの項目：サイドバーの構成 ／ 画面の移動</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>└ 従業員一覧 ／ 従業員登録 ／ 従業員詳細</t>
+          <t>画面ごとの項目：従業員一覧 ／ 従業員登録 ／ 従業員詳細</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>└ 人件費実績</t>
+          <t>画面ごとの項目：人件費実績</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>└ 従業員設定履歴 ／ 設定取込データ・実績取込データ</t>
+          <t>画面ごとの項目：従業員設定履歴 ／ 設定取込データ・実績取込データ</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -682,10 +682,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>└ 設定インポート ／ 列マッピングテンプレート ／ 設定・実績エクスポート</t>
+          <t>画面ごとの項目：設定インポート ／ 列マッピングテンプレート ／ 設定・実績エクスポート</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>画面の構成と移動、各画面で共通して使う項目の意味、権限、対象範囲</t>
+          <t>画面の構成、各画面で共通して使う項目の意味、権限、対象範囲</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>画面の構成と移動</t>
+          <t>画面の構成</t>
         </is>
       </c>
     </row>
@@ -750,2086 +750,2001 @@
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から移動いただけます。</t>
+          <t>起点となる画面は2つです。個人の設定を確認・変更する場合は従業員一覧から、月次の数字を確認する場合は人件費実績から、それぞれ画面上のボタンで移動いただけます。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>移動元</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>移動先</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>名前をクリック／詳細アイコン</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧の絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>「従業員登録」</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>「設定インポート」</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>「設定・実績エクスポート」</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>従業員設定の項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧・従業員登録・従業員詳細と、人件費実績の「従業員設定」で共通してお使いいただく項目です。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>2段目「設定取込データへ」</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>「保存」／「一覧へ戻る」</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>必須。従業員一覧でクリックすると従業員詳細へ移動します</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>従業員登録</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>「登録」</t>
+          <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>必須。既存と重複する場合は登録できません</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>「実績データ取込」</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>取込中の進捗表示 → 人件費実績に反映</t>
+          <t>必須。1店舗のみ。人件費の計上先になります</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>「従業員設定」</t>
+          <t>応援に行く店舗</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>設定編集モーダル →「更新保存」→ 人件費実績</t>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>「実績取込データへ」</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>給与単位</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>「人件費実績へ」</t>
+          <t>月給／時給</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>従業員設定履歴</t>
+          <t>単位給与額</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>名前をクリック</t>
+          <t>月給額または時給額</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>交通費単位</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
+          <t>日額／月額</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>設定インポート</t>
+          <t>単位交通費</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>「登録」</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
+          <t>交通費の金額</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>※ 締め・締め解除は画面が切り替わりません。人件費実績の同じ画面で、ボタンの表記が「締め」と「締め解除」に切り替わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧の絞り込みは2段構成としております。1段目が対象者の絞り込み（店舗／雇用区分／従業員名）、2段目が対象データの選択（月／取込データ）です。</t>
-        </is>
-      </c>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>応援先ごとの交通費</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当するデータがない場合は「データはありません。」と表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>従業員設定の項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧・従業員登録・従業員詳細・人件費実績の設定編集モーダルで、共通してお使いいただく項目です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>この内容が有効となる日付</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>必須。初期値は当日</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>人件費の項目と算出方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績と、従業員詳細の給与実績で共通してお使いいただく項目です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>必須。従業員一覧でクリックすると従業員詳細へ移動します</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>勤怠データとの突合に使用するコード</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>必須。既存と重複する場合は登録できません</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>所属店舗</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>主に勤務する店舗</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>必須。1店舗のみ。人件費の計上先になります</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>想定給与（概算給与）</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>総労働時間</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
+          <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>給与単位</t>
+          <t>みなし労働時間差分</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>月給／時給</t>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>単位給与額</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>月給額または時給額</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>必須。一覧では月給＝バッジ濃色、時給＝バッジ淡色で表示</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>交通費単位</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>日額／月額</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr"/>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>交通費は含みません</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>単位交通費</t>
+          <t>所属店舗労働時間</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>交通費の金額</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr"/>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>応援先ごとの交通費</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr"/>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>交通費</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr"/>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>適用日付</t>
+          <t>総支給額</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>この内容が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>必須。初期値は当日。所定労働時間・みなし残業時間の下に配置しております</t>
-        </is>
-      </c>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>人件費の項目と算出方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>人件費実績と、従業員詳細の給与実績で共通してお使いいただく項目です。</t>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>表示は次の単位に分かれております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>月別実績</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>全従業員の月次。給与計算モード（概算／実績）で表示列が切り替わります</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
+          <t>日別実績</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+          <t>1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費。交通費は所属店舗分と応援先分を別の列で表示</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>月次実績／日次実績</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>従業員1名分。年・月での絞り込みとCSV出力が可能です</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>勤怠実績の実働時間の合計</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>みなし労働時間差分</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>深夜残業代</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>※ 概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>設定変更履歴の項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>従業員詳細の「設定変更履歴」と、従業員設定履歴で共通してお使いいただく項目です。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>給与（実績給与）</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>適用日付と同じ</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>設定を入力した日時</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
+          <t>適用日を迎えると予約中→適用中に変化します</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
+          <t>変更の経路を記録します</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>総支給額</t>
+          <t>その他の項目</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr"/>
+          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>変更時点の値</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>表示は次の単位に分かれております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>場所</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>※ 従業員設定履歴は全従業員を横断で確認する画面です。項目は上記に「名前」を加えたものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>権限による違い</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>従業員管理は給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>月別実績</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>全従業員の月次。給与計算モード（概算／実績）で表示列が切り替わります</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>日別実績</t>
+          <t>可</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>全21列。1日ごとの勤務時間・ヘルプ時間・深夜残業時間・交通費。交通費は所属店舗分と応援先分を別の列で表示</t>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>人件費実績の閲覧</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>月次実績（17列）／日次実績（14列）</t>
+          <t>可</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>従業員1名分。年・月での絞り込みとCSV出力が可能です</t>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>※ 概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>設定変更履歴の項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細の「設定変更履歴」と、従業員設定履歴で共通してお使いいただく項目です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>本機能の対象外</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>適用日付と同じ</t>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>対象外の内容</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>設定を入力した日時</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>変更反映日時とは異なります</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>適用日を迎えると予約中→適用中に変化します</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>変更の経路を記録します</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>その他の項目</t>
+          <t>入退社の手続き・年末調整</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>雇用区分／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／所属店舗／ヘルプ先店舗</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>変更時点の値</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定履歴は全従業員を横断で確認する画面です。項目は上記に「名前」を加えたものです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>権限による違い</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>従業員管理は会社スコープの機能です。給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>導入時と毎月の運用で行う操作です。項目の意味は「共通項目」をご覧ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>はじめて設定する（導入時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>導入時に1回だけ行う作業です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>操作する場所</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>人件費実績の閲覧</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>店舗マスタを登録する</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>店舗の管理画面（従業員管理の対象外です）</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>従業員の設定をCSVで一括登録する</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>設定インポート</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>本機能の対象外</t>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ内容を確認する</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>不足分を1名ずつ登録する</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧 →「従業員登録」</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>設定インポートの画面では次の内容を指定いただけます。</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>対象外の内容</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>CSVテンプレート</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>従業員設定CSVテンプレート／給与設定CSVテンプレート</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。Excelで開いても文字化けいたしません</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr"/>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>保存済みの列の対応づけ</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>選択すると取込列設定に自動反映されます</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>操作手順</t>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>導入時と毎月の運用で行う操作です。項目の意味は「共通項目」をご覧ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>はじめて設定する（導入時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>導入時に1回だけ行う作業です。</t>
+          <t>CSVの記法は次のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>記法</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>例</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>セミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>店舗名:金額 をセミコロン区切り</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>青山店:700;新宿店:900</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>従業員を登録する</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧の右上「従業員登録」から、1名ずつご登録いただけます。入力項目は共通項目の「従業員設定の項目」をご覧ください。入力後「登録」を押すと従業員一覧に戻り、新しい行が追加されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>※ 必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>入口</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>操作する場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>店舗マスタを登録する</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>店舗の管理画面（従業員管理の対象外です）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>従業員の設定をCSVで一括登録する</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ内容を確認する</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>不足分を1名ずつ登録する</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧 →「従業員登録」</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>設定インポートの画面では次の内容を指定いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート（6列）／給与設定CSVテンプレート（9列）</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。BOM付きCSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>データ種類</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr"/>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>戻り先</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>従業員詳細</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>保存済みの列の対応づけ</t>
+          <t>従業員一覧 → 詳細アイコン → 修正 →「保存」</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>選択すると取込列設定に自動反映されます</t>
+          <t>従業員一覧</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>人件費実績</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
+          <t>人件費実績 →「従業員設定」→ 修正 →「更新保存」</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
+          <t>人件費実績（数字が再計算されます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>保存したときの動きは、適用日付によって変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>設定変更履歴</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>記法</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>例</t>
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>当日・過去日</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>セミコロン区切り</t>
+          <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>青山店;新宿店</t>
+          <t>「適用中」で追加</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>締め済み期間内</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>店舗名:金額 をセミコロン区切り</t>
+          <t>警告を表示し、反映されません</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>青山店:700;新宿店:900</t>
+          <t>追加されません</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
+          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="18" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
+          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>従業員を登録する</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="16" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧の右上「従業員登録」から、1名ずつご登録いただけます。入力項目は共通項目の「従業員設定の項目」をご覧ください。入力後「登録」を押すと従業員一覧に戻り、新しい行が追加されます。</t>
+          <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>※ 必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>従業員の設定を変更する</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。</t>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>操作する場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>月次の人件費を確認する</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>戻り先</t>
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>数字が合わない場合は原因を調べる</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>ケース別「数字が合わないとき」</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧 → 詳細アイコン → 修正 →「保存」</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>人件費実績 →「従業員設定」→ 修正 →「更新保存」</t>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>人件費実績（数字が再計算されます）</t>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>保存したときの動きは、適用日付によって変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>設定変更履歴</t>
+          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績タブにのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>未来日</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>「予約中」で追加</t>
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>当日・過去日</t>
+          <t>締め前</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>「即時反映しました」と表示。その時点から反映されます</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>「適用中」で追加</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>締め済み期間内</t>
+          <t>締め後</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>警告を表示し、反映されません</t>
+          <t>反映されません</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>追加されません</t>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>取り込んだ元データを確認する</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>毎月、同じ順序で行います。</t>
+          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>順</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>操作する場所</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>勤怠実績を取り込む</t>
+          <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>人件費実績 →「実績データ取込」</t>
+          <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>月次の人件費を確認する</t>
+          <t>前回の取込との差を表示</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>人件費実績（月別実績／日別実績）</t>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>数字が合わない場合は原因を調べる</t>
+          <t>取込を実行</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>ケース別「数字が合わないとき」</t>
+          <t>進捗を表示します</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>画面間の移動</t>
         </is>
       </c>
     </row>
     <row r="146" ht="18" customHeight="1">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>設定取込データ</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
+          <t>従業員設定／給与設定</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績タブにのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
+          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>「人件費実績へ」で人件費実績に戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>締め後</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="152" ht="18" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>締め解除後</t>
+          <t>① エクスポート種別</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>設定／実績</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="24" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>② エクスポートデータ詳細選択</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>③ 出力</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>「出力」でCSVを取得</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>データ項目のカテゴリ</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>ケース別</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>個別の状況への対応です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B156" s="5" t="inlineStr">
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい金額を入力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C156" s="5" t="inlineStr">
+      <c r="C171" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>設定：11項目／実績：総労働時間・給与・交通費ほか</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>前回差分表示</t>
-        </is>
-      </c>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>前回の取込との差を表示</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>読み込み</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>取込を実行</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>進捗を表示します</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>画面間の移動</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧の2段目「設定取込データへ」からも遷移可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>「人件費実績へ」で人件費実績に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B166" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
-        <is>
-          <t>① エクスポート種別</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>設定／実績</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>② エクスポートデータ詳細選択</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>設定：対象（複数選択可）＋データ項目　／　実績：給与実績の月＋データ項目</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>③ 出力</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>「出力」でCSVを取得</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr"/>
-    </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
-        <is>
-          <t>データ項目のカテゴリ</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="28" customHeight="1">
+    <row r="172" ht="18" customHeight="1">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>給与設定</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="28" customHeight="1">
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力ファイルはBOM付きCSVのため、Excelで文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="28" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t>ケース別</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>個別の状況への対応です。</t>
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="28" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2756,12 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2773,12 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴（変更ソースで絞り込み）</t>
         </is>
       </c>
     </row>
@@ -2865,321 +2790,291 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="28" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="24" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>CSVの列名がラクミーと違うとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="28" customHeight="1">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から遷移します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定履歴では、次の条件で絞り込みいただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="187" ht="18" customHeight="1">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>店舗・雇用区分</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>対象者で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>編集日時範囲</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>入力した日時の期間で絞り込み</t>
         </is>
       </c>
     </row>
     <row r="189" ht="18" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>従業員名</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="28" customHeight="1">
+          <t>氏名で検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="28" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+          <t>※ 各金額の算出方法は、共通項目の「人件費の項目と算出方法」に記載しております。</t>
         </is>
       </c>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="194" ht="18" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
         <is>
-          <t>順</t>
+          <t>項目</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C194" s="5" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="195" ht="18" customHeight="1">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴（変更ソースで絞り込み）</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
+          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>全社の合計</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>従業員設定履歴では、次の条件で絞り込みいただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>対象者で絞り込み</t>
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>編集日時範囲</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>入力した日時の期間で絞り込み</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>従業員名</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>氏名で検索</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="28" customHeight="1">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="18" customHeight="1">
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="28" customHeight="1">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>※ 各金額の算出方法は、共通項目の「人件費の項目と算出方法」に記載しております。</t>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+          <t>すでにご利用中のお客様（移行について）</t>
         </is>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
@@ -3191,497 +3086,347 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="18" customHeight="1">
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="28" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="18" customHeight="1">
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="28" customHeight="1">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>店舗別の人件費</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="28" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
         </is>
       </c>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>CSVの取り込みでエラーになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
-      <c r="A217" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>従業員コードが空</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="219" ht="18" customHeight="1">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="220" ht="18" customHeight="1">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="28" customHeight="1">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="24" customHeight="1">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様（移行について）</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="28" customHeight="1">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できない</t>
         </is>
       </c>
     </row>
     <row r="224" ht="18" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="28" customHeight="1">
+          <t>対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="226" ht="18" customHeight="1">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="18" customHeight="1">
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="28" customHeight="1">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="28" customHeight="1">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="28" customHeight="1">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになる</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="24" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>ご質問</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="28" customHeight="1">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>実績の金額が表示されない</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="28" customHeight="1">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>締めたあとに数字を直したい</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="232" ht="18" customHeight="1">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>日別実績で概算が選べない</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="18" customHeight="1">
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="28" customHeight="1">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>給与のみ変更したい</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="18" customHeight="1">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="18" customHeight="1">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B236" s="6" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="28" customHeight="1">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="24" customHeight="1">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できない</t>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="24" customHeight="1">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="16" customHeight="1">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
     <row r="239" ht="18" customHeight="1">
-      <c r="A239" s="5" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B239" s="5" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="inlineStr">
+        <is>
+          <t>該当画面</t>
         </is>
       </c>
     </row>
     <row r="240" ht="18" customHeight="1">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="18" customHeight="1">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>締め済み期間の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="28" customHeight="1">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>必須項目の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
-        <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="24" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="18" customHeight="1">
-      <c r="A244" s="5" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B244" s="5" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="28" customHeight="1">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="28" customHeight="1">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>締めたあとに数字を直したい</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
-        <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="18" customHeight="1">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>日別実績で概算が選べない</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
-        <is>
-          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="18" customHeight="1">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>店舗別の合計が全社と合わない</t>
-        </is>
-      </c>
-      <c r="B248" s="6" t="inlineStr">
-        <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="28" customHeight="1">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>給与のみ変更したい</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
-        <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="16" customHeight="1">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>ご不明な点はサポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="18" customHeight="1">
-      <c r="A252" s="5" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B252" s="5" t="inlineStr">
-        <is>
-          <t>確認場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="18" customHeight="1">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="18" customHeight="1">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B254" s="6" t="inlineStr">
-        <is>
-          <t>該当画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="18" customHeight="1">
-      <c r="A255" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース（手動編集／CSVインポート）</t>
-        </is>
-      </c>
-      <c r="B255" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
@@ -3689,89 +3434,89 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="A128:C128"/>
     <mergeCell ref="A193:C193"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="A208:C208"/>
     <mergeCell ref="A89:C89"/>
     <mergeCell ref="A192:C192"/>
-    <mergeCell ref="A105:C105"/>
     <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A235:C235"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A63:C63"/>
     <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A138:C138"/>
     <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A238:C238"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="A160:C160"/>
+    <mergeCell ref="A159:C159"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A81:C81"/>
     <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A147:C147"/>
+    <mergeCell ref="A161:C161"/>
     <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A201:C201"/>
     <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A250:C250"/>
+    <mergeCell ref="A228:C228"/>
     <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A243:C243"/>
-    <mergeCell ref="A221:C221"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A236:C236"/>
+    <mergeCell ref="A149:C149"/>
     <mergeCell ref="A214:C214"/>
     <mergeCell ref="A163:C163"/>
     <mergeCell ref="A223:C223"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A126:C126"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A150:C150"/>
     <mergeCell ref="A206:C206"/>
     <mergeCell ref="A122:C122"/>
     <mergeCell ref="A215:C215"/>
     <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A190:C190"/>
     <mergeCell ref="A72:C72"/>
     <mergeCell ref="A199:C199"/>
-    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A167:C167"/>
     <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A64:C64"/>
     <mergeCell ref="A191:C191"/>
+    <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
     <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A162:C162"/>
     <mergeCell ref="A177:C177"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A154:C154"/>
-    <mergeCell ref="A251:C251"/>
     <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A109:C109"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A230:C230"/>
+    <mergeCell ref="A117:C117"/>
     <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A94:C94"/>
     <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A216:C216"/>
-    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A168:C168"/>
     <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A65:C65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ本文" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掲載前チェック（社内用）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="撮影一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="掲載前チェック（社内用）" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,11 +51,15 @@
       <sz val="10"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
       <b val="1"/>
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +81,13 @@
         <fgColor rgb="00F1F3F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3BF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -99,11 +109,55 @@
         <color rgb="00D0D7DE"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -120,7 +174,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -621,368 +682,352 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>📸 設定インポート画面｜データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>設定インポートでは次の内容を指定いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定CSVテンプレート／給与設定CSVテンプレート</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>画面右上からダウンロード。Excelで開いても文字化けいたしません</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>データ種類</t>
+          <t>CSVテンプレート</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>King of Time／ジョブカン／新規作成</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr"/>
+          <t>従業員設定CSVテンプレート／給与設定CSVテンプレート</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>画面右上からダウンロード。Excelで開いても文字化けいたしません</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>データ種類</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映されます</t>
-        </is>
-      </c>
+          <t>King of Time／ジョブカン／新規作成</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
+          <t>保存済みの列の対応づけ</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>先頭に説明行があるCSVに対応</t>
+          <t>選択すると取込列設定に自動反映されます</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>CSV列とラクミー項目の対応</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>📸 取り込み列設定｜CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>記法</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>セミコロン区切り</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>店舗名:金額 をセミコロン区切り</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>従業員を登録する</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員一覧｜右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の右上「従業員登録」から、1名ずつご登録いただけます。入力後「登録」を押すと従業員一覧に戻り、新しい行が追加されます。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>従業員の氏名</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>勤怠データとの突合に使用するコード</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>必須。既存と重複する場合は登録できません</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>所属店舗</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>主に勤務する店舗</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>必須。1店舗のみ。人件費の計上先になります</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>応援に行く店舗</t>
+          <t>従業員の氏名</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>雇用区分</t>
+          <t>従業員コード</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイト</t>
+          <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>必須。既存と重複する場合は登録できません</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>給与単位・単位給与額</t>
+          <t>所属店舗</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>月給／時給と金額</t>
+          <t>主に勤務する店舗</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>必須</t>
+          <t>必須。1店舗のみ。人件費の計上先になります</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>交通費単位・単位交通費</t>
+          <t>ヘルプ先店舗</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>日額／月額と金額</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr"/>
+          <t>応援に行く店舗</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>雇用区分</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>応援先ごとの交通費</t>
+          <t>正社員／パート／アルバイト</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
+          <t>必須</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>所定労働時間</t>
+          <t>給与単位・単位給与額</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>月あたりの所定労働時間</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr"/>
+          <t>月給／時給と金額</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>みなし残業時間</t>
+          <t>交通費単位・単位交通費</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>月あたりのみなし残業時間</t>
+          <t>日額／月額と金額</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr"/>
@@ -990,2010 +1035,2444 @@
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>応援先ごとの交通費</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>所定労働時間</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>月あたりの所定労働時間</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>みなし残業時間</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>月あたりのみなし残業時間</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>この内容が有効となる日付</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員登録画面｜ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>※ 必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>従業員の設定を変更する</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>保存後</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>「従業員設定」→ 修正 →「更新保存」</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績に戻り、数字が再計算されます</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>保存したときの動きは、適用日付によって変わります。</t>
+          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>適用日付</t>
+          <t>入口</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>保存時の動作</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>設定変更履歴</t>
+          <t>保存後</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>未来日</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
+          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>「予約中」で追加</t>
+          <t>従業員一覧に戻ります</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>「従業員設定」→ 修正 →「更新保存」</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績に戻り、数字が再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>保存したときの動きは、適用日付によって変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>設定変更履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>「予約中」で追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
           <t>当日・過去日</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>「適用中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>締め済み期間内</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>警告を表示し、反映されません</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>追加されません</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>毎月の人件費を確定する</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>操作する場所</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>勤怠実績を取り込む</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>人件費実績 →「実績データ取込」</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>月次の人件費を確認する</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>人件費実績（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>数字が合わない場合は原因を調べる</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>「数字が合わないとき」をご覧ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>各金額は次のとおり算出しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>総労働時間</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>勤怠実績の実働時間の合計</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>みなし労働時間差分</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>深夜残業代</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="10" t="n"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>各金額は次のとおり算出しております。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>給与（実績給与）</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>想定給与（概算給与）</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>総労働時間</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>みなし労働時間差分</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>総支給額</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr"/>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>時間外1.25＋深夜0.25の割増</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>給与（実績給与）</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>交通費は含みません</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗労働時間</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>締め前</t>
+          <t>交通費</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>締め後</t>
+          <t>総支給額</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr"/>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>締め解除後</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>締め前</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>締め後</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>前回の取込との差を表示</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>読み込み</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>取込を実行</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>進捗を表示します</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>開き方</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>設定取込データ</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>対象とデータ項目を選ぶ</t>
+          <t>従業員設定／給与設定</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="10" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>エクスポート種別（設定／実績）を選ぶ</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>対象とデータ項目を選ぶ</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>「出力」でCSVを取得する</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="10" t="n"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>データ項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="26" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>ケース別</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>従業員設定</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>CSVの列名がラクミーと違うとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>ケース別</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
-        </is>
-      </c>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="10" t="n"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="10" t="n"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="10" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>編集・削除</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>マッピングテンプレートファイル</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>扱い</t>
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="139" ht="18" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="10" t="n"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>全社の合計</t>
-        </is>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
+        <is>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B146" s="7" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>絞り込み</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="28" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="28" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
         </is>
       </c>
     </row>
     <row r="155" ht="18" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>全社の合計</t>
         </is>
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="28" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="26" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="10" t="n"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>エラーの内容</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="161" ht="18" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="162" ht="18" customHeight="1">
       <c r="A162" s="7" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="163" ht="18" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
         </is>
       </c>
     </row>
     <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="28" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="10" t="n"/>
+    </row>
+    <row r="165" ht="28" customHeight="1">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="28" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="7" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="28" customHeight="1">
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="28" customHeight="1">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="28" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t>締めたあとに数字を直したい</t>
-        </is>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="28" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="26" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
       <c r="A176" s="7" t="inlineStr">
         <is>
-          <t>日別実績で概算が選べない</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="177" ht="18" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="28" customHeight="1">
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="18" customHeight="1">
       <c r="A178" s="7" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C182" s="7" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績の閲覧</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C183" s="7" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
       <c r="A184" s="7" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C184" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="186" ht="28" customHeight="1">
-      <c r="A186" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>必須項目の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>この機能でできないこと</t>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1">
+          <t>回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="28" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="18" customHeight="1">
+          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="28" customHeight="1">
       <c r="A190" s="7" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="191" ht="18" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>日別実績で概算が選べない</t>
         </is>
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="192" ht="18" customHeight="1">
       <c r="A192" s="7" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="28" customHeight="1">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B196" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>店長</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="198" ht="18" customHeight="1">
       <c r="A198" s="7" t="inlineStr">
         <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="16" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B213" s="7" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A193:C193"/>
+  <mergeCells count="80">
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A208:C208"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A156:C156"/>
+    <mergeCell ref="A165:C165"/>
+    <mergeCell ref="A173:C173"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A148:C148"/>
+    <mergeCell ref="A157:C157"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A174:C174"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A158:C158"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A179:C179"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A151:C151"/>
-    <mergeCell ref="A185:C185"/>
-    <mergeCell ref="A85:C85"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A194:C194"/>
     <mergeCell ref="A159:C159"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A180:C180"/>
-    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A200:C200"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A209:C209"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A167:C167"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A186:C186"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A201:C201"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A158:C158"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A195:C195"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A166:C166"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A172:C172"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A103:C103"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ヘルプページ 撮影が必要なスクリーンショット（15点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>撮影の指示</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>設定インポート画面</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>従業員登録画面</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績（月別実績・実績モード）</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>締めの確認画面</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>前回差分表示</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート画面</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>予約完了時のメッセージ</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」の表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>設定変更履歴</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3009,7 +3488,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ヘルプページ 掲載前チェック（社内用・顧客には出しません）</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -41,14 +41,14 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11.5"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <i val="1"/>
@@ -167,20 +167,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -579,2626 +579,2682 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>目次</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
           <t>操作手順</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>はじめて設定する／従業員を登録する／従業員の設定を変更する／毎月の人件費を確定する／取り込んだ元データを確認する／データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>ケース別</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する／CSVの列名がラクミーと違うとき／数字が合わないとき／応援（ヘルプ）勤務がある場合／締めたあとに給与改定が決まったとき／すでにご利用中のお客様</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります／設定が保存できません／数字・締めについて／どなたが操作できますか／この機能でできないこと／解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>はじめて設定する</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>導入時に1回だけ行う作業です。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>操作する場所</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>店舗マスタを登録する</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>店舗の管理画面（従業員管理の対象外です）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>従業員の設定をCSVで一括登録する</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ内容を確認する</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>不足分を1名ずつ登録する</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧 →「従業員登録」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>📸 設定インポート画面｜データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>設定インポートでは次の内容を指定いただけます。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>従業員の設定をCSVで一括登録する</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ内容を確認する</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>不足分を1名ずつ登録する</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧 →「従業員登録」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>📸 設定インポート画面｜データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>設定インポートでは次の内容を指定いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>CSVテンプレート</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>従業員設定CSVテンプレート／給与設定CSVテンプレート</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>画面右上からダウンロード。Excelで開いても文字化けいたしません</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>データ種類</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>King of Time／ジョブカン／新規作成</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>列マッピングテンプレート</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>保存済みの列の対応づけ</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>選択すると取込列設定に自動反映されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>CSV位置合わせ設定</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>ヘッダー行／データ開始行／開始列</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>先頭に説明行があるCSVに対応</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>取り込み列設定</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>CSV列とラクミー項目の対応</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>「全解除」で取込チェックを一括解除</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>📸 取り込み列設定｜CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CSVの記法は次のとおりです。</t>
-        </is>
-      </c>
+      <c r="C21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>保存済みの列の対応づけ</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>選択すると取込列設定に自動反映されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>CSV位置合わせ設定</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>ヘッダー行／データ開始行／開始列</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>先頭に説明行があるCSVに対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>取り込み列設定</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>CSV列とラクミー項目の対応</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>「全解除」で取込チェックを一括解除</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>📸 取り込み列設定｜CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CSVの記法は次のとおりです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>記法</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>セミコロン区切り</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>店舗名:金額 をセミコロン区切り</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>従業員を登録する</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>📸 従業員一覧｜右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の右上「従業員登録」から、1名ずつご登録いただけます。入力後「登録」を押すと従業員一覧に戻り、新しい行が追加されます。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>必須。既存と重複する場合は登録できません</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>必須。1店舗のみ。人件費の計上先になります</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>給与単位・単位給与額</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>月給／時給と金額</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>交通費単位・単位交通費</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>日額／月額と金額</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>応援先ごとの交通費</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>所定労働時間</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>月あたりの所定労働時間</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>みなし残業時間</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>月あたりのみなし残業時間</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>この内容が有効となる日付</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>📸 従業員登録画面｜ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
         </is>
       </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>※ 必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>従業員の設定を変更する</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>保存後</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>従業員一覧に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>「従業員設定」→ 修正 →「更新保存」</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績に戻り、数字が再計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="10" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>入口</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>保存後</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧に戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>「従業員設定」→ 修正 →「更新保存」</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績に戻り、数字が再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>保存したときの動きは、適用日付によって変わります。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>保存時の動作</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>設定変更履歴</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>未来日</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>「予約中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>当日・過去日</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>「適用中」で追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>締め済み期間内</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>警告を表示し、反映されません</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>追加されません</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>毎月の人件費を確定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
+          <t>締め済み期間内</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>警告を表示し、反映されません</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>追加されません</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>毎月、同じ順序で行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>操作する場所</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>勤怠実績を取り込む</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>人件費実績 →「実績データ取込」</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>月次の人件費を確認する</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>人件費実績（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>数字が合わない場合は原因を調べる</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>「数字が合わないとき」をご覧ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="n"/>
-      <c r="C66" s="10" t="n"/>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>各金額は次のとおり算出しております。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>月を締めて数字を確定する</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「締め」</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="10" t="n"/>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>各金額は次のとおり算出しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>算出方法</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>基礎時給</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>想定給与（概算給与）</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>総労働時間</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>みなし労働時間差分</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>深夜残業代</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>給与（実績給与）</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>交通費は含みません</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>所属店舗労働時間</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>ヘルプ時間</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>日別実績の合計</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>ヘルプ人件費</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>応援先店舗に計上し、所属店舗から差し引きます</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>交通費</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>給与とは別の費目</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>総支給額</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
+          <t>交通費</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>給与とは別の費目</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>総支給額</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>給与設定を過去日で変更</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>締め前</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>締め後</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>締め解除後</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="8" t="inlineStr">
         <is>
           <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="10" t="n"/>
-    </row>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>取り込んだ元データを確認する</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>前回の取込との差を表示</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>読み込み</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>取込を実行</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>進捗を表示します</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>開き方</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>設定取込データ</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>従業員設定／給与設定</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="8" t="inlineStr">
-        <is>
-          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="n"/>
-      <c r="C100" s="10" t="n"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="10" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>エクスポート種別（設定／実績）を選ぶ</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>対象とデータ項目を選ぶ</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>「出力」でCSVを取得する</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr"/>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n"/>
-      <c r="C108" s="10" t="n"/>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="10" t="n"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>データ項目</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>給与設定</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="26" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="119" ht="26" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="n"/>
-      <c r="C121" s="10" t="n"/>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
-        <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="10" t="n"/>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
       <c r="B126" s="9" t="n"/>
       <c r="C126" s="10" t="n"/>
     </row>
     <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="10" t="n"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="10" t="n"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C132" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="7" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>テンプレート登録</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>編集・削除</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>保存済みテンプレートの変更</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C130" s="7" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="28" customHeight="1">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1">
       <c r="A135" s="6" t="inlineStr">
         <is>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>確認する内容</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>確認する場所</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C137" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C138" s="7" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C139" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
-        <is>
-          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
-        </is>
-      </c>
-      <c r="B140" s="9" t="n"/>
-      <c r="C140" s="10" t="n"/>
-    </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="A142" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="10" t="n"/>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>変更反映日時</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>編集日時</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="6" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="28" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>変更ソース</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>絞り込み</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="B156" s="5" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="6" t="inlineStr">
         <is>
           <t>ヘルプ時間</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B157" s="6" t="inlineStr">
         <is>
           <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>ヘルプ人件費</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B158" s="6" t="inlineStr">
         <is>
           <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="18" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>全社の合計</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="n"/>
-      <c r="C156" s="10" t="n"/>
-    </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="16" customHeight="1">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
       <c r="A160" s="6" t="inlineStr">
         <is>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="10" t="n"/>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="B165" s="5" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B161" s="7" t="inlineStr">
+      <c r="B166" s="6" t="inlineStr">
         <is>
           <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="7" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="n"/>
-      <c r="C164" s="10" t="n"/>
-    </row>
-    <row r="165" ht="28" customHeight="1">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="18" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="10" t="n"/>
+    </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B173" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="28" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>過去の月の人件費</t>
         </is>
       </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="18" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>設定の入力</t>
-        </is>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="28" customHeight="1">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="26" customHeight="1">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="28" customHeight="1">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="26" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
           <t>エラーの内容</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="B180" s="5" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="7" t="inlineStr">
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>従業員コードが空</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="6" t="inlineStr">
         <is>
           <t>従業員コードが重複</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>同じコードの従業員は登録できません。コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="18" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t>金額がマイナス・数字以外</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="18" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="28" customHeight="1">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B189" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="6" t="inlineStr">
         <is>
           <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="28" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
+    <row r="191" ht="28" customHeight="1">
+      <c r="A191" s="6" t="inlineStr">
         <is>
           <t>必須項目の警告が表示される</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="B191" s="6" t="inlineStr">
         <is>
           <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
+    <row r="192" ht="22" customHeight="1">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>数字・締めについて</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="6" t="inlineStr">
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="5" t="inlineStr">
         <is>
           <t>ご質問</t>
         </is>
       </c>
-      <c r="B188" s="6" t="inlineStr">
+      <c r="B193" s="5" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
+    <row r="194" ht="28" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>実績の金額が表示されない</t>
         </is>
       </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="28" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
+    <row r="195" ht="28" customHeight="1">
+      <c r="A195" s="6" t="inlineStr">
         <is>
           <t>締めたあとに数字を直したい</t>
         </is>
       </c>
-      <c r="B190" s="7" t="inlineStr">
+      <c r="B195" s="6" t="inlineStr">
         <is>
           <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t>日別実績で概算が選べない</t>
-        </is>
-      </c>
-      <c r="B191" s="7" t="inlineStr">
-        <is>
-          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="18" customHeight="1">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>店舗別の合計が全社と合わない</t>
-        </is>
-      </c>
-      <c r="B192" s="7" t="inlineStr">
-        <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="28" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>給与のみ変更したい</t>
-        </is>
-      </c>
-      <c r="B193" s="7" t="inlineStr">
-        <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
+          <t>日別実績で概算が選べない</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="28" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="B201" s="5" t="inlineStr">
         <is>
           <t>オーナー・本部管理</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
+      <c r="C201" s="5" t="inlineStr">
         <is>
           <t>店長</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="6" t="inlineStr">
         <is>
           <t>従業員一覧・設定の編集</t>
         </is>
       </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="B202" s="6" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C197" s="7" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr">
         <is>
           <t>権限設定によります</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
-        <is>
-          <t>人件費実績の閲覧</t>
-        </is>
-      </c>
-      <c r="B198" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C198" s="7" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C199" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
       <c r="A203" s="6" t="inlineStr">
         <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="28" customHeight="1">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="B203" s="6" t="inlineStr">
+      <c r="B208" s="5" t="inlineStr">
         <is>
           <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="7" t="inlineStr">
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
-      <c r="B204" s="7" t="inlineStr">
+      <c r="B209" s="6" t="inlineStr">
         <is>
           <t>給与計算ソフト（データはエクスポートで出力可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>出退勤の打刻・シフトの作成</t>
-        </is>
-      </c>
-      <c r="B205" s="7" t="inlineStr">
-        <is>
-          <t>ラクミータイムレコード</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="18" customHeight="1">
-      <c r="A206" s="7" t="inlineStr">
-        <is>
-          <t>ログインアカウントの発行・権限の設定</t>
-        </is>
-      </c>
-      <c r="B206" s="7" t="inlineStr">
-        <is>
-          <t>権限設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="18" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
-        <is>
-          <t>入退社の手続き・年末調整</t>
-        </is>
-      </c>
-      <c r="B207" s="7" t="inlineStr">
-        <is>
-          <t>本機能の対象外です</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="5" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="210" ht="18" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
           <t>お知らせいただく内容</t>
         </is>
       </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>確認場所</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="7" t="inlineStr">
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="6" t="inlineStr">
         <is>
           <t>対象の従業員コードと年月</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>従業員一覧／人件費実績</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>画面に表示されたメッセージ</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>該当画面</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="18" customHeight="1">
-      <c r="A213" s="7" t="inlineStr">
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B218" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="80">
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A208:C208"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A21:C21"/>
+  <mergeCells count="81">
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A105:C105"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A156:C156"/>
-    <mergeCell ref="A165:C165"/>
-    <mergeCell ref="A173:C173"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A148:C148"/>
-    <mergeCell ref="A157:C157"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A174:C174"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A155:C155"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A205:C205"/>
+    <mergeCell ref="A118:C118"/>
     <mergeCell ref="A120:C120"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A159:C159"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A200:C200"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A209:C209"/>
+    <mergeCell ref="A96:C96"/>
     <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A201:C201"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A146:C146"/>
+    <mergeCell ref="A172:C172"/>
     <mergeCell ref="A187:C187"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A158:C158"/>
-    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A214:C214"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A163:C163"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A213:C213"/>
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A150:C150"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A167:C167"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A182:C182"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A169:C169"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A178:C178"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A153:C153"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="A137:C137"/>
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A195:C195"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A154:C154"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A207:C207"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A87:C87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3243,225 +3299,225 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>設定インポート画面</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>従業員登録画面</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>人件費実績（月別実績・実績モード）</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>締めの確認画面</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>設定・実績エクスポート画面</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>予約完了時のメッセージ</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>設定変更履歴</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>人件費実績（日別実績）</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>締め済み期間の警告</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
@@ -3495,220 +3551,220 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>待っている判断</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>月の途中で給与が変わる場合の計算例</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>判断1＝所定労働日割</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>ヘルプ勤務の人件費の計上先</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>深夜残業代の金額</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>みなし残業を超えた/届かなかったときの扱い</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>人件費実績のモーダルから直したときの適用日付</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>実装前</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>翌月で差額を調整する条件</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>判断2（対象費目）</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>次段階可</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>「設定インポート」「設定取込データ」の画面名</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>判断3・4（名称の統一）</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>権限による違いの表</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>リリースまで</t>
         </is>
@@ -3722,119 +3778,119 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>確認すること</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>予約した変更の取り消し手順</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>実装されているか、手順は何か</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>従業員を削除したときの過去実績の扱い</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>実績が残るか、消えるか</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>締め解除の記録（誰が・いつ）</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>締め済み期間への適用時の警告表示</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>警告が出るか（モック未実装。T-D07）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>締め実行時の事前チェック</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>CSV取り込みのエラー表示</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
         </is>
@@ -3848,286 +3904,286 @@
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>撮影する状態</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>対応する検証ID</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>サイドバー</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>「従業員管理」を展開した状態（7項目）</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>右上のテンプレートDLボタンが見える状態</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>CSVをドロップし、取り込み列設定が表示された状態</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>従業員登録</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>適用日付の入力欄と設定変更履歴が見える状態</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>フィルタ（変更ソース・期間）が見える状態</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>月別実績・実績モードで内訳の列が出た状態</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>締めの確認モーダル</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>①②が選択され、データ項目カードが見える状態</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>人件費実績</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>実績データ取込中の進捗モーダル</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>前回差分表示のモーダル（前回→新規の差）</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -586,7 +586,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>項目</t>
+          <t>大項目</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -595,7 +595,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>操作手順</t>
@@ -603,11 +603,11 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>はじめて設定する／従業員を登録する／従業員の設定を変更する／毎月の人件費を確定する／取り込んだ元データを確認する／データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+          <t>導入時と毎月の運用で行う操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ケース別</t>
@@ -615,11 +615,11 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する／CSVの列名がラクミーと違うとき／数字が合わないとき／応援（ヘルプ）勤務がある場合／締めたあとに給与改定が決まったとき／すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
+          <t>個別の状況への対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
@@ -627,7 +627,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>CSVの取り込みでエラーになります／設定が保存できません／数字・締めについて／どなたが操作できますか／この機能でできないこと／解決しない場合</t>
+          <t>エラーへの対処、権限、お問い合わせ</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C218"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1173,1226 +1173,1164 @@
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>従業員の設定を変更する</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>やりたいこと</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>方法</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>入口</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>保存後</t>
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>従業員を探す</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧の1段目で絞り込みます（店舗／雇用区分／従業員名の検索）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>従業員一覧</t>
+          <t>表示するデータを切り替える</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧に戻ります</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
+          <t>従業員一覧の2段目で対象データを選びます（月／取込データ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="28" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>人件費実績</t>
+          <t>従業員を削除する</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>「従業員設定」→ 修正 →「更新保存」</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績に戻り、数字が再計算されます</t>
+          <t>従業員一覧の削除アイコン、または従業員詳細の「従業員削除」→ 確認画面で「実行」</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="10" t="n"/>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>保存したときの動きは、適用日付によって変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>設定変更履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>未来日</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>「予約中」で追加</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>※ 該当する従業員がいない場合は「データはありません。」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>※ 削除は確認画面が表示されます。「キャンセル」を押した場合は削除されません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>当日・過去日</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>「即時反映しました」と表示。その時点から反映されます</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>「適用中」で追加</t>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>入口</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>保存後</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>締め済み期間内</t>
+          <t>従業員一覧</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>警告を表示し、反映されません</t>
+          <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>追加されません</t>
+          <t>従業員一覧に戻ります</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>「従業員設定」→ 修正 →「更新保存」</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績に戻り、数字が再計算されます</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>毎月の人件費を確定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>毎月、同じ順序で行います。</t>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>保存したときの動きは、適用日付によって変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>適用日付</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>保存時の動作</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>設定変更履歴</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>操作する場所</t>
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>当日・過去日</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>勤怠実績を取り込む</t>
+          <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>人件費実績 →「実績データ取込」</t>
+          <t>「適用中」で追加</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t>締め済み期間内</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>警告を表示し、反映されません</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>追加されません</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>毎月、同じ順序で行います。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>操作する場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績を取り込む</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>月次の人件費を確認する</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>人件費実績（月別実績／日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>数字が合わない場合は原因を調べる</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>「数字が合わないとき」をご覧ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>月を締めて数字を確定する</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="n"/>
-      <c r="C71" s="10" t="n"/>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>各金額は次のとおり算出しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
+          <t>数字が合わない場合は原因を調べる</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+          <t>「数字が合わないとき」をご覧ください</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>人件費実績 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>みなし労働時間差分</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>プラスが超過、マイナスが未達</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>深夜残業代</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>給与（実績給与）</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="10" t="n"/>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>所属店舗労働時間</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>総労働時間 − ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>所属店舗で勤務した時間</t>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>給与設定を過去日で変更</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>締め前</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>締め後</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>反映されません</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>交通費</t>
+          <t>締め解除後</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>給与とは別の費目</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>総支給額</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr"/>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>締め前</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>再計算して反映</t>
+          <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="10" t="n"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>※ 1名分の実績をご覧になる場合は、従業員詳細の「給与実績」から月次・日次のタブでご確認いただけます。年・月での絞り込みが可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>人件費の計算方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績と、従業員詳細の給与実績で共通の算出方法です。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>締め後</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>反映されません</t>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>算出方法</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>締め解除後</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>想定給与（概算給与）</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>勤怠実績の実働時間の合計</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
-        <is>
-          <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="n"/>
-      <c r="C95" s="10" t="n"/>
-    </row>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>みなし労働時間差分</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>プラスが超過、マイナスが未達</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>深夜残業代</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>時間外1.25＋深夜0.25の割増</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>給与（実績給与）</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>交通費は含みません</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗労働時間</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>総労働時間 − ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>プレビュー</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>取り込む内容の一覧を表示</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>読み込む前に中身をご確認いただけます</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>読み込み</t>
+          <t>交通費</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>取込を実行</t>
+          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>進捗を表示します</t>
+          <t>給与とは別の費目</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>タブ</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>開き方</t>
-        </is>
-      </c>
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>総支給額</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 ＋ 交通費</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr"/>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定／給与設定</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>月別データ／日別データ</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
-        <is>
-          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="n"/>
-      <c r="C105" s="10" t="n"/>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>プレビュー</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>取り込む内容の一覧を表示</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>前回差分表示</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>前回の取込との差を表示</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
+          <t>取込を実行</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>進捗を表示します</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>対象とデータ項目を選ぶ</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>タブ</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>開き方</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="6" t="inlineStr">
         <is>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="10" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>エクスポート種別（設定／実績）を選ぶ</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>対象とデータ項目を選ぶ</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>「出力」でCSVを取得する</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
-      <c r="B113" s="9" t="n"/>
-      <c r="C113" s="10" t="n"/>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="10" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>データ項目</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>給与設定</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="26" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>ケース別</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="A124" s="6" t="inlineStr">
         <is>
+          <t>従業員設定</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>人件費実績・従業員設定履歴・従業員詳細の給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>出力元</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>出力される内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>絞り込み後の行のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細の給与実績</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>※ 項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="26" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>ケース別</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい金額を入力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n"/>
-      <c r="C126" s="10" t="n"/>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="10" t="n"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n"/>
-      <c r="C127" s="10" t="n"/>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="10" t="n"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n"/>
-      <c r="C131" s="10" t="n"/>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="A135" s="6" t="inlineStr">
-        <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="28" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>設定取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="18" customHeight="1">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="n"/>
-      <c r="C145" s="10" t="n"/>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
-        </is>
-      </c>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="10" t="n"/>
     </row>
     <row r="147" ht="18" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
@@ -2405,855 +2343,1069 @@
           <t>内容</t>
         </is>
       </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="18" customHeight="1">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="149" ht="18" customHeight="1">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="150" ht="18" customHeight="1">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="28" customHeight="1">
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>マッピングテンプレートファイル</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="18" customHeight="1">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>絞り込み</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B156" s="5" t="inlineStr">
-        <is>
-          <t>扱い</t>
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="18" customHeight="1">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="159" ht="18" customHeight="1">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>人件費実績（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>全社の合計</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
-        </is>
-      </c>
-      <c r="B161" s="9" t="n"/>
-      <c r="C161" s="10" t="n"/>
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+        </is>
+      </c>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="10" t="n"/>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B165" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="18" customHeight="1">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="28" customHeight="1">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="167" ht="18" customHeight="1">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>絞り込み</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="18" customHeight="1">
-      <c r="A168" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="n"/>
-      <c r="C169" s="10" t="n"/>
-    </row>
-    <row r="170" ht="28" customHeight="1">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="28" customHeight="1">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
         </is>
       </c>
     </row>
     <row r="175" ht="18" customHeight="1">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>全社の合計</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="28" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="26" customHeight="1">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="10" t="n"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="18" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>エラーの内容</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="181" ht="18" customHeight="1">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="182" ht="18" customHeight="1">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
         </is>
       </c>
     </row>
     <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>雇用区分が不正</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="28" customHeight="1">
-      <c r="A186" s="6" t="inlineStr">
-        <is>
-          <t>列がずれる</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="10" t="n"/>
+    </row>
+    <row r="185" ht="28" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="18" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="18" customHeight="1">
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="28" customHeight="1">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="190" ht="18" customHeight="1">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="28" customHeight="1">
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="18" customHeight="1">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="7" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="18" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
-        <is>
-          <t>回答</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="28" customHeight="1">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="28" customHeight="1">
-      <c r="A195" s="6" t="inlineStr">
-        <is>
-          <t>締めたあとに数字を直したい</t>
-        </is>
-      </c>
-      <c r="B195" s="6" t="inlineStr">
-        <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="26" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>日別実績で概算が選べない</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="28" customHeight="1">
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="18" customHeight="1">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="18" customHeight="1">
-      <c r="A201" s="5" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="18" customHeight="1">
-      <c r="A202" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B202" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>店舗が見つからない</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>列がずれる</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績の閲覧</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="204" ht="18" customHeight="1">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="206" ht="28" customHeight="1">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>必須項目の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>この機能でできないこと</t>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="208" ht="18" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="18" customHeight="1">
+          <t>回答</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="28" customHeight="1">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="18" customHeight="1">
+          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="28" customHeight="1">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="211" ht="18" customHeight="1">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>日別実績で概算が選べない</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="212" ht="18" customHeight="1">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="7" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="18" customHeight="1">
-      <c r="A215" s="5" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B215" s="5" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="28" customHeight="1">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B216" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>店長</t>
         </is>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
         </is>
       </c>
     </row>
     <row r="218" ht="18" customHeight="1">
       <c r="A218" s="6" t="inlineStr">
         <is>
+          <t>人件費実績の閲覧</t>
+        </is>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="28" customHeight="1">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="7" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B227" s="6" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>従業員一覧／人件費実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>従業員設定履歴</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="88">
     <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A192:C192"/>
+    <mergeCell ref="A193:C193"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A136:C136"/>
     <mergeCell ref="A105:C105"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A179:C179"/>
     <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A185:C185"/>
+    <mergeCell ref="A194:C194"/>
+    <mergeCell ref="A184:C184"/>
     <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A220:C220"/>
+    <mergeCell ref="A229:C229"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A222:C222"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A205:C205"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A133:C133"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A160:C160"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A97:C97"/>
     <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A200:C200"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A121:C121"/>
     <mergeCell ref="A161:C161"/>
     <mergeCell ref="A170:C170"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A202:C202"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A186:C186"/>
+    <mergeCell ref="A228:C228"/>
     <mergeCell ref="A146:C146"/>
-    <mergeCell ref="A172:C172"/>
     <mergeCell ref="A187:C187"/>
+    <mergeCell ref="A221:C221"/>
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A108:C108"/>
     <mergeCell ref="A214:C214"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A163:C163"/>
     <mergeCell ref="A50:C50"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A213:C213"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A206:C206"/>
+    <mergeCell ref="A141:C141"/>
+    <mergeCell ref="A135:C135"/>
     <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A199:C199"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A215:C215"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A152:C152"/>
     <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A176:C176"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A114:C114"/>
     <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A107:C107"/>
     <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A162:C162"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A164:C164"/>
+    <mergeCell ref="A177:C177"/>
+    <mergeCell ref="A90:C90"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A139:C139"/>
     <mergeCell ref="A154:C154"/>
-    <mergeCell ref="A129:C129"/>
     <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A140:C140"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A117:C117"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A143:C143"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A142:C142"/>
     <mergeCell ref="A207:C207"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A168:C168"/>
+    <mergeCell ref="A78:C78"/>
     <mergeCell ref="A87:C87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,37 +29,27 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11.5"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10.5"/>
+      <color rgb="001F883D"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <color rgb="000969DA"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -68,26 +58,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDF4FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDE7F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F1F3F5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,92 +71,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00CED4DA"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D7DE"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -547,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -555,2859 +473,2784 @@
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>従業員管理</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ラクミー経営管理システムの従業員管理画面です。従業員の給与設定を適用日付で管理し、勤怠実績と合わせて月次の人件費を確認可能です。応援に出た分は応援先の店舗に計上されるため、店舗別の損益が実際の働き方と合います。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>※ 各種設定が必要です。店舗マスタの登録後にご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>各種設定が必要です。店舗マスタの登録後にご利用ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>目次</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>大項目</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>導入時と毎月の運用で行う操作</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>個別の状況への対応</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>エラーへの対処、権限、お問い合わせ</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>操作手順</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>はじめて設定する</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>導入時に1回だけ行う作業です。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>操作する場所</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>店舗マスタを登録する</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>店舗の管理画面（従業員管理の対象外です）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>従業員の設定をCSVで一括登録する</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>設定インポート</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>取り込んだ内容を確認する</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>不足分を1名ずつ登録する</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>従業員一覧 →「従業員登録」</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>📸 設定インポート画面｜データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
+    </row>
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>設定インポートでは次の内容を指定いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>CSVテンプレート</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>従業員設定CSVテンプレート／給与設定CSVテンプレート</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>画面右上からダウンロード。Excelで開いても文字化けいたしません</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>データ種類</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>King of Time／ジョブカン／新規作成</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>保存済みの列の対応づけ</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>選択すると取込列設定に自動反映されます</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>CSV位置合わせ設定</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>ヘッダー行／データ開始行／開始列</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>先頭に説明行があるCSVに対応</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>CSV列とラクミー項目の対応</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>「全解除」で取込チェックを一括解除</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>📸 取り込み列設定｜CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="16" customHeight="1">
+    </row>
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>CSVの記法は次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>記法</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>例</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>セミコロン区切り</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>青山店;新宿店</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>店舗名:金額 をセミコロン区切り</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>青山店:700;新宿店:900</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>※ お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>※ 従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>お使いの勤怠システムのCSVをそのままご利用いただけます。列名が異なる場合は「CSVの列名がラクミーと違うとき」をご覧ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定と給与設定は別のテンプレートです。両方を登録する場合は、それぞれ取り込んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>従業員を登録する</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>📸 従業員一覧｜右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
+    </row>
+    <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の右上「従業員登録」から、1名ずつご登録いただけます。入力後「登録」を押すと従業員一覧に戻り、新しい行が追加されます。</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>従業員の氏名</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>従業員コード</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>勤怠データとの突合に使用するコード</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>必須。既存と重複する場合は登録できません</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>所属店舗</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>主に勤務する店舗</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>必須。1店舗のみ。人件費の計上先になります</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先店舗</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>応援に行く店舗</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイト</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>給与単位・単位給与額</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>月給／時給と金額</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>交通費単位・単位交通費</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>日額／月額と金額</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>応援先ごとの交通費</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択すると入力欄が自動で表示されます</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>想定労働日数</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>月あたりの想定の勤務日数</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>月給の方のみの項目です（時給の方には表示されません）。入力をおすすめします。未入力の場合は所属店舗の休業日設定から求めた営業日数を使いますが、これは店舗が営業している日数のため、週休2日の方などは実際の勤務日数と差が出ます</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>所定労働時間</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>月あたりの所定労働時間</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>みなし残業時間</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>月あたりのみなし残業時間</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>この内容が有効となる日付</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>必須。初期値は当日</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>📸 従業員登録画面｜ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="10" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>※ ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>※ 必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須となります。店舗によって距離が異なるため、個別に設定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>必須項目が未入力の場合は登録されず、画面に残ります。「キャンセル」または「一覧へ戻る」で、登録せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>従業員を探す・削除する</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>やりたいこと</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>方法</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>従業員を探す</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の1段目で絞り込みます（店舗／雇用区分／従業員名の検索）</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>表示するデータを切り替える</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の2段目で対象データを選びます（月／取込データ）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>従業員を削除する</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>従業員一覧の削除アイコン、または従業員詳細の「従業員削除」→ 確認画面で「実行」</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>※ 該当する従業員がいない場合は「データはありません。」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>※ 削除は確認画面が表示されます。「キャンセル」を押した場合は削除されません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>該当する従業員がいない場合は「データはありません。」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>削除は確認画面が表示されます。「キャンセル」を押した場合は削除されません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>従業員の設定を変更する</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>入口</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>保存後</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>詳細アイコン → 従業員詳細で修正 →「保存」</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>従業員一覧に戻ります</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>「従業員設定」→ 修正 →「更新保存」</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績に戻り、数字が再計算されます</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧に戻り、数字が再計算されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="10" t="n"/>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>保存したときの動きは、適用日付によって変わります。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>適用日付</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>保存時の動作</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>未来日</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>「予約中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="6" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>当日・過去日</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>「適用中」で追加</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>締め済み期間内</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>警告を表示し、反映されません</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>追加されません</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>※ どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>※ 「一覧へ戻る」で変更せずに戻ることも可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>保存すると、従業員詳細の「設定変更履歴」に新しい行がいちばん上に追加されます。前の設定から変わった項目には色が付きますので、意図したとおりに保存できたかをその場でご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴は直近3件を表示しております。それより前の履歴は、右上の「すべての履歴」からご確認ください（その従業員で絞り込んだ状態で開きます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>「一覧へ戻る」で変更せずに戻ることも可能です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>毎月の人件費を確定する</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>操作する場所</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>勤怠実績を取り込む</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「実績データ取込」</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧 →「実績データ取込」</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>月次の人件費を確認する</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績／日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別実績／日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>数字が合わない場合は原因を調べる</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>「数字が合わないとき」をご覧ください</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>月を締めて数字を確定する</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績 →「締め」</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧 →「締め」</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>給与計算・社労士へ渡すCSVを出力する</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="n"/>
-      <c r="C78" s="10" t="n"/>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>📸 給与実績一覧（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>📸 給与実績一覧（日別実績・概算モード）｜給与計算モードを「概算」にした状態で、注記文と当月の営業日ぶんの行が入るように撮影。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>給与設定を過去日で変更</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>締め前</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>締め後</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>反映されません</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>締め解除後</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>再計算して反映</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>※ 1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
         </is>
       </c>
-      <c r="B87" s="9" t="n"/>
-      <c r="C87" s="10" t="n"/>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>※ 1名分の実績をご覧になる場合は、従業員詳細の「給与実績」から月次・日次のタブでご確認いただけます。年・月での絞り込みが可能です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>1名分の実績は、従業員詳細の「給与実績」で直近3か月をご確認いただけます。期間を指定してご覧になる場合や、CSVで出力される場合は、同じ欄の右上「すべての実績」から従業員別 給与実績をお開きください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>人件費の計算方法</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>人件費実績と、従業員詳細の給与実績で共通の算出方法です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧と、従業員詳細の給与実績で共通の算出方法です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>算出方法</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>基礎時給</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>想定給与（概算給与）</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>総労働時間</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>みなし労働時間差分</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>深夜残業代</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>給与（実績給与）</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>交通費は含みません</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="6" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代 ＋ 所属店舗の交通費 ＋ ヘルプ先の交通費</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>交通費を含みます</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>所属店舗労働時間</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>ヘルプ時間</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>日別実績の合計</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>ヘルプ人件費</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>交通費</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>月額：そのまま　／　日額：単位交通費 × 出勤日数</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>給与とは別の費目</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>総支給額</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 ＋ 交通費</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>※ 月別実績は給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認可能な見込みの数字、実績は勤怠取込後の実際の数字です。日別実績に概算モードはございません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。交通費も同じ考え方で、実際に働いた店舗に計上しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>月別実績・日別実績とも、給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認できる見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>取り込んだ元データを確認する</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>プレビュー</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
         <is>
           <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>前回の取込との差を表示</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
         <is>
           <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>読み込み</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>取込を実行</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
         <is>
           <t>進捗を表示します</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>タブ</t>
         </is>
       </c>
-      <c r="C111" s="5" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
         <is>
           <t>開き方</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>設定取込データ</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>従業員設定／給与設定</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>月別データ／日別データ</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>サイドバー、または人件費実績の「実績取込データへ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
         </is>
       </c>
-      <c r="B114" s="9" t="n"/>
-      <c r="C114" s="10" t="n"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>※ 金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>データを出力する</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="A119" s="6" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>エクスポート種別（設定／実績）を選ぶ</t>
         </is>
       </c>
-      <c r="C119" s="6" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>複数選択可</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="A120" s="6" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B120" s="6" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>対象とデータ項目を選ぶ</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>「出力」でCSVを取得する</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr"/>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
-      <c r="B122" s="9" t="n"/>
-      <c r="C122" s="10" t="n"/>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>データ項目</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>従業員設定</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>給与設定</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／通勤交通費／ヘルプ先交通費／総支給額</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>※ 種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>人件費実績・従業員設定履歴・従業員詳細の給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>出力元</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>出力される内容</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="A130" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>絞り込み後の行のみ</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細の給与実績</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>表示中のタブ（月次／日次）の内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>※ 項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="26" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="A138" s="6" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="A139" s="6" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="28" customHeight="1">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n"/>
-      <c r="C141" s="10" t="n"/>
-    </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n"/>
-      <c r="C142" s="10" t="n"/>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>※ 適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n"/>
-      <c r="C146" s="10" t="n"/>
-    </row>
-    <row r="147" ht="18" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="18" customHeight="1">
-      <c r="A148" s="6" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>テンプレート登録</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>編集・削除</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>保存済みテンプレートの変更</t>
         </is>
       </c>
-      <c r="C149" s="6" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
         <is>
           <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="18" customHeight="1">
-      <c r="A150" s="6" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>テンプレートダウンロード</t>
         </is>
       </c>
-      <c r="B150" s="6" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>マッピング表のCSVを取得</t>
         </is>
       </c>
-      <c r="C150" s="6" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
         <is>
           <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="18" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>マッピングテンプレートファイル</t>
         </is>
       </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>記入したCSVをアップロード</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
         <is>
           <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="28" customHeight="1">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>※ CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
         <is>
           <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>確認する内容</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
         <is>
           <t>確認する場所</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="18" customHeight="1">
-      <c r="A156" s="6" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B156" s="6" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>取り込んだ設定の元データ</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
         <is>
           <t>設定取込データ</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1">
-      <c r="A158" s="6" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B158" s="6" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>取り込んだ勤怠実績の元データ</t>
         </is>
       </c>
-      <c r="C158" s="6" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>実績取込データ</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="6" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B159" s="6" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>1日ごとの内訳</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="18" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
-        <is>
-          <t>📸 従業員設定履歴｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
-        </is>
-      </c>
-      <c r="B160" s="9" t="n"/>
-      <c r="C160" s="10" t="n"/>
-    </row>
-    <row r="161" ht="16" customHeight="1">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>従業員設定履歴では、変更の経緯を次の内容で確認いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="18" customHeight="1">
-      <c r="A162" s="5" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="6" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>変更反映日時</t>
         </is>
       </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="18" customHeight="1">
-      <c r="A164" s="6" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>編集日時</t>
         </is>
       </c>
-      <c r="B164" s="6" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="B165" s="6" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="28" customHeight="1">
-      <c r="A166" s="6" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>変更ソース</t>
         </is>
       </c>
-      <c r="B166" s="6" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="18" customHeight="1">
-      <c r="A167" s="6" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>絞り込み</t>
         </is>
       </c>
-      <c r="B167" s="6" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="28" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>※ まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="18" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="18" customHeight="1">
-      <c r="A172" s="6" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>ヘルプ時間</t>
         </is>
       </c>
-      <c r="B172" s="6" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="6" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>ヘルプ人件費</t>
         </is>
       </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>実績給与 × ヘルプ時間 ÷ 総労働時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="18" customHeight="1">
-      <c r="A174" s="6" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>応援先ごとに個別に設定します。店舗によって距離が異なるためです</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="18" customHeight="1">
-      <c r="A175" s="6" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>全社の合計</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="18" customHeight="1">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>📸 人件費実績（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
-        </is>
-      </c>
-      <c r="B176" s="9" t="n"/>
-      <c r="C176" s="10" t="n"/>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>※ 店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="18" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B180" s="5" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B181" s="6" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="18" customHeight="1">
-      <c r="A182" s="6" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B182" s="6" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="18" customHeight="1">
-      <c r="A183" s="6" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B183" s="6" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="18" customHeight="1">
-      <c r="A184" s="8" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
-      <c r="B184" s="9" t="n"/>
-      <c r="C184" s="10" t="n"/>
-    </row>
-    <row r="185" ht="28" customHeight="1">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="18" customHeight="1">
-      <c r="A188" s="5" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>タイトル</t>
         </is>
       </c>
-      <c r="B188" s="5" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="6" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>過去の月の人件費</t>
         </is>
       </c>
-      <c r="B189" s="6" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="18" customHeight="1">
-      <c r="A190" s="6" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>設定の入力</t>
         </is>
       </c>
-      <c r="B190" s="6" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="18" customHeight="1">
-      <c r="A191" s="6" t="inlineStr">
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
         <is>
           <t>変更履歴</t>
         </is>
       </c>
-      <c r="B191" s="6" t="inlineStr">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="6" t="inlineStr">
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
         <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B192" s="6" t="inlineStr">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="26" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="18" customHeight="1">
-      <c r="A195" s="5" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>エラーの内容</t>
         </is>
       </c>
-      <c r="B195" s="5" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="6" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>従業員コードが空</t>
         </is>
       </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="18" customHeight="1">
-      <c r="A197" s="6" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>従業員コードが重複</t>
         </is>
       </c>
-      <c r="B197" s="6" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="18" customHeight="1">
-      <c r="A198" s="6" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>金額がマイナス・数字以外</t>
         </is>
       </c>
-      <c r="B198" s="6" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="18" customHeight="1">
-      <c r="A199" s="6" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>店舗が見つからない</t>
         </is>
       </c>
-      <c r="B199" s="6" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="18" customHeight="1">
-      <c r="A200" s="6" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>雇用区分が不正</t>
         </is>
       </c>
-      <c r="B200" s="6" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="6" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B201" s="6" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="7" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
         <is>
           <t>設定が保存できません</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="18" customHeight="1">
-      <c r="A203" s="5" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>状況</t>
         </is>
       </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>対処</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="18" customHeight="1">
-      <c r="A204" s="6" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
-      <c r="B204" s="6" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="18" customHeight="1">
-      <c r="A205" s="6" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
-      <c r="B205" s="6" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="28" customHeight="1">
-      <c r="A206" s="6" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>必須項目の警告が表示される</t>
         </is>
       </c>
-      <c r="B206" s="6" t="inlineStr">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t>数字・締めについて</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="18" customHeight="1">
-      <c r="A208" s="5" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>ご質問</t>
         </is>
       </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>回答</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="28" customHeight="1">
-      <c r="A209" s="6" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>実績の金額が表示されない</t>
         </is>
       </c>
-      <c r="B209" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。人件費実績の「実績データ取込」を実行してください</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="28" customHeight="1">
-      <c r="A210" s="6" t="inlineStr">
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>締めたあとに数字を直したい</t>
         </is>
       </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="18" customHeight="1">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>日別実績で概算が選べない</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>日別実績に概算モードはございません。概算は月別実績のみでご確認いただけます</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="18" customHeight="1">
-      <c r="A212" s="6" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="28" customHeight="1">
-      <c r="A213" s="6" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>給与のみ変更したい</t>
         </is>
       </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="22" customHeight="1">
-      <c r="A214" s="7" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="2" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="18" customHeight="1">
-      <c r="A216" s="5" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>オーナー・本部管理</t>
         </is>
       </c>
-      <c r="C216" s="5" t="inlineStr">
+      <c r="C221" s="2" t="inlineStr">
         <is>
           <t>店長</t>
         </is>
       </c>
-    </row>
-    <row r="217" ht="18" customHeight="1">
-      <c r="A217" s="6" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>従業員一覧・設定の編集</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>権限設定によります</t>
         </is>
       </c>
-    </row>
-    <row r="218" ht="18" customHeight="1">
-      <c r="A218" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績の閲覧</t>
-        </is>
-      </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C223" s="2" t="inlineStr">
         <is>
           <t>今回のリリースでは対象外</t>
         </is>
       </c>
-    </row>
-    <row r="219" ht="18" customHeight="1">
-      <c r="A219" s="6" t="inlineStr">
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>月次の締め・締め解除</t>
         </is>
       </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C224" s="2" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-    </row>
-    <row r="220" ht="18" customHeight="1">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>※ 締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="28" customHeight="1">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>※ 人件費実績は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="22" customHeight="1">
-      <c r="A222" s="7" t="inlineStr">
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
         <is>
           <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="18" customHeight="1">
-      <c r="A223" s="5" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="B223" s="5" t="inlineStr">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="18" customHeight="1">
-      <c r="A224" s="6" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
-      <c r="B224" s="6" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="18" customHeight="1">
-      <c r="A225" s="6" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
-      <c r="B225" s="6" t="inlineStr">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="18" customHeight="1">
-      <c r="A226" s="6" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
-      <c r="B226" s="6" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>権限設定</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="18" customHeight="1">
-      <c r="A227" s="6" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B227" s="6" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="7" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>解決しない場合</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="16" customHeight="1">
-      <c r="A229" s="2" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="18" customHeight="1">
-      <c r="A230" s="5" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>お知らせいただく内容</t>
         </is>
       </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>確認場所</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="18" customHeight="1">
-      <c r="A231" s="6" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>対象の従業員コードと年月</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
-        <is>
-          <t>従業員一覧／人件費実績</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="18" customHeight="1">
-      <c r="A232" s="6" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>画面に表示されたメッセージ</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>該当画面</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="18" customHeight="1">
-      <c r="A233" s="6" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="88">
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A193:C193"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A179:C179"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A185:C185"/>
-    <mergeCell ref="A194:C194"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A220:C220"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A222:C222"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A160:C160"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A202:C202"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A186:C186"/>
-    <mergeCell ref="A228:C228"/>
-    <mergeCell ref="A146:C146"/>
-    <mergeCell ref="A187:C187"/>
-    <mergeCell ref="A221:C221"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A214:C214"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A141:C141"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A215:C215"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="A176:C176"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A169:C169"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A153:C153"/>
-    <mergeCell ref="A177:C177"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A154:C154"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A143:C143"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A142:C142"/>
-    <mergeCell ref="A207:C207"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A168:C168"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A87:C87"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3418,7 +3261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3427,249 +3270,264 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>ヘルプページ 撮影が必要なスクリーンショット（15点）</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ヘルプページ 撮影が必要なスクリーンショット（16点）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>撮影の指示</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="6" t="n">
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>設定インポート画面</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>データ種類・列マッピングテンプレート・CSV位置合わせ設定・取り込み列設定が1画面に収まる状態で撮影。ファイルをドラッグする領域も入れてください。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="n">
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>取り込み列設定</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>CSVの列とラクミーの項目が並んで対応づいている部分を拡大。「全解除」ボタンも入れてください。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="n">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>従業員一覧</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>右上の「従業員登録」「設定インポート」「設定・実績エクスポート」が見える状態で全体を撮影。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="n">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>従業員登録画面</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ヘルプ先店舗を2店舗選択し、ヘルプ先交通費の入力欄が自動表示された状態。適用日付の欄まで入れてください。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>従業員詳細</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="n">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（月別実績・実績モード）</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（月別実績・実績モード）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績・概算モード）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>給与計算モードを「概算」にした状態で、注記文と当月の営業日ぶんの行が入るように撮影。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>締めの確認画面</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>前回差分表示</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>設定・実績エクスポート画面</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>予約完了時のメッセージ</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績（日別実績）</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>締め済み期間の警告</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
@@ -3686,731 +3544,421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ヘルプページ 掲載前チェック（社内用・顧客には出しません）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>待っている判断</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>月の途中で給与が変わる場合の計算例</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>判断1＝所定労働日割</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>ヘルプ勤務の人件費の計上先</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>判断5＝振替（応援先に加算し所属店舗から差引）</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>交通費が人件費に含まれるか</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>判断6＝独立費目（通勤は所属店舗・応援先ぶんは応援先）</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>✅ 2026-08-03 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>深夜残業代の金額</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>判断7（割増率。暫定で基礎時給×1.5を適用）</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>実装前</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>みなし残業を超えた/届かなかったときの扱い</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>判断8（超過は×1.25、未達は減額なし を暫定適用）</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>実装前</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績のモーダルから直したときの適用日付</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>判断10（設定編集の入口を2つ残すか。記録は共通にする）</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>実装前</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>判断7＝割増率</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-07 確定・本文へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>みなし残業を超えた／届かなかったときの扱い</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>判断8＝超過は×1.25・未達は減額なし</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-07 確定・本文へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧のモーダルから直したときの適用日付</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>判断10＝設定編集の入口を2つ残すか</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-07 確定・本文へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>日次の想定給与と概算の日別</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>判断20＝想定労働日数の出所</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-13 確定・本文へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>日別の概算モードの説明</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>判断21＝概算の日別は営業日でならす</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>✅ 2026-08-13 確定・本文へ反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>翌月で差額を調整する条件</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>判断2（対象費目）</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>次段階可</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>判断2＝対象費目</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>❌ 未確定（この箇所は書けません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>「設定インポート」「設定取込データ」の画面名</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>判断3・4（名称の統一）</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>リリースまで</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>権限による違いの表</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>権限設定機能（rakmy_server#4750）のリリース範囲</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>リリースまで</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>判断3＝名称の統一</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>❌ 未確定（この箇所は書けません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>画面間のリンク名</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>判断4＝J-03と同時に決定</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>❌ 未確定（この箇所は書けません）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>実装確認が必要な箇所</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>箇所</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>確認すること</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>予約した変更の取り消し手順</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>実装されているか、手順は何か</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>従業員を削除したときの過去実績の扱い</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>実績が残るか、消えるか</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>締め解除の記録（誰が・いつ）</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>記録が残るか（検証プラン T-S05 の所見を参照）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>締め済み期間への適用時の警告表示</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>警告が出るか（モック未実装。T-D07）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>締め実行時の事前チェック</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>設定が未入力の従業員がいるときに警告が出るか（T-S03の所見・次段階）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>CSV取り込みのエラー表示</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>行単位でエラーになるか、全体が拒否されるか（T-I05）</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>撮影が必要なスクリーンショット（12枚）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>撮影する状態</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>対応する検証ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>サイドバー</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>「従業員管理」を展開した状態（7項目）</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>T-Z04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>右上のテンプレートDLボタンが見える状態</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>T-I02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>設定インポート</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>CSVをドロップし、取り込み列設定が表示された状態</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>T-I03</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>従業員登録</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>入力済み・ヘルプ先交通費の欄が出ている状態</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>T-R04</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>適用日付の入力欄と設定変更履歴が見える状態</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>T-D01</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>従業員設定履歴</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>フィルタ（変更ソース・期間）が見える状態</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>T-H04</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>月別実績・実績モードで内訳の列が出た状態</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>T-A02</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>締めの確認モーダル</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>T-S03</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>従業員詳細</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>締め済み期間への適用を試したときの警告（⚠️実装確認が必要）</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>T-D07</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>設定・実績エクスポート</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>①②が選択され、データ項目カードが見える状態</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>T-E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>人件費実績</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>実績データ取込中の進捗モーダル</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>T-A08</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>実績取込データ</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>前回差分表示のモーダル（前回→新規の差）</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>T-N02</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>※ 撮影は実装完了後の画面で行ってください。 モックの画面をそのまま掲載すると、実装との差異が顧客に見えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>撮影</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>撮影が必要なスクリーンショットは「撮影一覧」シート（16点）を見てください。本文の 📸 から自動で作っているため、本文と必ず一致します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>撮影は実装完了後の画面で行ってください。モックの画面をそのまま掲載すると、実装との差異が顧客に見えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>掲載の可否</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>判断1・5・6が確定し（2026-08-03）、人件費の説明を本文に反映しました。 残る掲載条件は次の2つです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>1. 判断7・8の確認（深夜残業の割増率／みなし残業の超過・未達の扱い）— 法定に沿った暫定値を適用しています</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2. 実装状況の確認と画面の撮影（未実装の機能を説明したまま公開しない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>- 判断7・8の確認 → 8/7 第1回ジャッジ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>- M4（ヘルプページ作成）→ 8/12〜8/13</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>- リリース Go/No-Go 判定 → 8/14</t>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>未確定の判断が 3件 残っています：J-02 翌月で差額を調整する条件／J-03 「設定インポート」「設定取込データ」の画面名／J-04 画面間のリンク名</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>加えて、実装状況の確認と画面の撮影が終わるまで公開しないでください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A36:D36"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D238"/>
+  <dimension ref="A1:D240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1785,1310 +1785,1276 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
+          <t>概算モードでは、勤怠実績が無くても分かる項目だけを表示します。給与・給与実績差分・ヘルプ人件費・深夜残業代などは実績モードでご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+          <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>読み込む前に中身をご確認いただけます</t>
+          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>読み込み</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>取込を実行</t>
+          <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>進捗を表示します</t>
+          <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>タブ</t>
+          <t>前回の取込との差を表示</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>開き方</t>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
+          <t>取込を実行</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
+          <t>進捗を表示します</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
+          <t>タブ</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
+          <t>開き方</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+          <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>対象とデータ項目を選ぶ</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>「出力」でCSVを取得する</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr"/>
+          <t>エクスポート種別（設定／実績）を選ぶ</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>対象とデータ項目を選ぶ</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>データ項目</t>
-        </is>
-      </c>
+          <t>「出力」でCSVを取得する</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>給与設定</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+          <t>データ項目</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>従業員設定</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>出力元</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>出力される内容</t>
+          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>出力元</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>絞り込み後の行のみ</t>
+          <t>出力される内容</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>従業員別 給与実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>絞り込み後の行のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
           <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
+          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>CSV最大10MB</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴一覧</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>確認する内容</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>取り込んだ設定の元データ</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="3" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -3098,7 +3064,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -3110,141 +3076,185 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D240"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>月給の方のみの項目です（時給の方には表示されません）。入力をおすすめします。未入力の場合は所属店舗の休業日設定から求めた営業日数を使いますが、これは店舗が営業している日数のため、週休2日の方などは実際の勤務日数と差が出ます</t>
+          <t>ご入力をおすすめします。日次の想定給与と、日額の交通費を月額に換算するのに使います。未入力の場合は所属店舗の休業日設定から求めた営業日数を使いますが、これは店舗が営業している日数のため、週休2日の方などは実際の勤務日数と差が出ます</t>
         </is>
       </c>
     </row>
@@ -1637,155 +1637,175 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>月給者：単位給与額　／　時給者：単位給与額 × 所定労働時間</t>
+          <t>月給者：単位給与額 ＋ 所属店舗の交通費　／　時給者：単位給与額 × 所定労働時間 ＋ 所属店舗の交通費</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>交通費が日額の場合は 単位交通費 × 想定労働日数。ヘルプ先の交通費は、何日応援に行くかが事前に決まらないため含みません。月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>想定給与（日次）</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込後に反映</t>
-        </is>
-      </c>
+          <t>月次の想定給与 ÷ 想定労働日数</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>みなし労働時間差分</t>
+          <t>総労働時間</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+          <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>プラスが超過、マイナスが未達</t>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>深夜残業代</t>
+          <t>みなし労働時間差分</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>給与（実績給与）</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代 ＋ 所属店舗の交通費 ＋ ヘルプ先の交通費</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>交通費を含みます</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代 ＋ ヘルプ先の交通費</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>所属店舗の交通費は概算給与に含まれています</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>給与実績差分</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>給与 − 想定給与</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>残るのは深夜残業代・みなし超過残業代・ヘルプ人件費（ヘルプ先の交通費を含む）です。いずれも勤怠実績が出て決まります</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>所属店舗労働時間</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+          <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。交通費も同じ考え方で、実際に働いた店舗に計上しております。</t>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>月別実績・日別実績とも、給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認できる見込みの数字、実績は勤怠取込後の実際の数字です。</t>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr"/>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。交通費も同じ考え方で、実際に働いた店舗に計上しております。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>概算モードでは、勤怠実績が無くても分かる項目だけを表示します。給与・給与実績差分・ヘルプ人件費・深夜残業代などは実績モードでご確認ください。</t>
+          <t>月別実績・日別実績とも、給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認できる見込みの数字、実績は勤怠取込後の実際の数字です。</t>
         </is>
       </c>
     </row>
@@ -1795,1310 +1815,1276 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
+          <t>概算モードでは、勤怠実績が無くても分かる項目だけを表示します。給与・給与実績差分・ヘルプ人件費・深夜残業代などは実績モードでご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
+      <c r="A111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+          <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>プレビュー</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>取り込む内容の一覧を表示</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>読み込む前に中身をご確認いただけます</t>
+          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>読み込み</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>取込を実行</t>
+          <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>進捗を表示します</t>
+          <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>タブ</t>
+          <t>前回の取込との差を表示</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>開き方</t>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
+          <t>取込を実行</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
+          <t>進捗を表示します</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
+          <t>タブ</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
+          <t>開き方</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+          <t>設定取込データ</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>従業員設定／給与設定</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
+          <t>実績取込データ</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>データを出力する</t>
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
+          <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>複数選択可</t>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>対象とデータ項目を選ぶ</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>「出力」でCSVを取得する</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr"/>
+          <t>エクスポート種別（設定／実績）を選ぶ</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>複数選択可</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>対象とデータ項目を選ぶ</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>データ項目</t>
-        </is>
-      </c>
+          <t>「出力」でCSVを取得する</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>従業員設定</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>給与設定</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+          <t>データ項目</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>従業員設定</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+          <t>給与設定</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>出力元</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>出力される内容</t>
+          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>出力元</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>絞り込み後の行のみ</t>
+          <t>出力される内容</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>従業員別 給与実績</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>設定変更履歴一覧</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>絞り込み後の行のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
           <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
+          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>CSV最大10MB</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+          <t>テンプレートダウンロード</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>マッピング表のCSVを取得</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴一覧</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>確認する内容</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>取り込んだ設定の元データ</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>設定取込データ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>実績取込データ</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -3108,7 +3094,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -3120,141 +3106,185 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>ご入力をおすすめします。日次の想定給与と、日額の交通費を月額に換算するのに使います。未入力の場合は所属店舗の休業日設定から求めた営業日数を使いますが、これは店舗が営業している日数のため、週休2日の方などは実際の勤務日数と差が出ます</t>
+          <t>日次の想定給与と、日額の交通費を月額に換算するのに使います。未入力でもかまいません。その場合は薄字で表示されている既定値を使います（月給の方は所属店舗の営業日数、時給の方は 所定労働時間 ÷ 8時間 の切り上げ）。週休2日の方や、既定値と違う契約の方はご入力ください</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1654,10 +1654,14 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>月次の想定給与 ÷ 想定労働日数</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr"/>
+          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方：単位給与額 × その日の想定勤務時間 ＋ その日ぶんの交通費</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>時給の方は、その日に入る時間で1日分が変わるため、日数で割らずに時間で計算します</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>日次の想定給与と、日額の交通費を月額に換算するのに使います。未入力でもかまいません。その場合は薄字で表示されている既定値を使います（月給の方は所属店舗の営業日数、時給の方は 所定労働時間 ÷ 8時間 の切り上げ）。週休2日の方や、既定値と違う契約の方はご入力ください</t>
+          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別の想定給与は出ますが、日別は「—」になります。月給の方は未入力でも所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方：単位給与額 × その日の想定勤務時間 ＋ その日ぶんの交通費</t>
+          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方：単位給与額 ×（所定労働時間 ÷ 想定労働日数）＋ 交通費 ÷ 想定労働日数</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>時給の方は、その日に入る時間で1日分が変わるため、日数で割らずに時間で計算します</t>
+          <t>時給の方は、その日に入る時間で1日分が変わるため、時間で計算します。想定労働日数が未入力の場合は「—」になります</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別の想定給与は出ますが、日別は「—」になります。月給の方は未入力でも所属店舗の営業日数を使います</t>
+          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別は出ますが日別は「—」になります（1日に何時間お入りになるかが決まらないためです。交通費だけを表示すると実際とかけ離れた金額になってしまいます）。月給の方は未入力でも所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別は出ますが日別は「—」になります（1日に何時間お入りになるかが決まらないためです。交通費だけを表示すると実際とかけ離れた金額になってしまいます）。月給の方は未入力でも所属店舗の営業日数を使います</t>
+          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別は出ますが日別の想定給与は「—」になります（1日に何時間お入りになるかが決まらないためです。交通費だけを表示すると実際とかけ離れた金額になってしまいます）。実際にお勤めになった日の「給与」は勤怠実績から計算されるため、必ず表示されます。月給の方は未入力でも所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>時給の方はご入力をおすすめします。入力すると 1日の想定勤務時間（所定労働時間 ÷ 想定労働日数）が決まり、日別の想定給与が出ます。未入力の場合、月別は出ますが日別の想定給与は「—」になります（1日に何時間お入りになるかが決まらないためです。交通費だけを表示すると実際とかけ離れた金額になってしまいます）。実際にお勤めになった日の「給与」は勤怠実績から計算されるため、必ず表示されます。月給の方は未入力でも所属店舗の営業日数を使います</t>
+          <t>交通費が日額の方は、月あたりの交通費を求めるのに使います（単位交通費 × 想定労働日数）。月給の方は日別の想定給与にも使います。未入力の場合、月給の方は所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方：単位給与額 ×（所定労働時間 ÷ 想定労働日数）＋ 交通費 ÷ 想定労働日数</t>
+          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方は表示しません（「—」）</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>時給の方は、その日に入る時間で1日分が変わるため、時間で計算します。想定労働日数が未入力の場合は「—」になります</t>
+          <t>時給の方は、その日に何時間お入りになる予定かがシステム上決まっていないためです。月別ではご確認いただけます</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1843,7 +1843,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ・実績取込データで、取り込んだ元のデータをご確認いただけます。</t>
+          <t>設定の取込結果・実績の取込結果で、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または従業員一覧の2段目「設定取込データへ」</t>
+          <t>サイドバー、または従業員一覧の2段目「設定の取込結果」</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>実績の取込結果</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または給与実績一覧の「実績取込データへ」</t>
+          <t>サイドバー、または給与実績一覧の「実績の取込結果」</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート管理」から開きます。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>設定取込データ</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>実績取込データ</t>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定取込データで元のファイルをご確認いただけます。</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
@@ -2656,14 +2656,14 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧へ」からお進みください。絞り込みが引き継がれます。</t>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費は所属店舗分と応援先分を別の列で表示しております。</t>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する</t>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
@@ -2739,400 +2739,366 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
+      <c r="A195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="3" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>実績の金額が表示されない</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -3142,7 +3108,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -3154,141 +3120,185 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>
@@ -3802,7 +3812,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>❌ 未確定（この箇所は書けません）</t>
+          <t>✅ 2026-08-13 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3832,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>❌ 未確定（この箇所は書けません）</t>
+          <t>✅ 2026-08-13 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3852,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>❌ 未確定（この箇所は書けません）</t>
+          <t>✅ 2026-08-13 確定・本文へ反映済み</t>
         </is>
       </c>
     </row>
@@ -3991,7 +4001,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>未確定の判断が 3件 残っています：J-02 翌月で差額を調整する条件／J-03 「設定インポート」「設定取込データ」の画面名／J-04 画面間のリンク名</t>
+          <t>判断はすべて確定しています。</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>交通費が日額の方は、月あたりの交通費を求めるのに使います（単位交通費 × 想定労働日数）。月給の方は日別の想定給与にも使います。未入力の場合、月給の方は所属店舗の営業日数を使います</t>
+          <t>通常はご入力不要です。勤怠実績の打刻から、直近3か月の平均出勤日数を自動で使います。実際と違う日数で見込みたい場合だけご入力ください。打刻がまだ無い場合（導入直後・新しくご登録された方）は、月給の方は所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D244"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2192,397 +2192,383 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>適用済みの設定を直したいとき</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
+          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>順</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>できる操作</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>予約中</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>編集・削除</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>適用中</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>内容の表示のみ</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>過去</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>内容の表示のみ</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>適用済みの設定は編集・削除いただけません。すでに人件費の金額に反映されているためで、変更すると過去の数字が変わってしまいます。</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
-        </is>
-      </c>
+      <c r="A150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
+          <t>直したい場合は、従業員詳細から新しい適用日付で登録してください。履歴は積み重なる形で残ります。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>給与改定を先の日付で予約する</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
+          <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>設定の取込結果</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>実績の取込結果</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
@@ -2594,711 +2580,804 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>扱い</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>順</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>全社の合計</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr"/>
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
+      <c r="A204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>店舗別の人件費</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>雇用区分が不正</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>必須項目の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>給与のみ変更したい</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>給与実績一覧の閲覧</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧／給与実績一覧</t>
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2462,363 +2462,335 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>退職された方の登録</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>従業員一覧から外れますが、過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>設定がいつ・どの経路で変わったか</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴一覧</t>
-        </is>
-      </c>
+      <c r="A173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>設定の取込結果</t>
+          <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>実績の取込結果</t>
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>適用中／予約中／過去</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
+          <t>変更反映日時</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>編集日時</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>扱い</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>絞り込み</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費</t>
-        </is>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
-        </is>
-      </c>
+      <c r="A201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
+          <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
         </is>
       </c>
     </row>
@@ -2828,556 +2800,652 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
+      <c r="A206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>店舗別の人件費</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
+          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
-        </is>
-      </c>
+      <c r="A216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
-        </is>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>金額がマイナス・数字以外</t>
-        </is>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
-        </is>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>店舗別の人件費</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>締め済み期間の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>必須項目の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>エラーの内容</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>雇用区分が不正</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>どなたが操作できますか</t>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>ご質問</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>実績の金額が表示されない</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>締めたあとに数字を直したい</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>給与のみ変更したい</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>ログインアカウントの発行・権限の設定</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>権限設定</t>
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>本機能の対象外です</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
+          <t>給与実績一覧の閲覧</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>確認場所</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>月次の締め・締め解除</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>該当画面</t>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2123,126 +2123,121 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+          <t>給与実績一覧の「従業員設定」から設定を直す場合も、適用日付をご指定いただけます。未来の日付なら予約、当日・過去の日付なら即時反映です。従業員詳細から直した場合とまったく同じ扱いになります。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>出力元</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>出力される内容</t>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
+          <t>出力元</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+          <t>出力される内容</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>絞り込み後の行のみ</t>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>従業員別 給与実績</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+          <t>絞り込み後の行のみ</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
           <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>適用済みの設定を直したいとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>できる操作</t>
+          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>予約中</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>できる操作</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>適用中</t>
+          <t>予約中</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>内容の表示のみ</t>
+          <t>編集・削除</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>過去</t>
+          <t>適用中</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -2254,1020 +2249,1010 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>過去</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>内容の表示のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
           <t>適用済みの設定は編集・削除いただけません。すでに人件費の金額に反映されているためで、変更すると過去の数字が変わってしまいます。</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr"/>
-    </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>直したい場合は、従業員詳細から新しい適用日付で登録してください。履歴は積み重なる形で残ります。</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
           <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>CSVの列名がラクミーと違うとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>CSV最大10MB</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
           <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>退職された方の登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
           <t>従業員一覧から外れますが、過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr"/>
-    </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>確認する内容</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>設定の取込結果</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>取り込んだ設定の元データ</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>実績の取込結果</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>取り込んだ勤怠実績の元データ</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
           <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
           <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr"/>
-    </row>
     <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
-        </is>
-      </c>
+      <c r="A202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
+          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
           <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr"/>
-    </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr"/>
-    </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
         <is>
           <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
           <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr"/>
-    </row>
     <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="3" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B233" s="2" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t>設定が保存できません</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
           <t>必須項目の警告が表示される</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
           <t>給与のみ変更したい</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="4" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
         <is>
           <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -3277,7 +3262,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -3289,7 +3274,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>給与実績一覧の閲覧</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -3299,7 +3284,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -3311,141 +3296,163 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
           <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
         <is>
           <t>この機能でできないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B259" s="2" t="inlineStr">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
         <is>
           <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>対象の従業員コードと年月</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>従業員一覧／給与実績一覧</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -2123,7 +2123,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の「従業員設定」から設定を直す場合も、適用日付をご指定いただけます。未来の日付なら予約、当日・過去の日付なら即時反映です。従業員詳細から直した場合とまったく同じ扱いになります。</t>
+          <t>設定を変更できるのは従業員詳細だけです。給与実績一覧をご覧になっていて設定を直したくなった場合は、「従業員詳細」列のアイコンからお進みください。</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2123,133 +2123,128 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>設定を変更できるのは従業員詳細だけです。給与実績一覧をご覧になっていて設定を直したくなった場合は、「従業員詳細」列のアイコンからお進みください。</t>
+          <t>給与実績一覧の「従業員設定」では、設定内容をその場でご確認いただけます（変更はできません）。絞り込みの条件は残りますので、閉じればそのまま作業を続けられます。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+          <t>設定を変更できるのは従業員詳細だけです。直す場合はモーダル内の「従業員詳細」ボタンからお進みください。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>出力元</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>出力される内容</t>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
+          <t>出力元</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+          <t>出力される内容</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>絞り込み後の行のみ</t>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>従業員別 給与実績</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+          <t>絞り込み後の行のみ</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
           <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>適用済みの設定を直したいとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>できる操作</t>
+          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>予約中</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>できる操作</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>適用中</t>
+          <t>予約中</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>内容の表示のみ</t>
+          <t>編集・削除</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>過去</t>
+          <t>適用中</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -2261,1020 +2256,1010 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>過去</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>内容の表示のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
           <t>適用済みの設定は編集・削除いただけません。すでに人件費の金額に反映されているためで、変更すると過去の数字が変わってしまいます。</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr"/>
-    </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>直したい場合は、従業員詳細から新しい適用日付で登録してください。履歴は積み重なる形で残ります。</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
           <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>CSVの列名がラクミーと違うとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>CSV最大10MB</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
           <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>退職された方の登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
           <t>従業員一覧から外れますが、過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr"/>
-    </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>確認する内容</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>設定の取込結果</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>取り込んだ設定の元データ</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>実績の取込結果</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>取り込んだ勤怠実績の元データ</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
           <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t>応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
           <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr"/>
-    </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
-        <is>
-          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
-        </is>
-      </c>
+      <c r="A203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
+          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
           <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr"/>
-    </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr"/>
-    </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
         <is>
           <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
           <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr"/>
-    </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="3" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>設定が保存できません</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
           <t>必須項目の警告が表示される</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
           <t>給与のみ変更したい</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="4" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
         <is>
           <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -3284,7 +3269,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -3296,7 +3281,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>給与実績一覧の閲覧</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -3306,7 +3291,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -3318,141 +3303,163 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
           <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="4" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>この機能でできないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B260" s="2" t="inlineStr">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="4" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
         <is>
           <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>対象の従業員コードと年月</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>従業員一覧／給与実績一覧</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2490,7 +2490,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧から外れますが、過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
+          <t>従業員一覧から外れ、概算モードの見込みからも外れます（これからかかる人件費の見込みなので、退職された方は含めません）。過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
+          <t>月の途中で交通費を変更された場合、交通費は日割りいたしません。月額の方はその月は変更前の金額のまま、翌月から新しい金額になります（定期代は月単位でご購入いただくためです）。日額の方は、適用日以降にご出勤された日から新しい金額になります。</t>
         </is>
       </c>
     </row>
@@ -2910,556 +2910,576 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>同じ適用日付で2回保存された場合は、あとから保存されたほうが有効になります。前のものも設定変更履歴に残りますので、経緯をたどれます。将来の日付のご予約は何件でも登録でき、適用日付の順に反映されます。</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
+      <c r="A220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+      <c r="A222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>設定の入力</t>
-        </is>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>店舗別の人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>過去の月の人件費</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>設定の入力</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>エラーの内容</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>店舗別の人件費</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが重複</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>金額がマイナス・数字以外</t>
-        </is>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>金額がマイナス・数字以外</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>対処</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>雇用区分が不正</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>必須項目の警告が表示される</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>状況</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>締め済み期間の警告が表示される</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>締めたあとに数字を直したい</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>店舗別の合計が全社と合わない</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>給与のみ変更したい</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>給与実績一覧の閲覧</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>従業員一覧・設定の編集</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>月次の締め・締め解除</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>ログインアカウントの発行・権限の設定</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>権限設定</t>
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
+          <t>ログインアカウントの発行・権限の設定</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>確認場所</t>
+          <t>権限設定</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>入退社の手続き・年末調整</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="inlineStr">
-        <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>該当画面</t>
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D271"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1176,7 +1176,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>設定を変更する入口は2つございます。どちらからでも同じ内容を変更いただけます。入力項目は「従業員を登録する」と同じです。</t>
+          <t>設定を変更できるのは従業員詳細だけです。入力項目は「従業員を登録する」と同じです。</t>
         </is>
       </c>
     </row>
@@ -1222,1041 +1222,1036 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>「従業員設定」→ 修正 →「更新保存」</t>
+          <t>「従業員設定」で内容を確認のみ。直す場合はモーダル内の「従業員詳細」からお進みください</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧に戻り、数字が再計算されます</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
+          <t>給与実績一覧で設定を変更できないのは、確定した数字を見る画面だからです。設定は従業員詳細で、適用日付を指定してご変更ください。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>保存したときの動きは、適用日付によって変わります。</t>
+          <t>📸 従業員詳細｜基本情報と適用日付、その下の設定変更履歴が続けて見える状態。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>適用日付</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>保存時の動作</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴</t>
+          <t>保存したときの動きは、適用日付によって変わります。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>未来日</t>
+          <t>適用日付</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
+          <t>保存時の動作</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>「予約中」で追加</t>
+          <t>設定変更履歴</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>当日・過去日</t>
+          <t>未来日</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>「即時反映しました」と表示。その時点から反映されます</t>
+          <t>「◯月◯日からの適用を予約しました」と表示。当日まで反映されません</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>「適用中」で追加</t>
+          <t>「予約中」で追加</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間内</t>
+          <t>当日・過去日</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>警告を表示し、反映されません</t>
+          <t>「即時反映しました」と表示。その時点から反映されます</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>追加されません</t>
+          <t>「適用中」で追加</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
+          <t>締め済み期間内</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>警告を表示し、反映されません</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>追加されません</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>保存すると、従業員詳細の「設定変更履歴」に新しい行がいちばん上に追加されます。前の設定から変わった項目には色が付きますので、意図したとおりに保存できたかをその場でご確認いただけます。</t>
+          <t>どちらの入口から編集しても、変更は設定変更履歴に記録されます。「いつ・何を変えたか」は必ず残ります。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴は直近3件を表示しております。それより前の履歴は、右上の「すべての履歴」からご確認ください（その従業員で絞り込んだ状態で開きます）。</t>
+          <t>保存すると、従業員詳細の「設定変更履歴」に新しい行がいちばん上に追加されます。前の設定から変わった項目には色が付きますので、意図したとおりに保存できたかをその場でご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>設定変更履歴は直近3件を表示しております。それより前の履歴は、右上の「すべての履歴」からご確認ください（その従業員で絞り込んだ状態で開きます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
           <t>「一覧へ戻る」で変更せずに戻ることも可能です。</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>毎月の人件費を確定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>操作する場所</t>
+          <t>毎月、同じ順序で行います。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>勤怠実績を取り込む</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧 →「実績データ取込」</t>
+          <t>操作する場所</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>月次の人件費を確認する</t>
+          <t>勤怠実績を取り込む</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（月別実績／日別実績）</t>
+          <t>給与実績一覧 →「実績データ取込」</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>数字が合わない場合は原因を調べる</t>
+          <t>月次の人件費を確認する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>「数字が合わないとき」をご覧ください</t>
+          <t>給与実績一覧（月別実績／日別実績）</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>月を締めて数字を確定する</t>
+          <t>数字が合わない場合は原因を調べる</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧 →「締め」</t>
+          <t>「数字が合わないとき」をご覧ください</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>給与計算・社労士へ渡すCSVを出力する</t>
+          <t>月を締めて数字を確定する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート</t>
+          <t>給与実績一覧 →「締め」</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>給与計算・社労士へ渡すCSVを出力する</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>設定・実績エクスポート</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績・概算モード）｜給与計算モードを「概算」にした状態で、注記文と当月の営業日ぶんの行が入るように撮影。</t>
+          <t>📸 給与実績一覧（月別実績・実績モード）｜店舗別の行と、その合計である全社の行が両方入る状態で撮影。給与計算モードの切替も入れてください。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
+          <t>📸 給与実績一覧（日別実績・概算モード）｜給与計算モードを「概算」にした状態で、注記文と当月の営業日ぶんの行が入るように撮影。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
+          <t>実績データ取込は画面右上のボタンから実行します。取込中は進捗が表示され、完了すると実績モードの金額に反映されます。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>給与設定を過去日で変更</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>勤怠を再取込</t>
+          <t>締めは月別実績にのみ表示されます。締めの前後で、数字の動き方が変わります。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>締め前</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>給与設定を過去日で変更</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>勤怠を再取込</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>締め後</t>
+          <t>締め前</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>再計算して反映</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>反映されません</t>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>締め解除後</t>
+          <t>締め後</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>反映されません</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>再計算して反映</t>
+          <t>反映されません</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
+          <t>締め解除後</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>再計算して反映</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
+          <t>1をお済ませになるまで実績の金額は表示されません。毎月はじめに実施してください。また4で締めたあとは金額が変わりませんので、給与計算・会計へ数字をお渡しになる前に実行してください。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
+          <t>締めを実行しても画面は切り替わりません。同じ画面でボタンの表記が「締め」から「締め解除」に変わります。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>📸 締めの確認画面｜「締め後はデータの編集ができなくなります」のメッセージと、実行・キャンセルのボタン。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
           <t>1名分の実績は、従業員詳細の「給与実績」で直近3か月をご確認いただけます。期間を指定してご覧になる場合や、CSVで出力される場合は、同じ欄の右上「すべての実績」から従業員別 給与実績をお開きください。</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>人件費の計算方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>給与実績一覧と、従業員詳細の給与実績で共通の算出方法です。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>算出方法</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>給与実績一覧と、従業員詳細の給与実績で共通の算出方法です。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>基礎時給</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>単位給与額 ÷ 所定労働時間</t>
+          <t>算出方法</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>想定給与（概算給与）</t>
+          <t>基礎時給</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>月給者：単位給与額 ＋ 所属店舗の交通費　／　時給者：単位給与額 × 所定労働時間 ＋ 所属店舗の交通費</t>
+          <t>単位給与額 ÷ 所定労働時間</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>交通費が日額の場合は 単位交通費 × 想定労働日数。ヘルプ先の交通費は、何日応援に行くかが事前に決まらないため含みません。月の途中で改定した場合は所定労働日数で日割り</t>
+          <t>月給者のみ。時給者は単位給与額がそのまま基礎時給</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>想定給与（日次）</t>
+          <t>想定給与（概算給与）</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方は表示しません（「—」）</t>
+          <t>月給者：単位給与額 ＋ 所属店舗の交通費　／　時給者：単位給与額 × 所定労働時間 ＋ 所属店舗の交通費</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>時給の方は、その日に何時間お入りになる予定かがシステム上決まっていないためです。月別ではご確認いただけます</t>
+          <t>交通費が日額の場合は 単位交通費 × 想定労働日数。ヘルプ先の交通費は、何日応援に行くかが事前に決まらないため含みません。月の途中で改定した場合は所定労働日数で日割り</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>総労働時間</t>
+          <t>想定給与（日次）</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>勤怠実績の実働時間の合計</t>
+          <t>月給の方：月次の想定給与 ÷ 想定労働日数　／　時給の方は表示しません（「—」）</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込後に反映</t>
+          <t>時給の方は、その日に何時間お入りになる予定かがシステム上決まっていないためです。月別ではご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>みなし労働時間差分</t>
+          <t>総労働時間</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
+          <t>勤怠実績の実働時間の合計</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>プラスが超過、マイナスが未達</t>
+          <t>実績データ取込後に反映</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>深夜残業代</t>
+          <t>みなし労働時間差分</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>基礎時給 × 1.5 × 深夜残業時間</t>
+          <t>総労働時間 −（所定労働時間 ＋ みなし残業時間）</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>時間外1.25＋深夜0.25の割増</t>
+          <t>プラスが超過、マイナスが未達</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>給与（実績給与）</t>
+          <t>深夜残業代</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代 ＋ ヘルプ先の交通費</t>
+          <t>基礎時給 × 1.5 × 深夜残業時間</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>所属店舗の交通費は概算給与に含まれています</t>
+          <t>時間外1.25＋深夜0.25の割増</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>給与実績差分</t>
+          <t>給与（実績給与）</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>給与 − 想定給与</t>
+          <t>概算給与 ＋ 深夜残業代 ＋ みなし超過残業代 ＋ ヘルプ先の交通費</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>残るのは深夜残業代・みなし超過残業代・ヘルプ人件費（ヘルプ先の交通費を含む）です。いずれも勤怠実績が出て決まります</t>
+          <t>所属店舗の交通費は概算給与に含まれています</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>所属店舗労働時間</t>
+          <t>給与実績差分</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>総労働時間 − ヘルプ時間</t>
+          <t>給与 − 想定給与</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>所属店舗で勤務した時間</t>
+          <t>残るのは深夜残業代・みなし超過残業代・ヘルプ人件費（ヘルプ先の交通費を含む）です。いずれも勤怠実績が出て決まります</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>所属店舗労働時間</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間</t>
+          <t>総労働時間 − ヘルプ時間</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>日別実績の合計</t>
+          <t>所属店舗で勤務した時間</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>応援先店舗で勤務した時間</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
+          <t>日別実績の合計</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。交通費も同じ考え方で、実際に働いた店舗に計上しております。</t>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>応援先店舗に計上し、所属店舗から差し引きます</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>店舗別の人件費を合計すると全社の人件費と一致します。応援分は所属店舗から差し引き、応援先店舗に加算しているためです。交通費も同じ考え方で、実際に働いた店舗に計上しております。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
           <t>月別実績・日別実績とも、給与計算モード（概算／実績）で表示が切り替わります。概算は月中でも確認できる見込みの数字、実績は勤怠取込後の実際の数字です。</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr"/>
-    </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>概算モードでは、勤怠実績が無くても分かる項目だけを表示します。給与・給与実績差分・ヘルプ人件費・深夜残業代などは実績モードでご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr"/>
-    </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>日別実績の概算は、月の見込み額を当月の営業日でならした額です（月次の概算給与 ÷ 営業日数）。どなたがどの日に出勤するかは確定していないため、1日ごとの正確な額ではございません。実績モードの想定給与とは数字が異なります。</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>取り込んだ元データを確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>設定の取込結果・実績の取込結果で、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>設定の取込結果・実績の取込結果で、取り込んだ元のデータをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>プレビュー</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>取り込む内容の一覧を表示</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>読み込む前に中身をご確認いただけます</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>前回差分表示</t>
+          <t>プレビュー</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>前回の取込との差を表示</t>
+          <t>取り込む内容の一覧を表示</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
+          <t>読み込む前に中身をご確認いただけます</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>読み込み</t>
+          <t>前回差分表示</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>取込を実行</t>
+          <t>前回の取込との差を表示</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>進捗を表示します</t>
+          <t>例：単位給与額 前回320,000円 → 新規340,000円</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>画面</t>
+          <t>読み込み</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>タブ</t>
+          <t>取込を実行</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>開き方</t>
+          <t>進捗を表示します</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>設定の取込結果</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>従業員設定／給与設定</t>
+          <t>タブ</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または従業員一覧の2段目「設定の取込結果」</t>
+          <t>開き方</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>実績の取込結果</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>月別データ／日別データ</t>
+          <t>従業員設定／給与設定</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>サイドバー、または給与実績一覧の「実績の取込結果」</t>
+          <t>サイドバー、または従業員一覧の2段目「設定の取込結果」</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+          <t>実績の取込結果</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>月別データ／日別データ</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>サイドバー、または給与実績一覧の「実績の取込結果」</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>📸 前回差分表示｜「前回320,000円 → 新規340,000円」のように、変わる項目だけが並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>金額が大きく変わる場合は、取り込む前に前回差分表示でご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>データを出力する</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>給与計算ソフトや社労士へお渡しになる場合に使用します。従業員一覧の右上「設定・実績エクスポート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>エクスポート種別（設定／実績）を選ぶ</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>複数選択可</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>対象とデータ項目を選ぶ</t>
+          <t>エクスポート種別（設定／実績）を選ぶ</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>対象を2つ選択した場合は2ファイル出力</t>
+          <t>複数選択可</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>「出力」でCSVを取得する</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr"/>
+          <t>対象とデータ項目を選ぶ</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>対象を2つ選択した場合は2ファイル出力</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>「出力」でCSVを取得する</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>データ項目</t>
+          <t>📸 設定・実績エクスポート画面｜エクスポート種別と、選択したデータ項目のチェックが見える状態。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>従業員設定</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
+          <t>データ項目</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>給与設定</t>
+          <t>従業員設定</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
+          <t>従業員コード／氏名／雇用区分／所属店舗／ヘルプ先店舗／適用日付</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>給与設定</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
+          <t>従業員コード／氏名／給与単位／単位給与額／交通費単位／単位交通費／所定労働時間／みなし残業時間／適用日付</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
+          <t>実績</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>従業員コード／氏名／対象年月／雇用区分／所属店舗／概算給与／総労働時間／ヘルプ人件費／深夜残業代／実績給与／給与実績差分</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の「従業員設定」では、設定内容をその場でご確認いただけます（変更はできません）。絞り込みの条件は残りますので、閉じればそのまま作業を続けられます。</t>
+          <t>種別・対象・項目のいずれかが未選択の場合は出力できません。出力したファイルはExcelで開いても文字化けいたしません。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>設定を変更できるのは従業員詳細だけです。直す場合はモーダル内の「従業員詳細」ボタンからお進みください。</t>
+          <t>給与実績一覧の「従業員設定」では、設定内容をその場でご確認いただけます（変更はできません）。絞り込みの条件は残りますので、閉じればそのまま作業を続けられます。</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
+          <t>設定を変更できるのは従業員詳細だけです。直す場合はモーダル内の「従業員詳細」ボタンからお進みください。</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>出力元</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>出力される内容</t>
+          <t>給与実績一覧・設定変更履歴一覧・従業員別 給与実績では、画面の「CSVエクスポート」からも出力いただけます。</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧</t>
+          <t>出力元</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
+          <t>出力される内容</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>給与実績一覧</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>絞り込み後の行のみ</t>
+          <t>表示中のタブ（月別実績／日別実績）・給与計算モード・絞り込みの内容</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>従業員別 給与実績</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+          <t>絞り込み後の行のみ</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>従業員別 給与実績</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>表示中のタブ（月次／日次）・給与計算モード・指定した年月範囲の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
           <t>項目を選んで出力する場合は設定・実績エクスポート、画面で見ている内容をそのまま出す場合は各画面のCSVエクスポートをご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>ケース別</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>適用済みの設定を直したいとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>できる操作</t>
+          <t>設定変更履歴で、ステータスによってできる操作が変わります。</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>予約中</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>できる操作</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>適用中</t>
+          <t>予約中</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>内容の表示のみ</t>
+          <t>編集・削除</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>過去</t>
+          <t>適用中</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -2268,1040 +2263,1030 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>過去</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>内容の表示のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
           <t>適用済みの設定は編集・削除いただけません。すでに人件費の金額に反映されているためで、変更すると過去の数字が変わってしまいます。</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr"/>
-    </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>直したい場合は、従業員詳細から新しい適用日付で登録してください。履歴は積み重なる形で残ります。</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>給与改定を先の日付で予約する</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>改定日を待たずに、あらかじめご登録いただけます。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい金額を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
+          <t>従業員詳細で新しい金額を入力する</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に改定日（未来の日付）を指定して「保存」する</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
+          <t>「◯月◯日からの適用を予約しました」と表示され、設定変更履歴に「予約中」で追加されます。適用日を迎えるまで、従業員一覧の値と人件費の金額は変わりません。</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+          <t>📸 予約完了時のメッセージ｜「◯月◯日からの適用を予約しました」の表示。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>📸 設定変更履歴｜ステータスが「予約中」の行と「適用中」の行が並んでいる状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
           <t>適用日を迎えると、設定変更履歴のステータスが「予約中」から「適用中」に変わり、それまでの設定は「過去」になります。</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="4" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>CSVの列名がラクミーと違うとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>テンプレート登録</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
+          <t>名称・データ種類・列の対応を設定</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
+          <t>編集・削除</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>マッピング表のCSVを取得</t>
+          <t>保存済みテンプレートの変更</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>行数が多い場合に使用</t>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>記入したCSVをアップロード</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>CSV最大10MB</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>マッピングテンプレートファイル</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>記入したCSVをアップロード</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>CSV最大10MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
           <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>退職された方の登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
+          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
           <t>従業員一覧から外れ、概算モードの見込みからも外れます（これからかかる人件費の見込みなので、退職された方は含めません）。過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr"/>
-    </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>数字が合わないとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>確認する内容</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>確認する場所</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>確認する内容</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ設定の元データ</t>
+          <t>設定がいつ・どの経路で変わったか</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>設定の取込結果</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>取り込んだ勤怠実績の元データ</t>
+          <t>取り込んだ設定の元データ</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>実績の取込結果</t>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>1日ごとの内訳</t>
+          <t>取り込んだ勤怠実績の元データ</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>変更反映日時</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>設定が有効となる日付</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>変更ソース</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
           <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>ヘルプ時間</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>ヘルプ人件費</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ヘルプ先交通費</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
           <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr"/>
-    </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
-        </is>
-      </c>
+      <c r="A204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
+          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
           <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr"/>
-    </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr"/>
-    </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t>締めたあとに給与改定が決まったとき</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>従業員詳細で新しい設定を入力する</t>
+          <t>操作</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
           <t>月の途中で交通費を変更された場合、交通費は日割りいたしません。月額の方はその月は変更前の金額のまま、翌月から新しい金額になります（定期代は月単位でご購入いただくためです）。日額の方は、適用日以降にご出勤された日から新しい金額になります。</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr"/>
-    </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>同じ適用日付で2回保存された場合は、あとから保存されたほうが有効になります。前のものも設定変更履歴に残りますので、経緯をたどれます。将来の日付のご予約は何件でも登録でき、適用日付の順に反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr"/>
-    </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr"/>
-    </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
         <is>
           <t>すでにご利用中のお客様</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>設定の入力</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
+          <t>変更履歴</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
           <t>店舗別の人件費</t>
         </is>
       </c>
-      <c r="B230" s="2" t="inlineStr">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="3" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが空</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>従業員コードが重複</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
+          <t>雇用区分が不正</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
           <t>列がずれる</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
         <is>
           <t>設定が保存できません</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費が未入力</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>ヘルプ先交通費が未入力</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
           <t>必須項目の警告が表示される</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
         <is>
           <t>数字・締めについて</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>ご質問</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>締めたあとに数字を直したい</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>店舗別の合計が全社と合わない</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
           <t>給与のみ変更したい</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
         <is>
           <t>どなたが操作できますか</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧・設定の編集</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>オーナー・本部管理</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>権限設定によります</t>
+          <t>店長</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -3311,7 +3296,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>今回のリリースでは対象外</t>
+          <t>権限設定によります</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -3323,7 +3308,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>給与実績一覧の閲覧</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -3333,7 +3318,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>今回のリリースでは対象外</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -3345,141 +3330,163 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
           <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
         <is>
           <t>この機能でできないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>給与明細の作成・支給や控除の計算</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+          <t>ご利用いただくもの</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
+          <t>給与明細の作成・支給や控除の計算</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>出退勤の打刻・シフトの作成</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>ラクミータイムレコード</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
           <t>入退社の手続き・年末調整</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>本機能の対象外です</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
         <is>
           <t>解決しない場合</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
-        <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
+          <t>お知らせいただく内容</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>確認場所</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>画面に表示されたメッセージ</t>
+          <t>対象の従業員コードと年月</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>該当画面</t>
+          <t>従業員一覧／給与実績一覧</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2370,544 +2370,539 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>勤怠システムで新しく登録された方がいるとき</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
+          <t>ラクミーに登録の無い従業員コードが勤怠データに含まれていた場合、その方の実績は取り込まれず、件数と理由が「実績の取込結果」に表示されます。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+          <t>自動で追加したい場合は、連携設定の「新しい従業員を自動で追加する」をONにしてください（既定はOFF）。</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
+          <t>設定</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
+          <t>取り込んだときの動き</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>テンプレート登録</t>
+          <t>OFF（既定）</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>名称・データ種類・列の対応を設定</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>「行を追加」でマッピング行を追加</t>
+          <t>取り込まず、件数と理由を表示します</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>編集・削除</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>保存済みテンプレートの変更</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>編集時は「更新する」で保存</t>
+          <t>従業員を自動で追加し、従業員一覧に表示します</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>テンプレートダウンロード</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>マッピング表のCSVを取得</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>行数が多い場合に使用</t>
+          <t>📸 連携設定の自動追加チェックボックス｜「新しい従業員を自動で追加する」がOFFの状態で撮影。</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>マッピングテンプレートファイル</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>記入したCSVをアップロード</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>CSV最大10MB</t>
+          <t>自動で追加された方は、給与設定が空の状態です。単価が入っていないため人件費を計算できません。給与実績一覧のエラーの絞り込み「給与設定が未入力」でご確認のうえ、従業員詳細から設定をご入力ください。</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
-        </is>
-      </c>
+      <c r="A172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>退職された方の登録</t>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>既定をOFFにしているのは、退職された方の打刻が残っていた場合など、意図しない方が追加されることを防ぐためです。</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>従業員一覧から外れ、概算モードの見込みからも外れます（これからかかる人件費の見込みなので、退職された方は含めません）。過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
+          <t>勤怠システムによって列名が異なります（例：従業員コード／スタッフコード）。列マッピングテンプレートに対応づけを保存いただくと、次回以降は選択するだけで取り込めます。設定インポートの「列マッピングテンプレート」から開きます。</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr"/>
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>📸 列マッピングテンプレート｜勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>数字が合わないとき</t>
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>テンプレート登録</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>名称・データ種類・列の対応を設定</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>「行を追加」でマッピング行を追加</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
+          <t>編集・削除</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>保存済みテンプレートの変更</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>編集時は「更新する」で保存</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>順</t>
+          <t>テンプレートダウンロード</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>確認する内容</t>
+          <t>マッピング表のCSVを取得</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>確認する場所</t>
+          <t>行数が多い場合に使用</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>マッピングテンプレートファイル</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>設定がいつ・どの経路で変わったか</t>
+          <t>記入したCSVをアップロード</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>CSV最大10MB</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ設定の元データ</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>設定の取込結果</t>
+          <t>CSVの先頭に説明行が入っている場合は、設定インポートの「CSV位置合わせ設定」でヘッダー行・データ開始行・開始列をご指定ください。</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>取り込んだ勤怠実績の元データ</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>実績の取込結果</t>
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>退職された方の登録</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>1日ごとの内訳</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>従業員詳細の在籍状態を「退職」に変更してください。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>従業員一覧から外れ、概算モードの見込みからも外れます（これからかかる人件費の見込みなので、退職された方は含めません）。過去の人件費と設定変更履歴はそのまま残ります。給与実績一覧で過去の月をご覧いただくと、在籍されていた月には表示されます。</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
-        </is>
-      </c>
+      <c r="A186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>削除はなさらないでください。実績のある方を削除すると、確定済みの人件費が変わってしまいます。実績のない方（誤って登録された場合など）だけ削除いただけます。</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>変更反映日時</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>設定が有効となる日付</t>
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>編集日時</t>
-        </is>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>設定を入力した日時。変更反映日時とは異なります</t>
+          <t>上から順にご確認いただくと、原因を絞り込めます。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ステータス</t>
+          <t>順</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>適用中／予約中／過去</t>
+          <t>確認する内容</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>確認する場所</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>変更ソース</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
+          <t>設定がいつ・どの経路で変わったか</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>絞り込み</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
+          <t>取り込んだ設定の元データ</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>設定の取込結果</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>取り込んだ勤怠実績の元データ</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>実績の取込結果</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>1日ごとの内訳</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧（日別実績）</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
+          <t>📸 設定変更履歴一覧｜変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>扱い</t>
+          <t>設定変更履歴一覧では、変更の経緯を次の内容で確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ人件費</t>
+          <t>変更反映日時</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
+          <t>設定が有効となる日付</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ先交通費</t>
+          <t>編集日時</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+          <t>設定を入力した日時。変更反映日時とは異なります</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>全社の合計</t>
+          <t>ステータス</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>変わりません。店舗間で振り替えているだけのためです</t>
+          <t>適用中／予約中／過去</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>変更ソース</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>手動編集／更新予約／CSVインポート(King of Time)／CSVインポート(ジョブカン)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
+          <t>絞り込み</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>変更ソース／店舗・雇用区分／編集日時範囲／従業員名</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
+          <t>まず変更ソースをご確認ください。手動編集であれば操作された方に、CSVインポートであれば設定の取込結果で元のファイルをご確認いただけます。</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr"/>
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
+          <t>応援に出た分の人件費は、所属店舗から差し引き、応援先の店舗に計上します。実際に働いた店舗の損益と合わせるためです。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
+          <t>タイトル</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr"/>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ時間</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>応援先店舗で勤務した時間。日別実績の合計です</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
+          <t>ヘルプ人件費</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>（給与部分 × ヘルプ時間 ÷ 総労働時間）＋ 応援先の交通費</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr"/>
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>応援先ごとに個別に設定します。設定した金額はヘルプ人件費に含めて表示されます</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
+          <t>全社の合計</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>変わりません。店舗間で振り替えているだけのためです</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>📸 給与実績一覧（日別実績）｜ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
+          <t>店舗を絞ってご覧になる場合は、従業員一覧で店舗を選び「この店舗の給与実績一覧」からお進みください。絞り込みが引き継がれます。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>順</t>
-        </is>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>操作</t>
+          <t>取り込みでエラーがあった場合の扱いは次のとおりです。</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>従業員詳細で新しい設定を入力する</t>
-        </is>
-      </c>
+      <c r="A214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
+          <t>- 交通費が未設定の方 … 交通費0円として計算し、金額は表示します。エラーの絞り込み「交通費欠損」で抽出できます</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
+          <t>- 出退勤の打刻漏れがある日 … その日は出勤日に数えず、日別にも表示しません。エラーの絞り込み「出退勤打刻漏れ」で抽出できます</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
-        </is>
-      </c>
+      <c r="A217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>月の途中で交通費を変更された場合、交通費は日割りいたしません。月額の方はその月は変更前の金額のまま、翌月から新しい金額になります（定期代は月単位でご購入いただくためです）。日額の方は、適用日以降にご出勤された日から新しい金額になります。</t>
+          <t>あとから出勤として扱う場合は、勤怠システム側で打刻を修正してから、その月を取り込み直してください。締め済みの月は、締めを解除してから取り込み直し、もう一度締めます。</t>
         </is>
       </c>
     </row>
@@ -2917,576 +2912,662 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>同じ適用日付で2回保存された場合は、あとから保存されたほうが有効になります。前のものも設定変更履歴に残りますので、経緯をたどれます。将来の日付のご予約は何件でも登録でき、適用日付の順に反映されます。</t>
+          <t>店舗別の金額が想定と異なる場合は、日別実績のヘルプ時間をご確認ください。交通費に専用の列はございません。所属店舗分は人件費に、応援先分はヘルプ人件費に含めて表示しております。</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr"/>
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
+          <t>締めた月に遡る改定が決まった場合は、次の手順で対応いただけます。</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr"/>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>従業員詳細で新しい設定を入力する</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>すでにご利用中のお客様</t>
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>適用日付に、締め済み期間の翌日以降を指定して保存する</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>差額の調整が必要な場合は、翌月の人件費で調整する（基本給のみが対象です）</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>タイトル</t>
-        </is>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
+          <t>📸 締め済み期間の警告｜締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>過去の月の人件費</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
+          <t>月の途中で交通費を変更された場合、交通費は日割りいたしません。月額の方はその月は変更前の金額のまま、翌月から新しい金額になります（定期代は月単位でご購入いただくためです）。日額の方は、適用日以降にご出勤された日から新しい金額になります。</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>設定の入力</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
-        </is>
-      </c>
+      <c r="A229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>変更履歴</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>移行時点の設定が履歴の1件目として記録されます</t>
+          <t>同じ適用日付で2回保存された場合は、あとから保存されたほうが有効になります。前のものも設定変更履歴に残りますので、経緯をたどれます。将来の日付のご予約は何件でも登録でき、適用日付の順に反映されます。</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
-        <is>
-          <t>店舗別の人件費</t>
-        </is>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
-        </is>
-      </c>
+      <c r="A231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>翌月に回す差額の調整は基本給だけを対象としております。深夜残業代・みなし超過残業代・交通費は、単価が変われば自動で計算し直されるためです。</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>CSVの取り込みでエラーになります</t>
-        </is>
-      </c>
+      <c r="A233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>エラーの内容</t>
-        </is>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
+          <t>締めた月に遡る日付を指定した場合は警告が表示され、反映されません。締めを解除して修正することも可能ですが、確定済みの数字が変わるため、通常の運用ではおすすめしておりません。</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードが空</t>
-        </is>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>従業員コードは必須です。全行にご入力ください</t>
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>従業員コードが重複</t>
-        </is>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
+          <t>既存の従業員データはそのまま引き継がれます。項目の増減はございません。</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>金額がマイナス・数字以外</t>
+          <t>タイトル</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
+          <t>内容</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>店舗が見つからない</t>
+          <t>過去の月の人件費</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
+          <t>変わりません。既存の設定に過去日の適用日付を付与するため、過去の月は当時の設定で計算されます</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>雇用区分が不正</t>
+          <t>設定の入力</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
+          <t>入れ直す必要はございません。適用日付の欄が追加されます</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>列がずれる</t>
+          <t>変更履歴</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
+          <t>移行時点の設定が履歴の1件目として記録されます</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>設定が保存できません</t>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の人件費</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>応援勤務がある場合は変わります。応援先店舗に人件費が移るためです。全社の合計は変わりません</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>状況</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>対処</t>
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先交通費が未入力</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>締め済み期間の警告が表示される</t>
+          <t>エラーの内容</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>必須項目の警告が表示される</t>
+          <t>従業員コードが空</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
+          <t>従業員コードは必須です。全行にご入力ください</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="4" t="inlineStr">
-        <is>
-          <t>数字・締めについて</t>
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>従業員コードが重複</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>同じコードの従業員は登録できません。コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>ご質問</t>
+          <t>金額がマイナス・数字以外</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>回答</t>
+          <t>単位給与額・交通費は0以上の数字でご入力ください</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>実績の金額が表示されない</t>
+          <t>店舗が見つからない</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
+          <t>未登録の店舗コードです。先に店舗を登録するか、コードをご確認ください</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>締めたあとに数字を直したい</t>
+          <t>雇用区分が不正</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
+          <t>正社員／パート／アルバイトのいずれかでご入力ください</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+          <t>列がずれる</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
+          <t>CSVの先頭に説明行がある可能性があります。CSV位置合わせ設定で開始行をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>店舗別の合計が全社と合わない</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>給与のみ変更したい</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
+          <t>対処</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>どなたが操作できますか</t>
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ先交通費が未入力</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ先店舗を選択した場合、店舗ごとの交通費がすべて必須です</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
+          <t>締め済み期間の警告が表示される</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>その月はすでに締められております。翌月以降の適用日付をご指定ください</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>操作</t>
+          <t>必須項目の警告が表示される</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>オーナー・本部管理</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>店長</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>従業員</t>
+          <t>名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額・適用日付は必須です</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧・設定の編集</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>権限設定によります</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧の閲覧</t>
+          <t>ご質問</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>今回のリリースでは対象外</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>回答</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>月次の締め・締め解除</t>
+          <t>実績の金額が表示されない</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>不可</t>
+          <t>実績データ取込がお済みでない可能性があります。給与実績一覧の「実績データ取込」を実行してください</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
+          <t>締めたあとに数字を直したい</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>締めを解除すると編集可能になり、再計算されます。ただし確定済みの数字が変わるため、通常は翌月での調整をおすすめしております</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
+          <t>日別実績の概算と実績で、同じ日の金額が違う</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>用途が異なるためです。概算は「営業日1日あたりの見込み人件費」（月次の概算給与 ÷ 営業日数）、実績モードの想定給与は「その方が1日働いたときの標準額」（月次の概算給与 ÷ 想定労働日数）です</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>この機能でできないこと</t>
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>店舗別の合計が全社と合わない</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>合計は一致する仕様です。相違がある場合はサポートまでお問い合わせください</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>給与のみ変更したい</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>ご利用いただくもの</t>
+          <t>給与設定のCSVテンプレートのみを取り込んでください。従業員設定とは別のテンプレートです</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>給与明細の作成・支給や控除の計算</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>出退勤の打刻・シフトの作成</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>ラクミータイムレコード</t>
+          <t>給与情報を含むため、権限設定で参照できる範囲を制御しております。</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>ログインアカウントの発行・権限の設定</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>権限設定</t>
+          <t>オーナー・本部管理</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>店長</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>従業員</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>入退社の手続き・年末調整</t>
+          <t>従業員一覧・設定の編集</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>本機能の対象外です</t>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>権限設定によります</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>解決しない場合</t>
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>給与実績一覧の閲覧</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>今回のリリースでは対象外</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+          <t>月次の締め・締め解除</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>不可</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>お知らせいただく内容</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>確認場所</t>
+          <t>締めは会社単位で行うため、店長は実行できません。店舗ごとに締めると月次が分断されるためです。</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>対象の従業員コードと年月</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>従業員一覧／給与実績一覧</t>
+          <t>給与実績一覧は店舗単位での絞り込みに対応しておりません。店長に公開すると全社の金額が表示されるため、権限設定では非公開としてください。店舗単位での参照は次の段階での対応を予定しております。</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>画面に表示されたメッセージ</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>該当画面</t>
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>この機能でできないこと</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>ご利用いただくもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>給与明細の作成・支給や控除の計算</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>給与計算ソフト（データはエクスポートで出力可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>出退勤の打刻・シフトの作成</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>ラクミータイムレコード</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>ログインアカウントの発行・権限の設定</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>権限設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>入退社の手続き・年末調整</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>本機能の対象外です</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>解決しない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>サポートまでお問い合わせください。お問い合わせの際は次をお知らせいただくとスムーズです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>お知らせいただく内容</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>確認場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>対象の従業員コードと年月</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>従業員一覧／給与実績一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>画面に表示されたメッセージ</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>該当画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
           <t>変更ソース（手動編集／CSVインポート）</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>設定変更履歴一覧</t>
         </is>
@@ -3503,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3514,7 +3595,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>ヘルプページ 撮影が必要なスクリーンショット（16点）</t>
+          <t>ヘルプページ 撮影が必要なスクリーンショット（17点）</t>
         </is>
       </c>
     </row>
@@ -3715,33 +3796,33 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>連携設定の自動追加チェックボックス</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
+          <t>「新しい従業員を自動で追加する」がOFFの状態で撮影。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
+          <t>勤怠システムの列名（例：スタッフコード）とラクミーの項目（従業員コード）が対応づいている状態。</t>
         </is>
       </c>
     </row>
@@ -3751,12 +3832,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>給与実績一覧（日別実績）</t>
+          <t>設定変更履歴一覧</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+          <t>変更ソースで絞り込み、手動編集とCSVインポートの行が混在している状態。</t>
         </is>
       </c>
     </row>
@@ -3766,10 +3847,25 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>給与実績一覧（日別実績）</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ヘルプ時間・ヘルプ人件費の列と、所属店舗分・応援先分に分かれた交通費の列が見える状態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>締め済み期間の警告</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>締めた月に遡る適用日付を入れて保存しようとしたときの警告表示。</t>
         </is>
@@ -4168,7 +4264,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>撮影が必要なスクリーンショットは「撮影一覧」シート（16点）を見てください。本文の 📸 から自動で作っているため、本文と必ず一致します。</t>
+          <t>撮影が必要なスクリーンショットは「撮影一覧」シート（17点）を見てください。本文の 📸 から自動で作っているため、本文と必ず一致します。</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -2434,7 +2434,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>自動で追加された方は、給与設定が空の状態です。単価が入っていないため人件費を計算できません。給与実績一覧のエラーの絞り込み「給与設定が未入力」でご確認のうえ、従業員詳細から設定をご入力ください。</t>
+          <t>自動で追加された方は、給与設定が空の状態です。単価が入っていないため人件費を計算できません。従業員一覧の絞り込み「設定 → 給与設定が未入力」で該当の方を抽出し、従業員詳細から設定をご入力ください。給与実績一覧の「エラー → 給与設定が未入力」でも、その月の金額が欠けている方をご確認いただけます。</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_05_ヘルプページ.xlsx
+++ b/20260805_従業員管理_05_ヘルプページ.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>通常はご入力不要です。勤怠実績の打刻から、直近3か月の平均出勤日数を自動で使います。実際と違う日数で見込みたい場合だけご入力ください。打刻がまだ無い場合（導入直後・新しくご登録された方）は、月給の方は所属店舗の営業日数を使います</t>
+          <t>通常はご入力不要です。勤怠実績の打刻から、直近3か月の平均出勤日数を自動で使います。一度使われた日数はその月の値として保存されますので、あとから月を取り込み直しても過去の月の金額は変わりません。実際と違う日数で見込みたい場合だけご入力ください。打刻がまだ無い場合（導入直後・新しくご登録された方）は、月給の方は所属店舗の営業日数を使います</t>
         </is>
       </c>
     </row>
